--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <f>SUM('SO_260219_Dum'!I53:I449)</f>
+        <f>SUM('SO_260219_Dum'!I53:I451)</f>
         <v/>
       </c>
       <c r="E14" s="7">
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L450"/>
+  <dimension ref="B2:L452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="D16" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C16)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C16)</f>
         <v/>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="D17" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C17)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C17)</f>
         <v/>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="D18" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C18)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C18)</f>
         <v/>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="D19" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C19)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C19)</f>
         <v/>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="D20" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C20)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C20)</f>
         <v/>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="D21" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C21)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C21)</f>
         <v/>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="D22" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C22)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C22)</f>
         <v/>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="D23" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C23)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C23)</f>
         <v/>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="D24" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C24)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C24)</f>
         <v/>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D25" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C25)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C25)</f>
         <v/>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="D26" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C26)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C26)</f>
         <v/>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="D27" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C27)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C27)</f>
         <v/>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="D28" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C28)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C28)</f>
         <v/>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="D29" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C29)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C29)</f>
         <v/>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D30" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C30)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C30)</f>
         <v/>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="D31" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C31)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C31)</f>
         <v/>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="D32" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C32)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C32)</f>
         <v/>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="D33" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C33)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C33)</f>
         <v/>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="D34" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C34)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C34)</f>
         <v/>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="D35" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C35)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C35)</f>
         <v/>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D36" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C36)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C36)</f>
         <v/>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D37" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C37)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C37)</f>
         <v/>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="D38" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C38)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C38)</f>
         <v/>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D39" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C39)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C39)</f>
         <v/>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="D40" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C40)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C40)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="D41" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C41)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C41)</f>
         <v/>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="D42" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C42)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C42)</f>
         <v/>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="D43" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C43)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C43)</f>
         <v/>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="D44" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C44)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C44)</f>
         <v/>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="D45" s="7">
-        <f>SUMIFS(I51:I450,L51:L450,C45)</f>
+        <f>SUMIFS(I51:I452,L51:L452,C45)</f>
         <v/>
       </c>
     </row>
@@ -5875,100 +5875,100 @@
       <c r="L176" s="17" t="n"/>
     </row>
     <row r="177">
-      <c r="B177" s="21" t="n"/>
-      <c r="C177" s="22" t="inlineStr">
+      <c r="B177" s="23" t="n">
+        <v>61</v>
+      </c>
+      <c r="C177" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D177" s="24" t="inlineStr">
+        <is>
+          <t>762085112</t>
+        </is>
+      </c>
+      <c r="E177" s="24" t="inlineStr">
+        <is>
+          <t>Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
+        </is>
+      </c>
+      <c r="F177" s="23" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G177" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="H177" s="26" t="n"/>
+      <c r="I177" s="26">
+        <f>IF(H177="",0,G177*H177)</f>
+        <v/>
+      </c>
+      <c r="J177" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K177" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L177" s="5" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="17" t="n"/>
+      <c r="C178" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D178" s="17" t="n"/>
+      <c r="E178" s="29" t="inlineStr">
+        <is>
+          <t>11 pozic kleštin × 2 konce × 2 svorníky/spoj = 44 ks + rezerva ≈ 50 ks</t>
+        </is>
+      </c>
+      <c r="F178" s="17" t="n"/>
+      <c r="G178" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="H178" s="17" t="n"/>
+      <c r="I178" s="17" t="n"/>
+      <c r="J178" s="17" t="n"/>
+      <c r="K178" s="17" t="n"/>
+      <c r="L178" s="17" t="n"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="21" t="n"/>
+      <c r="C179" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D177" s="22" t="inlineStr">
+      <c r="D179" s="22" t="inlineStr">
         <is>
           <t>HSV-6</t>
         </is>
       </c>
-      <c r="E177" s="22" t="inlineStr">
+      <c r="E179" s="22" t="inlineStr">
         <is>
           <t>HSV-6 Bourací práce</t>
         </is>
       </c>
-      <c r="F177" s="21" t="n"/>
-      <c r="G177" s="21" t="n"/>
-      <c r="H177" s="21" t="n"/>
-      <c r="I177" s="21" t="n"/>
-      <c r="J177" s="21" t="n"/>
-      <c r="K177" s="21" t="n"/>
-      <c r="L177" s="21" t="n"/>
-    </row>
-    <row r="178">
-      <c r="B178" s="23" t="n">
-        <v>61</v>
-      </c>
-      <c r="C178" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D178" s="24" t="inlineStr">
-        <is>
-          <t>962041141</t>
-        </is>
-      </c>
-      <c r="E178" s="24" t="inlineStr">
-        <is>
-          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
-        </is>
-      </c>
-      <c r="F178" s="23" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G178" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="H178" s="26" t="n"/>
-      <c r="I178" s="26">
-        <f>IF(H178="",0,G178*H178)</f>
-        <v/>
-      </c>
-      <c r="J178" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K178" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu202/801-3-Budovy-a-haly---b]</t>
-        </is>
-      </c>
-      <c r="L178" s="5" t="inlineStr">
-        <is>
-          <t>HSV-6 Bourací práce</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="B179" s="17" t="n"/>
-      <c r="C179" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D179" s="17" t="n"/>
-      <c r="E179" s="29" t="inlineStr">
-        <is>
-          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
-        </is>
-      </c>
-      <c r="F179" s="17" t="n"/>
-      <c r="G179" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="H179" s="17" t="n"/>
-      <c r="I179" s="17" t="n"/>
-      <c r="J179" s="17" t="n"/>
-      <c r="K179" s="17" t="n"/>
-      <c r="L179" s="17" t="n"/>
+      <c r="F179" s="21" t="n"/>
+      <c r="G179" s="21" t="n"/>
+      <c r="H179" s="21" t="n"/>
+      <c r="I179" s="21" t="n"/>
+      <c r="J179" s="21" t="n"/>
+      <c r="K179" s="21" t="n"/>
+      <c r="L179" s="21" t="n"/>
     </row>
     <row r="180">
       <c r="B180" s="23" t="n">
@@ -5979,19 +5979,23 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D180" s="24" t="inlineStr"/>
+      <c r="D180" s="24" t="inlineStr">
+        <is>
+          <t>962041141</t>
+        </is>
+      </c>
       <c r="E180" s="24" t="inlineStr">
         <is>
-          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
+          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
         </is>
       </c>
       <c r="F180" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G180" s="25" t="n">
-        <v>140.9</v>
+        <v>12</v>
       </c>
       <c r="H180" s="26" t="n"/>
       <c r="I180" s="26">
@@ -6003,9 +6007,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K180" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
+      <c r="K180" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu202/801-3-Budovy-a-haly---b]</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
@@ -6022,13 +6026,14 @@
         </is>
       </c>
       <c r="D181" s="17" t="n"/>
-      <c r="E181" s="29">
-        <f> plocha krytiny ~141</f>
-        <v/>
+      <c r="E181" s="29" t="inlineStr">
+        <is>
+          <t>TZ B m.10.e: 9 t dřeva × 0.75 t/m³ = 12 m³ dřeva</t>
+        </is>
       </c>
       <c r="F181" s="17" t="n"/>
       <c r="G181" s="30" t="n">
-        <v>140.9</v>
+        <v>12</v>
       </c>
       <c r="H181" s="17" t="n"/>
       <c r="I181" s="17" t="n"/>
@@ -6045,23 +6050,19 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D182" s="24" t="inlineStr">
-        <is>
-          <t>962031132</t>
-        </is>
-      </c>
+      <c r="D182" s="24" t="inlineStr"/>
       <c r="E182" s="24" t="inlineStr">
         <is>
-          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
+          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
         </is>
       </c>
       <c r="F182" s="23" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G182" s="25" t="n">
-        <v>6</v>
+        <v>140.9</v>
       </c>
       <c r="H182" s="26" t="n"/>
       <c r="I182" s="26">
@@ -6073,9 +6074,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K182" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K182" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
       <c r="L182" s="5" t="inlineStr">
@@ -6092,14 +6093,13 @@
         </is>
       </c>
       <c r="D183" s="17" t="n"/>
-      <c r="E183" s="29" t="inlineStr">
-        <is>
-          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
-        </is>
+      <c r="E183" s="29">
+        <f> plocha krytiny ~141</f>
+        <v/>
       </c>
       <c r="F183" s="17" t="n"/>
       <c r="G183" s="30" t="n">
-        <v>6</v>
+        <v>140.9</v>
       </c>
       <c r="H183" s="17" t="n"/>
       <c r="I183" s="17" t="n"/>
@@ -6118,21 +6118,21 @@
       </c>
       <c r="D184" s="24" t="inlineStr">
         <is>
-          <t>962041141</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="E184" s="24" t="inlineStr">
         <is>
-          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
+          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
         </is>
       </c>
       <c r="F184" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G184" s="25" t="n">
-        <v>104.4</v>
+        <v>6</v>
       </c>
       <c r="H184" s="26" t="n"/>
       <c r="I184" s="26">
@@ -6163,13 +6163,14 @@
         </is>
       </c>
       <c r="D185" s="17" t="n"/>
-      <c r="E185" s="29">
-        <f> zastavěna 104.4 m²</f>
-        <v/>
+      <c r="E185" s="29" t="inlineStr">
+        <is>
+          <t>odhad — 3.NP nadezdívka půdy ~104 m² × 0.45 m výška ~6</t>
+        </is>
       </c>
       <c r="F185" s="17" t="n"/>
       <c r="G185" s="30" t="n">
-        <v>104.4</v>
+        <v>6</v>
       </c>
       <c r="H185" s="17" t="n"/>
       <c r="I185" s="17" t="n"/>
@@ -6188,12 +6189,12 @@
       </c>
       <c r="D186" s="24" t="inlineStr">
         <is>
-          <t>962031132</t>
+          <t>962041141</t>
         </is>
       </c>
       <c r="E186" s="24" t="inlineStr">
         <is>
-          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
+          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
         </is>
       </c>
       <c r="F186" s="23" t="inlineStr">
@@ -6202,7 +6203,7 @@
         </is>
       </c>
       <c r="G186" s="25" t="n">
-        <v>80</v>
+        <v>104.4</v>
       </c>
       <c r="H186" s="26" t="n"/>
       <c r="I186" s="26">
@@ -6233,14 +6234,13 @@
         </is>
       </c>
       <c r="D187" s="17" t="n"/>
-      <c r="E187" s="29" t="inlineStr">
-        <is>
-          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
-        </is>
+      <c r="E187" s="29">
+        <f> zastavěna 104.4 m²</f>
+        <v/>
       </c>
       <c r="F187" s="17" t="n"/>
       <c r="G187" s="30" t="n">
-        <v>80</v>
+        <v>104.4</v>
       </c>
       <c r="H187" s="17" t="n"/>
       <c r="I187" s="17" t="n"/>
@@ -6264,16 +6264,16 @@
       </c>
       <c r="E188" s="24" t="inlineStr">
         <is>
-          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
+          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
         </is>
       </c>
       <c r="F188" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G188" s="25" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="H188" s="26" t="n"/>
       <c r="I188" s="26">
@@ -6306,12 +6306,12 @@
       <c r="D189" s="17" t="n"/>
       <c r="E189" s="29" t="inlineStr">
         <is>
-          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
+          <t>odhad — interier 2 patra × ~40 m² příček = 80</t>
         </is>
       </c>
       <c r="F189" s="17" t="n"/>
       <c r="G189" s="30" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="H189" s="17" t="n"/>
       <c r="I189" s="17" t="n"/>
@@ -6330,21 +6330,21 @@
       </c>
       <c r="D190" s="24" t="inlineStr">
         <is>
-          <t>781473810</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="E190" s="24" t="inlineStr">
         <is>
-          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
+          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
         </is>
       </c>
       <c r="F190" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G190" s="25" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="H190" s="26" t="n"/>
       <c r="I190" s="26">
@@ -6356,9 +6356,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K190" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu202/801-3-Budovy-a-haly---b]</t>
+      <c r="K190" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L190" s="5" t="inlineStr">
@@ -6377,12 +6377,12 @@
       <c r="D191" s="17" t="n"/>
       <c r="E191" s="29" t="inlineStr">
         <is>
-          <t>2 koupelny × ~30 m² obkladů = 60</t>
+          <t>odhad počtu nových otvorů (= počet IPN160 překladů)</t>
         </is>
       </c>
       <c r="F191" s="17" t="n"/>
       <c r="G191" s="30" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="H191" s="17" t="n"/>
       <c r="I191" s="17" t="n"/>
@@ -6401,12 +6401,12 @@
       </c>
       <c r="D192" s="24" t="inlineStr">
         <is>
-          <t>974031132</t>
+          <t>781473810</t>
         </is>
       </c>
       <c r="E192" s="24" t="inlineStr">
         <is>
-          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
+          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="F192" s="23" t="inlineStr">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="G192" s="25" t="n">
-        <v>153.51</v>
+        <v>60</v>
       </c>
       <c r="H192" s="26" t="n"/>
       <c r="I192" s="26">
@@ -6427,9 +6427,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K192" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K192" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu202/801-3-Budovy-a-haly---b]</t>
         </is>
       </c>
       <c r="L192" s="5" t="inlineStr">
@@ -6448,12 +6448,12 @@
       <c r="D193" s="17" t="n"/>
       <c r="E193" s="29" t="inlineStr">
         <is>
-          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
+          <t>2 koupelny × ~30 m² obkladů = 60</t>
         </is>
       </c>
       <c r="F193" s="17" t="n"/>
       <c r="G193" s="30" t="n">
-        <v>153.51</v>
+        <v>60</v>
       </c>
       <c r="H193" s="17" t="n"/>
       <c r="I193" s="17" t="n"/>
@@ -6472,21 +6472,21 @@
       </c>
       <c r="D194" s="24" t="inlineStr">
         <is>
-          <t>974041151</t>
+          <t>974031132</t>
         </is>
       </c>
       <c r="E194" s="24" t="inlineStr">
         <is>
-          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
+          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
         </is>
       </c>
       <c r="F194" s="23" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G194" s="25" t="n">
-        <v>5</v>
+        <v>153.51</v>
       </c>
       <c r="H194" s="26" t="n"/>
       <c r="I194" s="26">
@@ -6519,12 +6519,12 @@
       <c r="D195" s="17" t="n"/>
       <c r="E195" s="29" t="inlineStr">
         <is>
-          <t>100 m² × 0.05 m tl. zásypu = 5</t>
+          <t>podlahova × 0.7 = ~154 m² (bez 3.NP nového)</t>
         </is>
       </c>
       <c r="F195" s="17" t="n"/>
       <c r="G195" s="30" t="n">
-        <v>5</v>
+        <v>153.51</v>
       </c>
       <c r="H195" s="17" t="n"/>
       <c r="I195" s="17" t="n"/>
@@ -6543,21 +6543,21 @@
       </c>
       <c r="D196" s="24" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>974041151</t>
         </is>
       </c>
       <c r="E196" s="24" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
         </is>
       </c>
       <c r="F196" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G196" s="25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H196" s="26" t="n"/>
       <c r="I196" s="26">
@@ -6590,12 +6590,12 @@
       <c r="D197" s="17" t="n"/>
       <c r="E197" s="29" t="inlineStr">
         <is>
-          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
+          <t>100 m² × 0.05 m tl. zásypu = 5</t>
         </is>
       </c>
       <c r="F197" s="17" t="n"/>
       <c r="G197" s="30" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H197" s="17" t="n"/>
       <c r="I197" s="17" t="n"/>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="D198" s="24" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>968071120</t>
         </is>
       </c>
       <c r="E198" s="24" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
         </is>
       </c>
       <c r="F198" s="23" t="inlineStr">
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G198" s="25" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H198" s="26" t="n"/>
       <c r="I198" s="26">
@@ -6661,12 +6661,12 @@
       <c r="D199" s="17" t="n"/>
       <c r="E199" s="29" t="inlineStr">
         <is>
-          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
+          <t>odhad — ~10 oken + ~15 dveří (vstupní + vnitřní)</t>
         </is>
       </c>
       <c r="F199" s="17" t="n"/>
       <c r="G199" s="30" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H199" s="17" t="n"/>
       <c r="I199" s="17" t="n"/>
@@ -6685,21 +6685,21 @@
       </c>
       <c r="D200" s="24" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="E200" s="24" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="F200" s="23" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G200" s="25" t="n">
-        <v>56.5</v>
+        <v>12</v>
       </c>
       <c r="H200" s="26" t="n"/>
       <c r="I200" s="26">
@@ -6732,12 +6732,12 @@
       <c r="D201" s="17" t="n"/>
       <c r="E201" s="29" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
+          <t>odhad — 2 koupelny × ~5 ks + WC + dřez = ~12</t>
         </is>
       </c>
       <c r="F201" s="17" t="n"/>
       <c r="G201" s="30" t="n">
-        <v>56.5</v>
+        <v>12</v>
       </c>
       <c r="H201" s="17" t="n"/>
       <c r="I201" s="17" t="n"/>
@@ -6756,21 +6756,21 @@
       </c>
       <c r="D202" s="24" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>997013501</t>
         </is>
       </c>
       <c r="E202" s="24" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="F202" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>t</t>
         </is>
       </c>
       <c r="G202" s="25" t="n">
-        <v>16</v>
+        <v>56.5</v>
       </c>
       <c r="H202" s="26" t="n"/>
       <c r="I202" s="26">
@@ -6803,12 +6803,12 @@
       <c r="D203" s="17" t="n"/>
       <c r="E203" s="29" t="inlineStr">
         <is>
-          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
+          <t>TZ B m.10.e: 46 (beton/cihly) + 9 (dřevo) + 0.1 (kov) + 0.1 (EPS) + 0.2 (sádra) + 1.0 (směs) = 56.4</t>
         </is>
       </c>
       <c r="F203" s="17" t="n"/>
       <c r="G203" s="30" t="n">
-        <v>16</v>
+        <v>56.5</v>
       </c>
       <c r="H203" s="17" t="n"/>
       <c r="I203" s="17" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="E204" s="24" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="F204" s="23" t="inlineStr">
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="G204" s="25" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H204" s="26" t="n"/>
       <c r="I204" s="26">
@@ -6874,12 +6874,12 @@
       <c r="D205" s="17" t="n"/>
       <c r="E205" s="29" t="inlineStr">
         <is>
-          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
+          <t>DXF INSERT okno* total 16 ks (Path C Tier 4 — front 9 + back 7)</t>
         </is>
       </c>
       <c r="F205" s="17" t="n"/>
       <c r="G205" s="30" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H205" s="17" t="n"/>
       <c r="I205" s="17" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="D206" s="24" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="E206" s="24" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="F206" s="23" t="inlineStr">
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="G206" s="25" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H206" s="26" t="n"/>
       <c r="I206" s="26">
@@ -6945,12 +6945,12 @@
       <c r="D207" s="17" t="n"/>
       <c r="E207" s="29" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
+          <t>DXF INSERT dveře = 2 (Path C Tier 4) + TZ ARS</t>
         </is>
       </c>
       <c r="F207" s="17" t="n"/>
       <c r="G207" s="30" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H207" s="17" t="n"/>
       <c r="I207" s="17" t="n"/>
@@ -6969,21 +6969,21 @@
       </c>
       <c r="D208" s="24" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="E208" s="24" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="F208" s="23" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G208" s="25" t="n">
-        <v>0.6</v>
+        <v>15</v>
       </c>
       <c r="H208" s="26" t="n"/>
       <c r="I208" s="26">
@@ -6995,9 +6995,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K208" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu202/801-3-Budovy-a-haly---b]</t>
+      <c r="K208" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L208" s="5" t="inlineStr">
@@ -7016,12 +7016,12 @@
       <c r="D209" s="17" t="n"/>
       <c r="E209" s="29" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
+          <t>DXF SM__dveře polylines 102 / ~3 fáze / ~2.3 symbol per dveře ≈ 15 ks návrh (Path C confidence 0.65)</t>
         </is>
       </c>
       <c r="F209" s="17" t="n"/>
       <c r="G209" s="30" t="n">
-        <v>0.6</v>
+        <v>15</v>
       </c>
       <c r="H209" s="17" t="n"/>
       <c r="I209" s="17" t="n"/>
@@ -7040,12 +7040,12 @@
       </c>
       <c r="D210" s="24" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="E210" s="24" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="F210" s="23" t="inlineStr">
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="G210" s="25" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="H210" s="26" t="n"/>
       <c r="I210" s="26">
@@ -7087,12 +7087,12 @@
       <c r="D211" s="17" t="n"/>
       <c r="E211" s="29" t="inlineStr">
         <is>
-          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
         </is>
       </c>
       <c r="F211" s="17" t="n"/>
       <c r="G211" s="30" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="H211" s="17" t="n"/>
       <c r="I211" s="17" t="n"/>
@@ -7101,100 +7101,100 @@
       <c r="L211" s="17" t="n"/>
     </row>
     <row r="212">
-      <c r="B212" s="21" t="n"/>
-      <c r="C212" s="22" t="inlineStr">
+      <c r="B212" s="23" t="n">
+        <v>78</v>
+      </c>
+      <c r="C212" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D212" s="24" t="inlineStr">
+        <is>
+          <t>961044111</t>
+        </is>
+      </c>
+      <c r="E212" s="24" t="inlineStr">
+        <is>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+        </is>
+      </c>
+      <c r="F212" s="23" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G212" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H212" s="26" t="n"/>
+      <c r="I212" s="26">
+        <f>IF(H212="",0,G212*H212)</f>
+        <v/>
+      </c>
+      <c r="J212" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K212" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu202/801-3-Budovy-a-haly---b]</t>
+        </is>
+      </c>
+      <c r="L212" s="5" t="inlineStr">
+        <is>
+          <t>HSV-6 Bourací práce</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" s="17" t="n"/>
+      <c r="C213" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D213" s="17" t="n"/>
+      <c r="E213" s="29" t="inlineStr">
+        <is>
+          <t>odhad ze řez A-A bourání + půdorys bourání 1.NP/1.PP, ~8 m³ celkem (opěrné zídky + venkovní schodiště zahrada/dvůr)</t>
+        </is>
+      </c>
+      <c r="F213" s="17" t="n"/>
+      <c r="G213" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H213" s="17" t="n"/>
+      <c r="I213" s="17" t="n"/>
+      <c r="J213" s="17" t="n"/>
+      <c r="K213" s="17" t="n"/>
+      <c r="L213" s="17" t="n"/>
+    </row>
+    <row r="214">
+      <c r="B214" s="21" t="n"/>
+      <c r="C214" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D212" s="22" t="inlineStr">
+      <c r="D214" s="22" t="inlineStr">
         <is>
           <t>HSV-7</t>
         </is>
       </c>
-      <c r="E212" s="22" t="inlineStr">
+      <c r="E214" s="22" t="inlineStr">
         <is>
           <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
-      <c r="F212" s="21" t="n"/>
-      <c r="G212" s="21" t="n"/>
-      <c r="H212" s="21" t="n"/>
-      <c r="I212" s="21" t="n"/>
-      <c r="J212" s="21" t="n"/>
-      <c r="K212" s="21" t="n"/>
-      <c r="L212" s="21" t="n"/>
-    </row>
-    <row r="213">
-      <c r="B213" s="23" t="n">
-        <v>78</v>
-      </c>
-      <c r="C213" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D213" s="24" t="inlineStr">
-        <is>
-          <t>622401110</t>
-        </is>
-      </c>
-      <c r="E213" s="24" t="inlineStr">
-        <is>
-          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
-        </is>
-      </c>
-      <c r="F213" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G213" s="25" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="H213" s="26" t="n"/>
-      <c r="I213" s="26">
-        <f>IF(H213="",0,G213*H213)</f>
-        <v/>
-      </c>
-      <c r="J213" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K213" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L213" s="5" t="inlineStr">
-        <is>
-          <t>HSV-7 Fasáda ETICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="B214" s="17" t="n"/>
-      <c r="C214" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D214" s="17" t="n"/>
-      <c r="E214" s="29" t="inlineStr">
-        <is>
-          <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
-        </is>
-      </c>
-      <c r="F214" s="17" t="n"/>
-      <c r="G214" s="30" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="H214" s="17" t="n"/>
-      <c r="I214" s="17" t="n"/>
-      <c r="J214" s="17" t="n"/>
-      <c r="K214" s="17" t="n"/>
-      <c r="L214" s="17" t="n"/>
+      <c r="F214" s="21" t="n"/>
+      <c r="G214" s="21" t="n"/>
+      <c r="H214" s="21" t="n"/>
+      <c r="I214" s="21" t="n"/>
+      <c r="J214" s="21" t="n"/>
+      <c r="K214" s="21" t="n"/>
+      <c r="L214" s="21" t="n"/>
     </row>
     <row r="215">
       <c r="B215" s="23" t="n">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="D215" s="24" t="inlineStr">
         <is>
-          <t>622221121</t>
+          <t>622401110</t>
         </is>
       </c>
       <c r="E215" s="24" t="inlineStr">
         <is>
-          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="F215" s="23" t="inlineStr">
@@ -7233,9 +7233,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K215" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.isover.cz/produkty/eps/isover-eps-70f]</t>
+      <c r="K215" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L215" s="5" t="inlineStr">
@@ -7254,7 +7254,7 @@
       <c r="D216" s="17" t="n"/>
       <c r="E216" s="29" t="inlineStr">
         <is>
-          <t>obvod 38.7 m × 0.55 × 13.0 m = 276.7 m² (PBŘ: tl. max 200 mm povolena, řez S01+S12a EXPLICIT 160 mm applied)</t>
+          <t>obvod 38.7 m (DXF) × 0.55 (volná fasáda, štíty zachované) × výška 13.0 m = 276.7 m²</t>
         </is>
       </c>
       <c r="F216" s="17" t="n"/>
@@ -7278,12 +7278,12 @@
       </c>
       <c r="D217" s="24" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>622221121</t>
         </is>
       </c>
       <c r="E217" s="24" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="F217" s="23" t="inlineStr">
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="G217" s="25" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="H217" s="26" t="n"/>
       <c r="I217" s="26">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="K217" s="31" t="inlineStr">
         <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://baumit.cz/produkty/komponenty-pro-zateplovani/zaklad]</t>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.isover.cz/produkty/eps/isover-eps-70f]</t>
         </is>
       </c>
       <c r="L217" s="5" t="inlineStr">
@@ -7325,12 +7325,12 @@
       <c r="D218" s="17" t="n"/>
       <c r="E218" s="29" t="inlineStr">
         <is>
-          <t>obvod 38.7 m × 0.5 m výška sokl × 0.7 (řadovka) = 13.5 m²</t>
+          <t>obvod 38.7 m × 0.55 × 13.0 m = 276.7 m² (PBŘ: tl. max 200 mm povolena, řez S01+S12a EXPLICIT 160 mm applied)</t>
         </is>
       </c>
       <c r="F218" s="17" t="n"/>
       <c r="G218" s="30" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="H218" s="17" t="n"/>
       <c r="I218" s="17" t="n"/>
@@ -7349,21 +7349,21 @@
       </c>
       <c r="D219" s="24" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622223111</t>
         </is>
       </c>
       <c r="E219" s="24" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="F219" s="23" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G219" s="25" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="H219" s="26" t="n"/>
       <c r="I219" s="26">
@@ -7375,9 +7375,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K219" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K219" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://baumit.cz/produkty/komponenty-pro-zateplovani/zaklad]</t>
         </is>
       </c>
       <c r="L219" s="5" t="inlineStr">
@@ -7396,12 +7396,12 @@
       <c r="D220" s="17" t="n"/>
       <c r="E220" s="29" t="inlineStr">
         <is>
-          <t>Σ per-typ okno 16 ks × per-window perimeter (2×(W+H)) z DXF bbox = 82.2 bm</t>
+          <t>obvod 38.7 m × 0.5 m výška sokl × 0.7 (řadovka) = 13.5 m²</t>
         </is>
       </c>
       <c r="F220" s="17" t="n"/>
       <c r="G220" s="30" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="H220" s="17" t="n"/>
       <c r="I220" s="17" t="n"/>
@@ -7425,16 +7425,16 @@
       </c>
       <c r="E221" s="24" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F221" s="23" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G221" s="25" t="n">
-        <v>1</v>
+        <v>82.2</v>
       </c>
       <c r="H221" s="26" t="n"/>
       <c r="I221" s="26">
@@ -7467,12 +7467,12 @@
       <c r="D222" s="17" t="n"/>
       <c r="E222" s="29" t="inlineStr">
         <is>
-          <t>paušál — dle pohledů NCS NZÚ</t>
+          <t>Σ per-typ okno 16 ks × per-window perimeter (2×(W+H)) z DXF bbox = 82.2 bm</t>
         </is>
       </c>
       <c r="F222" s="17" t="n"/>
       <c r="G222" s="30" t="n">
-        <v>1</v>
+        <v>82.2</v>
       </c>
       <c r="H222" s="17" t="n"/>
       <c r="I222" s="17" t="n"/>
@@ -7491,21 +7491,21 @@
       </c>
       <c r="D223" s="24" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E223" s="24" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F223" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G223" s="25" t="n">
-        <v>290.2</v>
+        <v>1</v>
       </c>
       <c r="H223" s="26" t="n"/>
       <c r="I223" s="26">
@@ -7517,9 +7517,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K223" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cz.weber/ncs-odstiny-dle-nzu-2023]</t>
+      <c r="K223" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L223" s="5" t="inlineStr">
@@ -7538,12 +7538,12 @@
       <c r="D224" s="17" t="n"/>
       <c r="E224" s="29" t="inlineStr">
         <is>
-          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
+          <t>paušál — dle pohledů NCS NZÚ</t>
         </is>
       </c>
       <c r="F224" s="17" t="n"/>
       <c r="G224" s="30" t="n">
-        <v>290.2</v>
+        <v>1</v>
       </c>
       <c r="H224" s="17" t="n"/>
       <c r="I224" s="17" t="n"/>
@@ -7552,125 +7552,125 @@
       <c r="L224" s="17" t="n"/>
     </row>
     <row r="225">
-      <c r="B225" s="19" t="n"/>
-      <c r="C225" s="20" t="inlineStr">
+      <c r="B225" s="23" t="n">
+        <v>84</v>
+      </c>
+      <c r="C225" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D225" s="24" t="inlineStr">
+        <is>
+          <t>622521111</t>
+        </is>
+      </c>
+      <c r="E225" s="24" t="inlineStr">
+        <is>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+        </is>
+      </c>
+      <c r="F225" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G225" s="25" t="n">
+        <v>290.2</v>
+      </c>
+      <c r="H225" s="26" t="n"/>
+      <c r="I225" s="26">
+        <f>IF(H225="",0,G225*H225)</f>
+        <v/>
+      </c>
+      <c r="J225" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K225" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cz.weber/ncs-odstiny-dle-nzu-2023]</t>
+        </is>
+      </c>
+      <c r="L225" s="5" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" s="17" t="n"/>
+      <c r="C226" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D226" s="17" t="n"/>
+      <c r="E226" s="29" t="inlineStr">
+        <is>
+          <t>ETICS plocha 276.7 m² + sokl 13.5 m² = 290.2 m²</t>
+        </is>
+      </c>
+      <c r="F226" s="17" t="n"/>
+      <c r="G226" s="30" t="n">
+        <v>290.2</v>
+      </c>
+      <c r="H226" s="17" t="n"/>
+      <c r="I226" s="17" t="n"/>
+      <c r="J226" s="17" t="n"/>
+      <c r="K226" s="17" t="n"/>
+      <c r="L226" s="17" t="n"/>
+    </row>
+    <row r="227">
+      <c r="B227" s="19" t="n"/>
+      <c r="C227" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D225" s="20" t="inlineStr">
+      <c r="D227" s="20" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E225" s="20" t="inlineStr">
+      <c r="E227" s="20" t="inlineStr">
         <is>
           <t>Práce a dodávky M (montáže)</t>
         </is>
       </c>
-      <c r="F225" s="19" t="n"/>
-      <c r="G225" s="19" t="n"/>
-      <c r="H225" s="19" t="n"/>
-      <c r="I225" s="19" t="n"/>
-      <c r="J225" s="19" t="n"/>
-      <c r="K225" s="19" t="n"/>
-      <c r="L225" s="19" t="n"/>
-    </row>
-    <row r="226">
-      <c r="B226" s="21" t="n"/>
-      <c r="C226" s="22" t="inlineStr">
+      <c r="F227" s="19" t="n"/>
+      <c r="G227" s="19" t="n"/>
+      <c r="H227" s="19" t="n"/>
+      <c r="I227" s="19" t="n"/>
+      <c r="J227" s="19" t="n"/>
+      <c r="K227" s="19" t="n"/>
+      <c r="L227" s="19" t="n"/>
+    </row>
+    <row r="228">
+      <c r="B228" s="21" t="n"/>
+      <c r="C228" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D226" s="22" t="inlineStr">
+      <c r="D228" s="22" t="inlineStr">
         <is>
           <t>M-21</t>
         </is>
       </c>
-      <c r="E226" s="22" t="inlineStr">
+      <c r="E228" s="22" t="inlineStr">
         <is>
           <t>M-21 ELI silnoproud</t>
         </is>
       </c>
-      <c r="F226" s="21" t="n"/>
-      <c r="G226" s="21" t="n"/>
-      <c r="H226" s="21" t="n"/>
-      <c r="I226" s="21" t="n"/>
-      <c r="J226" s="21" t="n"/>
-      <c r="K226" s="21" t="n"/>
-      <c r="L226" s="21" t="n"/>
-    </row>
-    <row r="227">
-      <c r="B227" s="23" t="n">
-        <v>84</v>
-      </c>
-      <c r="C227" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D227" s="24" t="inlineStr">
-        <is>
-          <t>210010011</t>
-        </is>
-      </c>
-      <c r="E227" s="24" t="inlineStr">
-        <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
-        </is>
-      </c>
-      <c r="F227" s="23" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G227" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H227" s="26" t="n"/>
-      <c r="I227" s="26">
-        <f>IF(H227="",0,G227*H227)</f>
-        <v/>
-      </c>
-      <c r="J227" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K227" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L227" s="5" t="inlineStr">
-        <is>
-          <t>M-21 ELI silnoproud</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="B228" s="17" t="n"/>
-      <c r="C228" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D228" s="17" t="n"/>
-      <c r="E228" s="29" t="inlineStr">
-        <is>
-          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
-        </is>
-      </c>
-      <c r="F228" s="17" t="n"/>
-      <c r="G228" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H228" s="17" t="n"/>
-      <c r="I228" s="17" t="n"/>
-      <c r="J228" s="17" t="n"/>
-      <c r="K228" s="17" t="n"/>
-      <c r="L228" s="17" t="n"/>
+      <c r="F228" s="21" t="n"/>
+      <c r="G228" s="21" t="n"/>
+      <c r="H228" s="21" t="n"/>
+      <c r="I228" s="21" t="n"/>
+      <c r="J228" s="21" t="n"/>
+      <c r="K228" s="21" t="n"/>
+      <c r="L228" s="21" t="n"/>
     </row>
     <row r="229">
       <c r="B229" s="23" t="n">
@@ -7683,21 +7683,21 @@
       </c>
       <c r="D229" s="24" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E229" s="24" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F229" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G229" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H229" s="26" t="n"/>
       <c r="I229" s="26">
@@ -7730,12 +7730,12 @@
       <c r="D230" s="17" t="n"/>
       <c r="E230" s="29" t="inlineStr">
         <is>
-          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
+          <t>TZ ARS — stávající ELI plně bourána; B m.10.e — 0.1 t kovů celkem</t>
         </is>
       </c>
       <c r="F230" s="17" t="n"/>
       <c r="G230" s="30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H230" s="17" t="n"/>
       <c r="I230" s="17" t="n"/>
@@ -7754,21 +7754,21 @@
       </c>
       <c r="D231" s="24" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E231" s="24" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F231" s="23" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G231" s="25" t="n">
-        <v>700</v>
+        <v>4</v>
       </c>
       <c r="H231" s="26" t="n"/>
       <c r="I231" s="26">
@@ -7801,12 +7801,12 @@
       <c r="D232" s="17" t="n"/>
       <c r="E232" s="29" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
+          <t>1 hlavní + 3 podružné = 4 rozvaděče</t>
         </is>
       </c>
       <c r="F232" s="17" t="n"/>
       <c r="G232" s="30" t="n">
-        <v>700</v>
+        <v>4</v>
       </c>
       <c r="H232" s="17" t="n"/>
       <c r="I232" s="17" t="n"/>
@@ -7825,21 +7825,21 @@
       </c>
       <c r="D233" s="24" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E233" s="24" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F233" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G233" s="25" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="H233" s="26" t="n"/>
       <c r="I233" s="26">
@@ -7872,12 +7872,12 @@
       <c r="D234" s="17" t="n"/>
       <c r="E234" s="29" t="inlineStr">
         <is>
-          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
+          <t>RD 219 m² × ~3.2 bm/m² standard ELI = 700 bm; vyjasnění #7 working assumption</t>
         </is>
       </c>
       <c r="F234" s="17" t="n"/>
       <c r="G234" s="30" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="H234" s="17" t="n"/>
       <c r="I234" s="17" t="n"/>
@@ -7896,12 +7896,12 @@
       </c>
       <c r="D235" s="24" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E235" s="24" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F235" s="23" t="inlineStr">
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="G235" s="25" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H235" s="26" t="n"/>
       <c r="I235" s="26">
@@ -7943,12 +7943,12 @@
       <c r="D236" s="17" t="n"/>
       <c r="E236" s="29" t="inlineStr">
         <is>
-          <t>standard RD 220 m² = ~35 ks svítidel</t>
+          <t>RD 219 m² × ~0.3 ks/m² standard 3-byt. dispozice = 70 ks</t>
         </is>
       </c>
       <c r="F236" s="17" t="n"/>
       <c r="G236" s="30" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H236" s="17" t="n"/>
       <c r="I236" s="17" t="n"/>
@@ -7967,21 +7967,21 @@
       </c>
       <c r="D237" s="24" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E237" s="24" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F237" s="23" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G237" s="25" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H237" s="26" t="n"/>
       <c r="I237" s="26">
@@ -8014,12 +8014,12 @@
       <c r="D238" s="17" t="n"/>
       <c r="E238" s="29" t="inlineStr">
         <is>
-          <t>TZ ARS — 'příprava na osazení FVE'</t>
+          <t>standard RD 220 m² = ~35 ks svítidel</t>
         </is>
       </c>
       <c r="F238" s="17" t="n"/>
       <c r="G238" s="30" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H238" s="17" t="n"/>
       <c r="I238" s="17" t="n"/>
@@ -8038,12 +8038,12 @@
       </c>
       <c r="D239" s="24" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E239" s="24" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F239" s="23" t="inlineStr">
@@ -8085,7 +8085,7 @@
       <c r="D240" s="17" t="n"/>
       <c r="E240" s="29" t="inlineStr">
         <is>
-          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+          <t>TZ ARS — 'příprava na osazení FVE'</t>
         </is>
       </c>
       <c r="F240" s="17" t="n"/>
@@ -8099,125 +8099,125 @@
       <c r="L240" s="17" t="n"/>
     </row>
     <row r="241">
-      <c r="B241" s="19" t="n"/>
-      <c r="C241" s="20" t="inlineStr">
+      <c r="B241" s="23" t="n">
+        <v>91</v>
+      </c>
+      <c r="C241" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D241" s="24" t="inlineStr">
+        <is>
+          <t>996019011</t>
+        </is>
+      </c>
+      <c r="E241" s="24" t="inlineStr">
+        <is>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+        </is>
+      </c>
+      <c r="F241" s="23" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G241" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H241" s="26" t="n"/>
+      <c r="I241" s="26">
+        <f>IF(H241="",0,G241*H241)</f>
+        <v/>
+      </c>
+      <c r="J241" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K241" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L241" s="5" t="inlineStr">
+        <is>
+          <t>M-21 ELI silnoproud</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" s="17" t="n"/>
+      <c r="C242" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D242" s="17" t="n"/>
+      <c r="E242" s="29" t="inlineStr">
+        <is>
+          <t>ČSN 33 2000-6 — povinná revize před kolaudací</t>
+        </is>
+      </c>
+      <c r="F242" s="17" t="n"/>
+      <c r="G242" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" s="17" t="n"/>
+      <c r="I242" s="17" t="n"/>
+      <c r="J242" s="17" t="n"/>
+      <c r="K242" s="17" t="n"/>
+      <c r="L242" s="17" t="n"/>
+    </row>
+    <row r="243">
+      <c r="B243" s="19" t="n"/>
+      <c r="C243" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D241" s="20" t="inlineStr">
+      <c r="D243" s="20" t="inlineStr">
         <is>
           <t>PSV</t>
         </is>
       </c>
-      <c r="E241" s="20" t="inlineStr">
+      <c r="E243" s="20" t="inlineStr">
         <is>
           <t>Práce a dodávky PSV</t>
         </is>
       </c>
-      <c r="F241" s="19" t="n"/>
-      <c r="G241" s="19" t="n"/>
-      <c r="H241" s="19" t="n"/>
-      <c r="I241" s="19" t="n"/>
-      <c r="J241" s="19" t="n"/>
-      <c r="K241" s="19" t="n"/>
-      <c r="L241" s="19" t="n"/>
-    </row>
-    <row r="242">
-      <c r="B242" s="21" t="n"/>
-      <c r="C242" s="22" t="inlineStr">
+      <c r="F243" s="19" t="n"/>
+      <c r="G243" s="19" t="n"/>
+      <c r="H243" s="19" t="n"/>
+      <c r="I243" s="19" t="n"/>
+      <c r="J243" s="19" t="n"/>
+      <c r="K243" s="19" t="n"/>
+      <c r="L243" s="19" t="n"/>
+    </row>
+    <row r="244">
+      <c r="B244" s="21" t="n"/>
+      <c r="C244" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D242" s="22" t="inlineStr">
+      <c r="D244" s="22" t="inlineStr">
         <is>
           <t>PSV-71</t>
         </is>
       </c>
-      <c r="E242" s="22" t="inlineStr">
+      <c r="E244" s="22" t="inlineStr">
         <is>
           <t>PSV-71 Izolace HI</t>
         </is>
       </c>
-      <c r="F242" s="21" t="n"/>
-      <c r="G242" s="21" t="n"/>
-      <c r="H242" s="21" t="n"/>
-      <c r="I242" s="21" t="n"/>
-      <c r="J242" s="21" t="n"/>
-      <c r="K242" s="21" t="n"/>
-      <c r="L242" s="21" t="n"/>
-    </row>
-    <row r="243">
-      <c r="B243" s="23" t="n">
-        <v>91</v>
-      </c>
-      <c r="C243" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D243" s="24" t="inlineStr">
-        <is>
-          <t>712311101</t>
-        </is>
-      </c>
-      <c r="E243" s="24" t="inlineStr">
-        <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
-        </is>
-      </c>
-      <c r="F243" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G243" s="25" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="H243" s="26" t="n"/>
-      <c r="I243" s="26">
-        <f>IF(H243="",0,G243*H243)</f>
-        <v/>
-      </c>
-      <c r="J243" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K243" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://stavimbydlim.cz/postup-hydroizolace-zakladove-desky-]</t>
-        </is>
-      </c>
-      <c r="L243" s="5" t="inlineStr">
-        <is>
-          <t>PSV-71 Izolace HI</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="B244" s="17" t="n"/>
-      <c r="C244" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D244" s="17" t="n"/>
-      <c r="E244" s="29" t="inlineStr">
-        <is>
-          <t>(zastavena × 0.7 rozsah 1.NP) × 1.10 přesah = 80.4</t>
-        </is>
-      </c>
-      <c r="F244" s="17" t="n"/>
-      <c r="G244" s="30" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="H244" s="17" t="n"/>
-      <c r="I244" s="17" t="n"/>
-      <c r="J244" s="17" t="n"/>
-      <c r="K244" s="17" t="n"/>
-      <c r="L244" s="17" t="n"/>
+      <c r="F244" s="21" t="n"/>
+      <c r="G244" s="21" t="n"/>
+      <c r="H244" s="21" t="n"/>
+      <c r="I244" s="21" t="n"/>
+      <c r="J244" s="21" t="n"/>
+      <c r="K244" s="21" t="n"/>
+      <c r="L244" s="21" t="n"/>
     </row>
     <row r="245">
       <c r="B245" s="23" t="n">
@@ -8230,21 +8230,21 @@
       </c>
       <c r="D245" s="24" t="inlineStr">
         <is>
-          <t>712381111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E245" s="24" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F245" s="23" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G245" s="25" t="n">
-        <v>12</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H245" s="26" t="n"/>
       <c r="I245" s="26">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="K245" s="31" t="inlineStr">
         <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://cze.sika.com/cs/produkty-pro-stavebnictvi/hydroizola]</t>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://stavimbydlim.cz/postup-hydroizolace-zakladove-desky-]</t>
         </is>
       </c>
       <c r="L245" s="5" t="inlineStr">
@@ -8277,12 +8277,12 @@
       <c r="D246" s="17" t="n"/>
       <c r="E246" s="29" t="inlineStr">
         <is>
-          <t>podsanační síť ~12 bm (3 řady × 4 m pod podlahou 1.NP)</t>
+          <t>(zastavena × 0.7 rozsah 1.NP) × 1.10 přesah = 80.4</t>
         </is>
       </c>
       <c r="F246" s="17" t="n"/>
       <c r="G246" s="30" t="n">
-        <v>12</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H246" s="17" t="n"/>
       <c r="I246" s="17" t="n"/>
@@ -8299,19 +8299,23 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D247" s="24" t="inlineStr"/>
+      <c r="D247" s="24" t="inlineStr">
+        <is>
+          <t>712381111</t>
+        </is>
+      </c>
       <c r="E247" s="24" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F247" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G247" s="25" t="n">
-        <v>40.5</v>
+        <v>12</v>
       </c>
       <c r="H247" s="26" t="n"/>
       <c r="I247" s="26">
@@ -8325,7 +8329,7 @@
       </c>
       <c r="K247" s="31" t="inlineStr">
         <is>
-          <t>⚠ family 711 OK — leaf KROS lookup [evidence: https://cze.sika.com/cs/produkty-pro-stavebnictvi/hydroizola]</t>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://cze.sika.com/cs/produkty-pro-stavebnictvi/hydroizola]</t>
         </is>
       </c>
       <c r="L247" s="5" t="inlineStr">
@@ -8344,12 +8348,12 @@
       <c r="D248" s="17" t="n"/>
       <c r="E248" s="29" t="inlineStr">
         <is>
-          <t>3 koupelny × (~5.5 m² podlaha + ~8 m² stěny v okolí sprchy) = 40.5</t>
+          <t>podsanační síť ~12 bm (3 řady × 4 m pod podlahou 1.NP)</t>
         </is>
       </c>
       <c r="F248" s="17" t="n"/>
       <c r="G248" s="30" t="n">
-        <v>40.5</v>
+        <v>12</v>
       </c>
       <c r="H248" s="17" t="n"/>
       <c r="I248" s="17" t="n"/>
@@ -8358,96 +8362,96 @@
       <c r="L248" s="17" t="n"/>
     </row>
     <row r="249">
-      <c r="B249" s="21" t="n"/>
-      <c r="C249" s="22" t="inlineStr">
+      <c r="B249" s="23" t="n">
+        <v>94</v>
+      </c>
+      <c r="C249" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D249" s="24" t="inlineStr"/>
+      <c r="E249" s="24" t="inlineStr">
+        <is>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+        </is>
+      </c>
+      <c r="F249" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G249" s="25" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H249" s="26" t="n"/>
+      <c r="I249" s="26">
+        <f>IF(H249="",0,G249*H249)</f>
+        <v/>
+      </c>
+      <c r="J249" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K249" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family 711 OK — leaf KROS lookup [evidence: https://cze.sika.com/cs/produkty-pro-stavebnictvi/hydroizola]</t>
+        </is>
+      </c>
+      <c r="L249" s="5" t="inlineStr">
+        <is>
+          <t>PSV-71 Izolace HI</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" s="17" t="n"/>
+      <c r="C250" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D250" s="17" t="n"/>
+      <c r="E250" s="29" t="inlineStr">
+        <is>
+          <t>3 koupelny × (~5.5 m² podlaha + ~8 m² stěny v okolí sprchy) = 40.5</t>
+        </is>
+      </c>
+      <c r="F250" s="17" t="n"/>
+      <c r="G250" s="30" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H250" s="17" t="n"/>
+      <c r="I250" s="17" t="n"/>
+      <c r="J250" s="17" t="n"/>
+      <c r="K250" s="17" t="n"/>
+      <c r="L250" s="17" t="n"/>
+    </row>
+    <row r="251">
+      <c r="B251" s="21" t="n"/>
+      <c r="C251" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D249" s="22" t="inlineStr">
+      <c r="D251" s="22" t="inlineStr">
         <is>
           <t>PSV-71</t>
         </is>
       </c>
-      <c r="E249" s="22" t="inlineStr">
+      <c r="E251" s="22" t="inlineStr">
         <is>
           <t>PSV-71 Izolace TI</t>
         </is>
       </c>
-      <c r="F249" s="21" t="n"/>
-      <c r="G249" s="21" t="n"/>
-      <c r="H249" s="21" t="n"/>
-      <c r="I249" s="21" t="n"/>
-      <c r="J249" s="21" t="n"/>
-      <c r="K249" s="21" t="n"/>
-      <c r="L249" s="21" t="n"/>
-    </row>
-    <row r="250">
-      <c r="B250" s="23" t="n">
-        <v>94</v>
-      </c>
-      <c r="C250" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D250" s="24" t="inlineStr"/>
-      <c r="E250" s="24" t="inlineStr">
-        <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
-        </is>
-      </c>
-      <c r="F250" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G250" s="25" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="H250" s="26" t="n"/>
-      <c r="I250" s="26">
-        <f>IF(H250="",0,G250*H250)</f>
-        <v/>
-      </c>
-      <c r="J250" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K250" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family 713121 OK — leaf KROS lookup [evidence: https://styrotrade.cz/cs/produkty/strechy/izolace-bezne-zati]</t>
-        </is>
-      </c>
-      <c r="L250" s="5" t="inlineStr">
-        <is>
-          <t>PSV-71 Izolace TI</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="B251" s="17" t="n"/>
-      <c r="C251" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D251" s="17" t="n"/>
-      <c r="E251" s="29" t="inlineStr">
-        <is>
-          <t>(rozsah 1.NP 73 m²) + (3.NP nadstavba 104 m²) = ~177 m²</t>
-        </is>
-      </c>
-      <c r="F251" s="17" t="n"/>
-      <c r="G251" s="30" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="H251" s="17" t="n"/>
-      <c r="I251" s="17" t="n"/>
-      <c r="J251" s="17" t="n"/>
-      <c r="K251" s="17" t="n"/>
-      <c r="L251" s="17" t="n"/>
+      <c r="F251" s="21" t="n"/>
+      <c r="G251" s="21" t="n"/>
+      <c r="H251" s="21" t="n"/>
+      <c r="I251" s="21" t="n"/>
+      <c r="J251" s="21" t="n"/>
+      <c r="K251" s="21" t="n"/>
+      <c r="L251" s="21" t="n"/>
     </row>
     <row r="252">
       <c r="B252" s="23" t="n">
@@ -8461,7 +8465,7 @@
       <c r="D252" s="24" t="inlineStr"/>
       <c r="E252" s="24" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F252" s="23" t="inlineStr">
@@ -8470,7 +8474,7 @@
         </is>
       </c>
       <c r="G252" s="25" t="n">
-        <v>104.4</v>
+        <v>177.5</v>
       </c>
       <c r="H252" s="26" t="n"/>
       <c r="I252" s="26">
@@ -8501,13 +8505,14 @@
         </is>
       </c>
       <c r="D253" s="17" t="n"/>
-      <c r="E253" s="29">
-        <f> zastavěna plocha 104.4 m² (strop 2.NP/3.NP)</f>
-        <v/>
+      <c r="E253" s="29" t="inlineStr">
+        <is>
+          <t>(rozsah 1.NP 73 m²) + (3.NP nadstavba 104 m²) = ~177 m²</t>
+        </is>
       </c>
       <c r="F253" s="17" t="n"/>
       <c r="G253" s="30" t="n">
-        <v>104.4</v>
+        <v>177.5</v>
       </c>
       <c r="H253" s="17" t="n"/>
       <c r="I253" s="17" t="n"/>
@@ -8516,100 +8521,95 @@
       <c r="L253" s="17" t="n"/>
     </row>
     <row r="254">
-      <c r="B254" s="21" t="n"/>
-      <c r="C254" s="22" t="inlineStr">
+      <c r="B254" s="23" t="n">
+        <v>96</v>
+      </c>
+      <c r="C254" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D254" s="24" t="inlineStr"/>
+      <c r="E254" s="24" t="inlineStr">
+        <is>
+          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+        </is>
+      </c>
+      <c r="F254" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G254" s="25" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="H254" s="26" t="n"/>
+      <c r="I254" s="26">
+        <f>IF(H254="",0,G254*H254)</f>
+        <v/>
+      </c>
+      <c r="J254" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K254" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family 713121 OK — leaf KROS lookup [evidence: https://styrotrade.cz/cs/produkty/strechy/izolace-bezne-zati]</t>
+        </is>
+      </c>
+      <c r="L254" s="5" t="inlineStr">
+        <is>
+          <t>PSV-71 Izolace TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" s="17" t="n"/>
+      <c r="C255" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D255" s="17" t="n"/>
+      <c r="E255" s="29">
+        <f> zastavěna plocha 104.4 m² (strop 2.NP/3.NP)</f>
+        <v/>
+      </c>
+      <c r="F255" s="17" t="n"/>
+      <c r="G255" s="30" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="H255" s="17" t="n"/>
+      <c r="I255" s="17" t="n"/>
+      <c r="J255" s="17" t="n"/>
+      <c r="K255" s="17" t="n"/>
+      <c r="L255" s="17" t="n"/>
+    </row>
+    <row r="256">
+      <c r="B256" s="21" t="n"/>
+      <c r="C256" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D254" s="22" t="inlineStr">
+      <c r="D256" s="22" t="inlineStr">
         <is>
           <t>PSV-72</t>
         </is>
       </c>
-      <c r="E254" s="22" t="inlineStr">
+      <c r="E256" s="22" t="inlineStr">
         <is>
           <t>PSV-72 ZTI</t>
         </is>
       </c>
-      <c r="F254" s="21" t="n"/>
-      <c r="G254" s="21" t="n"/>
-      <c r="H254" s="21" t="n"/>
-      <c r="I254" s="21" t="n"/>
-      <c r="J254" s="21" t="n"/>
-      <c r="K254" s="21" t="n"/>
-      <c r="L254" s="21" t="n"/>
-    </row>
-    <row r="255">
-      <c r="B255" s="23" t="n">
-        <v>96</v>
-      </c>
-      <c r="C255" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D255" s="24" t="inlineStr">
-        <is>
-          <t>722290515</t>
-        </is>
-      </c>
-      <c r="E255" s="24" t="inlineStr">
-        <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
-        </is>
-      </c>
-      <c r="F255" s="23" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G255" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H255" s="26" t="n"/>
-      <c r="I255" s="26">
-        <f>IF(H255="",0,G255*H255)</f>
-        <v/>
-      </c>
-      <c r="J255" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K255" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.sanitino.cz/vodovodni-baterie]</t>
-        </is>
-      </c>
-      <c r="L255" s="5" t="inlineStr">
-        <is>
-          <t>PSV-72 ZTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="B256" s="17" t="n"/>
-      <c r="C256" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D256" s="17" t="n"/>
-      <c r="E256" s="29" t="inlineStr">
-        <is>
-          <t>TZ ARS dům §4 — stávající přípojka zachována bez změny</t>
-        </is>
-      </c>
-      <c r="F256" s="17" t="n"/>
-      <c r="G256" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H256" s="17" t="n"/>
-      <c r="I256" s="17" t="n"/>
-      <c r="J256" s="17" t="n"/>
-      <c r="K256" s="17" t="n"/>
-      <c r="L256" s="17" t="n"/>
+      <c r="F256" s="21" t="n"/>
+      <c r="G256" s="21" t="n"/>
+      <c r="H256" s="21" t="n"/>
+      <c r="I256" s="21" t="n"/>
+      <c r="J256" s="21" t="n"/>
+      <c r="K256" s="21" t="n"/>
+      <c r="L256" s="21" t="n"/>
     </row>
     <row r="257">
       <c r="B257" s="23" t="n">
@@ -8622,21 +8622,21 @@
       </c>
       <c r="D257" s="24" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E257" s="24" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F257" s="23" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G257" s="25" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="H257" s="26" t="n"/>
       <c r="I257" s="26">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="K257" s="31" t="inlineStr">
         <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.ceskestavby.cz/jak-se-stavi-dum/sprchy-vany-vana]</t>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.sanitino.cz/vodovodni-baterie]</t>
         </is>
       </c>
       <c r="L257" s="5" t="inlineStr">
@@ -8669,12 +8669,12 @@
       <c r="D258" s="17" t="n"/>
       <c r="E258" s="29" t="inlineStr">
         <is>
-          <t>3 patra × ~25 bm rozvodů (koupelny + kuchyně + bojler 3.NP) = 75 (round 80)</t>
+          <t>TZ ARS dům §4 — stávající přípojka zachována bez změny</t>
         </is>
       </c>
       <c r="F258" s="17" t="n"/>
       <c r="G258" s="30" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="H258" s="17" t="n"/>
       <c r="I258" s="17" t="n"/>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="D259" s="24" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E259" s="24" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F259" s="23" t="inlineStr">
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="G259" s="25" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H259" s="26" t="n"/>
       <c r="I259" s="26">
@@ -8719,9 +8719,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K259" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K259" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.ceskestavby.cz/jak-se-stavi-dum/sprchy-vany-vana]</t>
         </is>
       </c>
       <c r="L259" s="5" t="inlineStr">
@@ -8740,12 +8740,12 @@
       <c r="D260" s="17" t="n"/>
       <c r="E260" s="29" t="inlineStr">
         <is>
-          <t>3 patra × ~20 bm odpadní + svislé propojení = 60</t>
+          <t>3 patra × ~25 bm rozvodů (koupelny + kuchyně + bojler 3.NP) = 75 (round 80)</t>
         </is>
       </c>
       <c r="F260" s="17" t="n"/>
       <c r="G260" s="30" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H260" s="17" t="n"/>
       <c r="I260" s="17" t="n"/>
@@ -8764,21 +8764,21 @@
       </c>
       <c r="D261" s="24" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E261" s="24" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F261" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G261" s="25" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="H261" s="26" t="n"/>
       <c r="I261" s="26">
@@ -8811,12 +8811,12 @@
       <c r="D262" s="17" t="n"/>
       <c r="E262" s="29" t="inlineStr">
         <is>
-          <t>DXF rooms 1.06 + 3.05 kuchyně MTEXT (každá obytná místnost + kuchyně) = 2 dřezy</t>
+          <t>3 patra × ~20 bm odpadní + svislé propojení = 60</t>
         </is>
       </c>
       <c r="F262" s="17" t="n"/>
       <c r="G262" s="30" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="H262" s="17" t="n"/>
       <c r="I262" s="17" t="n"/>
@@ -8835,12 +8835,12 @@
       </c>
       <c r="D263" s="24" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E263" s="24" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F263" s="23" t="inlineStr">
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="G263" s="25" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H263" s="26" t="n"/>
       <c r="I263" s="26">
@@ -8882,12 +8882,12 @@
       <c r="D264" s="17" t="n"/>
       <c r="E264" s="29" t="inlineStr">
         <is>
-          <t>12 sanit. zařízení × 1 baterie + 3 drobnosti (rohové ventily, sifony) = 15</t>
+          <t>DXF rooms 1.06 + 3.05 kuchyně MTEXT (každá obytná místnost + kuchyně) = 2 dřezy</t>
         </is>
       </c>
       <c r="F264" s="17" t="n"/>
       <c r="G264" s="30" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H264" s="17" t="n"/>
       <c r="I264" s="17" t="n"/>
@@ -8906,12 +8906,12 @@
       </c>
       <c r="D265" s="24" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E265" s="24" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F265" s="23" t="inlineStr">
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="G265" s="25" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H265" s="26" t="n"/>
       <c r="I265" s="26">
@@ -8953,12 +8953,12 @@
       <c r="D266" s="17" t="n"/>
       <c r="E266" s="29" t="inlineStr">
         <is>
-          <t>TZ ARS — 'akumulační zásobník TUV v suterénu napojený na topný systém'</t>
+          <t>12 sanit. zařízení × 1 baterie + 3 drobnosti (rohové ventily, sifony) = 15</t>
         </is>
       </c>
       <c r="F266" s="17" t="n"/>
       <c r="G266" s="30" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H266" s="17" t="n"/>
       <c r="I266" s="17" t="n"/>
@@ -8977,12 +8977,12 @@
       </c>
       <c r="D267" s="24" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E267" s="24" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F267" s="23" t="inlineStr">
@@ -9024,7 +9024,7 @@
       <c r="D268" s="17" t="n"/>
       <c r="E268" s="29" t="inlineStr">
         <is>
-          <t>TZ ARS — 'elektrický bojler v koupelně 3.NP'</t>
+          <t>TZ ARS — 'akumulační zásobník TUV v suterénu napojený na topný systém'</t>
         </is>
       </c>
       <c r="F268" s="17" t="n"/>
@@ -9048,12 +9048,12 @@
       </c>
       <c r="D269" s="24" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E269" s="24" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F269" s="23" t="inlineStr">
@@ -9095,7 +9095,7 @@
       <c r="D270" s="17" t="n"/>
       <c r="E270" s="29" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>TZ ARS — 'elektrický bojler v koupelně 3.NP'</t>
         </is>
       </c>
       <c r="F270" s="17" t="n"/>
@@ -9119,12 +9119,12 @@
       </c>
       <c r="D271" s="24" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E271" s="24" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F271" s="23" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="D273" s="24" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E273" s="24" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F273" s="23" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="D275" s="24" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E275" s="24" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F275" s="23" t="inlineStr">
@@ -9308,7 +9308,7 @@
       <c r="D276" s="17" t="n"/>
       <c r="E276" s="29" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>set split from 260219_dum.PSV72.004 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="F276" s="17" t="n"/>
@@ -9332,12 +9332,12 @@
       </c>
       <c r="D277" s="24" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E277" s="24" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F277" s="23" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="D279" s="24" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E279" s="24" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F279" s="23" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="E281" s="24" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F281" s="23" t="inlineStr">
@@ -9521,7 +9521,7 @@
       <c r="D282" s="17" t="n"/>
       <c r="E282" s="29" t="inlineStr">
         <is>
-          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
+          <t>set split from 260219_dum.PSV72.005 per audit v2 GAP_005 — 1 fixture per item</t>
         </is>
       </c>
       <c r="F282" s="17" t="n"/>
@@ -9545,12 +9545,12 @@
       </c>
       <c r="D283" s="24" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E283" s="24" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F283" s="23" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="D285" s="24" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E285" s="24" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F285" s="23" t="inlineStr">
@@ -9677,100 +9677,100 @@
       <c r="L286" s="17" t="n"/>
     </row>
     <row r="287">
-      <c r="B287" s="21" t="n"/>
-      <c r="C287" s="22" t="inlineStr">
+      <c r="B287" s="23" t="n">
+        <v>112</v>
+      </c>
+      <c r="C287" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D287" s="24" t="inlineStr">
+        <is>
+          <t>725221201</t>
+        </is>
+      </c>
+      <c r="E287" s="24" t="inlineStr">
+        <is>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+        </is>
+      </c>
+      <c r="F287" s="23" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G287" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" s="26" t="n"/>
+      <c r="I287" s="26">
+        <f>IF(H287="",0,G287*H287)</f>
+        <v/>
+      </c>
+      <c r="J287" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K287" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L287" s="5" t="inlineStr">
+        <is>
+          <t>PSV-72 ZTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" s="17" t="n"/>
+      <c r="C288" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D288" s="17" t="n"/>
+      <c r="E288" s="29" t="inlineStr">
+        <is>
+          <t>set split from 260219_dum.PSV72.006 per audit v2 GAP_005 — 1 fixture per item</t>
+        </is>
+      </c>
+      <c r="F288" s="17" t="n"/>
+      <c r="G288" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" s="17" t="n"/>
+      <c r="I288" s="17" t="n"/>
+      <c r="J288" s="17" t="n"/>
+      <c r="K288" s="17" t="n"/>
+      <c r="L288" s="17" t="n"/>
+    </row>
+    <row r="289">
+      <c r="B289" s="21" t="n"/>
+      <c r="C289" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D287" s="22" t="inlineStr">
+      <c r="D289" s="22" t="inlineStr">
         <is>
           <t>PSV-73</t>
         </is>
       </c>
-      <c r="E287" s="22" t="inlineStr">
+      <c r="E289" s="22" t="inlineStr">
         <is>
           <t>PSV-73 Vytápění</t>
         </is>
       </c>
-      <c r="F287" s="21" t="n"/>
-      <c r="G287" s="21" t="n"/>
-      <c r="H287" s="21" t="n"/>
-      <c r="I287" s="21" t="n"/>
-      <c r="J287" s="21" t="n"/>
-      <c r="K287" s="21" t="n"/>
-      <c r="L287" s="21" t="n"/>
-    </row>
-    <row r="288">
-      <c r="B288" s="23" t="n">
-        <v>112</v>
-      </c>
-      <c r="C288" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D288" s="24" t="inlineStr">
-        <is>
-          <t>733241011</t>
-        </is>
-      </c>
-      <c r="E288" s="24" t="inlineStr">
-        <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
-        </is>
-      </c>
-      <c r="F288" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G288" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H288" s="26" t="n"/>
-      <c r="I288" s="26">
-        <f>IF(H288="",0,G288*H288)</f>
-        <v/>
-      </c>
-      <c r="J288" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K288" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L288" s="5" t="inlineStr">
-        <is>
-          <t>PSV-73 Vytápění</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="B289" s="17" t="n"/>
-      <c r="C289" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D289" s="17" t="n"/>
-      <c r="E289" s="29" t="inlineStr">
-        <is>
-          <t>TZ ARS dům §4 — sporáková kamna v 1.PP/1.NP zóně</t>
-        </is>
-      </c>
-      <c r="F289" s="17" t="n"/>
-      <c r="G289" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H289" s="17" t="n"/>
-      <c r="I289" s="17" t="n"/>
-      <c r="J289" s="17" t="n"/>
-      <c r="K289" s="17" t="n"/>
-      <c r="L289" s="17" t="n"/>
+      <c r="F289" s="21" t="n"/>
+      <c r="G289" s="21" t="n"/>
+      <c r="H289" s="21" t="n"/>
+      <c r="I289" s="21" t="n"/>
+      <c r="J289" s="21" t="n"/>
+      <c r="K289" s="21" t="n"/>
+      <c r="L289" s="21" t="n"/>
     </row>
     <row r="290">
       <c r="B290" s="23" t="n">
@@ -9783,17 +9783,17 @@
       </c>
       <c r="D290" s="24" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E290" s="24" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F290" s="23" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G290" s="25" t="n">
@@ -9828,9 +9828,10 @@
         </is>
       </c>
       <c r="D291" s="17" t="n"/>
-      <c r="E291" s="29">
-        <f> ks kamen</f>
-        <v/>
+      <c r="E291" s="29" t="inlineStr">
+        <is>
+          <t>TZ ARS dům §4 — sporáková kamna v 1.PP/1.NP zóně</t>
+        </is>
       </c>
       <c r="F291" s="17" t="n"/>
       <c r="G291" s="30" t="n">
@@ -9853,17 +9854,17 @@
       </c>
       <c r="D292" s="24" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E292" s="24" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F292" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G292" s="25" t="n">
@@ -9898,10 +9899,9 @@
         </is>
       </c>
       <c r="D293" s="17" t="n"/>
-      <c r="E293" s="29" t="inlineStr">
-        <is>
-          <t>TZ ARS — elektrokotel pro 3.NP samostatný byt</t>
-        </is>
+      <c r="E293" s="29">
+        <f> ks kamen</f>
+        <v/>
       </c>
       <c r="F293" s="17" t="n"/>
       <c r="G293" s="30" t="n">
@@ -9924,12 +9924,12 @@
       </c>
       <c r="D294" s="24" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E294" s="24" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F294" s="23" t="inlineStr">
@@ -9971,7 +9971,7 @@
       <c r="D295" s="17" t="n"/>
       <c r="E295" s="29" t="inlineStr">
         <is>
-          <t>TZ ARS — 'krbem na tuhá paliva' v 3.NP</t>
+          <t>TZ ARS — elektrokotel pro 3.NP samostatný byt</t>
         </is>
       </c>
       <c r="F295" s="17" t="n"/>
@@ -9995,12 +9995,12 @@
       </c>
       <c r="D296" s="24" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E296" s="24" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F296" s="23" t="inlineStr">
@@ -10042,7 +10042,7 @@
       <c r="D297" s="17" t="n"/>
       <c r="E297" s="29" t="inlineStr">
         <is>
-          <t>TZ ARS — multisplit TČ vzduch-vzduch</t>
+          <t>TZ ARS — 'krbem na tuhá paliva' v 3.NP</t>
         </is>
       </c>
       <c r="F297" s="17" t="n"/>
@@ -10066,12 +10066,12 @@
       </c>
       <c r="D298" s="24" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E298" s="24" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F298" s="23" t="inlineStr">
@@ -10080,7 +10080,7 @@
         </is>
       </c>
       <c r="G298" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H298" s="26" t="n"/>
       <c r="I298" s="26">
@@ -10113,12 +10113,12 @@
       <c r="D299" s="17" t="n"/>
       <c r="E299" s="29" t="inlineStr">
         <is>
-          <t>TZ ARS — 'vnitřní jednotky v obytných místnostech', odhad 5 ks (3 patra × ~1.7 j/patro)</t>
+          <t>TZ ARS — multisplit TČ vzduch-vzduch</t>
         </is>
       </c>
       <c r="F299" s="17" t="n"/>
       <c r="G299" s="30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H299" s="17" t="n"/>
       <c r="I299" s="17" t="n"/>
@@ -10137,21 +10137,21 @@
       </c>
       <c r="D300" s="24" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E300" s="24" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F300" s="23" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G300" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H300" s="26" t="n"/>
       <c r="I300" s="26">
@@ -10184,12 +10184,12 @@
       <c r="D301" s="17" t="n"/>
       <c r="E301" s="29" t="inlineStr">
         <is>
-          <t>TZ ARS — komín revize a úpravy stávajícího</t>
+          <t>TZ ARS — 'vnitřní jednotky v obytných místnostech', odhad 5 ks (3 patra × ~1.7 j/patro)</t>
         </is>
       </c>
       <c r="F301" s="17" t="n"/>
       <c r="G301" s="30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H301" s="17" t="n"/>
       <c r="I301" s="17" t="n"/>
@@ -10208,21 +10208,21 @@
       </c>
       <c r="D302" s="24" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E302" s="24" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F302" s="23" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G302" s="25" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H302" s="26" t="n"/>
       <c r="I302" s="26">
@@ -10255,12 +10255,12 @@
       <c r="D303" s="17" t="n"/>
       <c r="E303" s="29" t="inlineStr">
         <is>
-          <t>TZ ARS — vyjasnění #6 working assumption, multisplit + doplň. radiátory</t>
+          <t>TZ ARS — komín revize a úpravy stávajícího</t>
         </is>
       </c>
       <c r="F303" s="17" t="n"/>
       <c r="G303" s="30" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H303" s="17" t="n"/>
       <c r="I303" s="17" t="n"/>
@@ -10269,100 +10269,100 @@
       <c r="L303" s="17" t="n"/>
     </row>
     <row r="304">
-      <c r="B304" s="21" t="n"/>
-      <c r="C304" s="22" t="inlineStr">
+      <c r="B304" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="C304" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D304" s="24" t="inlineStr">
+        <is>
+          <t>733111021</t>
+        </is>
+      </c>
+      <c r="E304" s="24" t="inlineStr">
+        <is>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+        </is>
+      </c>
+      <c r="F304" s="23" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G304" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H304" s="26" t="n"/>
+      <c r="I304" s="26">
+        <f>IF(H304="",0,G304*H304)</f>
+        <v/>
+      </c>
+      <c r="J304" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K304" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L304" s="5" t="inlineStr">
+        <is>
+          <t>PSV-73 Vytápění</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" s="17" t="n"/>
+      <c r="C305" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D305" s="17" t="n"/>
+      <c r="E305" s="29" t="inlineStr">
+        <is>
+          <t>TZ ARS — vyjasnění #6 working assumption, multisplit + doplň. radiátory</t>
+        </is>
+      </c>
+      <c r="F305" s="17" t="n"/>
+      <c r="G305" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="H305" s="17" t="n"/>
+      <c r="I305" s="17" t="n"/>
+      <c r="J305" s="17" t="n"/>
+      <c r="K305" s="17" t="n"/>
+      <c r="L305" s="17" t="n"/>
+    </row>
+    <row r="306">
+      <c r="B306" s="21" t="n"/>
+      <c r="C306" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D304" s="22" t="inlineStr">
+      <c r="D306" s="22" t="inlineStr">
         <is>
           <t>PSV-76</t>
         </is>
       </c>
-      <c r="E304" s="22" t="inlineStr">
+      <c r="E306" s="22" t="inlineStr">
         <is>
           <t>PSV-76 Klempíř</t>
         </is>
       </c>
-      <c r="F304" s="21" t="n"/>
-      <c r="G304" s="21" t="n"/>
-      <c r="H304" s="21" t="n"/>
-      <c r="I304" s="21" t="n"/>
-      <c r="J304" s="21" t="n"/>
-      <c r="K304" s="21" t="n"/>
-      <c r="L304" s="21" t="n"/>
-    </row>
-    <row r="305">
-      <c r="B305" s="23" t="n">
-        <v>120</v>
-      </c>
-      <c r="C305" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D305" s="24" t="inlineStr">
-        <is>
-          <t>764312235</t>
-        </is>
-      </c>
-      <c r="E305" s="24" t="inlineStr">
-        <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
-        </is>
-      </c>
-      <c r="F305" s="23" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G305" s="25" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="H305" s="26" t="n"/>
-      <c r="I305" s="26">
-        <f>IF(H305="",0,G305*H305)</f>
-        <v/>
-      </c>
-      <c r="J305" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K305" s="31" t="inlineStr">
-        <is>
-          <t>⚠ chapter OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu201/800-764-Konstrukce-klem]</t>
-        </is>
-      </c>
-      <c r="L305" s="5" t="inlineStr">
-        <is>
-          <t>PSV-76 Klempíř</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="B306" s="17" t="n"/>
-      <c r="C306" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D306" s="17" t="n"/>
-      <c r="E306" s="29" t="inlineStr">
-        <is>
-          <t>DXF klempířina total 173.8 m × 0.40 (oplechování+úžlabí+hřeben+lemy) = 69.5 bm</t>
-        </is>
-      </c>
-      <c r="F306" s="17" t="n"/>
-      <c r="G306" s="30" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="H306" s="17" t="n"/>
-      <c r="I306" s="17" t="n"/>
-      <c r="J306" s="17" t="n"/>
-      <c r="K306" s="17" t="n"/>
-      <c r="L306" s="17" t="n"/>
+      <c r="F306" s="21" t="n"/>
+      <c r="G306" s="21" t="n"/>
+      <c r="H306" s="21" t="n"/>
+      <c r="I306" s="21" t="n"/>
+      <c r="J306" s="21" t="n"/>
+      <c r="K306" s="21" t="n"/>
+      <c r="L306" s="21" t="n"/>
     </row>
     <row r="307">
       <c r="B307" s="23" t="n">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="D307" s="24" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E307" s="24" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F307" s="23" t="inlineStr">
@@ -10389,7 +10389,7 @@
         </is>
       </c>
       <c r="G307" s="25" t="n">
-        <v>20.8</v>
+        <v>69.5</v>
       </c>
       <c r="H307" s="26" t="n"/>
       <c r="I307" s="26">
@@ -10420,13 +10420,14 @@
         </is>
       </c>
       <c r="D308" s="17" t="n"/>
-      <c r="E308" s="29">
-        <f> 16 oken (DXF INSERT) × průměrná šíře 1.3 m parapetu</f>
-        <v/>
+      <c r="E308" s="29" t="inlineStr">
+        <is>
+          <t>DXF klempířina total 173.8 m × 0.40 (oplechování+úžlabí+hřeben+lemy) = 69.5 bm</t>
+        </is>
       </c>
       <c r="F308" s="17" t="n"/>
       <c r="G308" s="30" t="n">
-        <v>20.8</v>
+        <v>69.5</v>
       </c>
       <c r="H308" s="17" t="n"/>
       <c r="I308" s="17" t="n"/>
@@ -10445,12 +10446,12 @@
       </c>
       <c r="D309" s="24" t="inlineStr">
         <is>
-          <t>764454802</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E309" s="24" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F309" s="23" t="inlineStr">
@@ -10459,7 +10460,7 @@
         </is>
       </c>
       <c r="G309" s="25" t="n">
-        <v>43.5</v>
+        <v>20.8</v>
       </c>
       <c r="H309" s="26" t="n"/>
       <c r="I309" s="26">
@@ -10490,14 +10491,13 @@
         </is>
       </c>
       <c r="D310" s="17" t="n"/>
-      <c r="E310" s="29" t="inlineStr">
-        <is>
-          <t>DXF klempířina total 173.8 m × 0.25 (svody+žlaby) = 43.5 bm</t>
-        </is>
+      <c r="E310" s="29">
+        <f> 16 oken (DXF INSERT) × průměrná šíře 1.3 m parapetu</f>
+        <v/>
       </c>
       <c r="F310" s="17" t="n"/>
       <c r="G310" s="30" t="n">
-        <v>43.5</v>
+        <v>20.8</v>
       </c>
       <c r="H310" s="17" t="n"/>
       <c r="I310" s="17" t="n"/>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="D311" s="24" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E311" s="24" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F311" s="23" t="inlineStr">
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="G311" s="25" t="n">
-        <v>26.1</v>
+        <v>43.5</v>
       </c>
       <c r="H311" s="26" t="n"/>
       <c r="I311" s="26">
@@ -10563,12 +10563,12 @@
       <c r="D312" s="17" t="n"/>
       <c r="E312" s="29" t="inlineStr">
         <is>
-          <t>DXF klempířina total 173.8 m × 0.15 (vikýře+atika+lemy) = 26.1 bm</t>
+          <t>DXF klempířina total 173.8 m × 0.25 (svody+žlaby) = 43.5 bm</t>
         </is>
       </c>
       <c r="F312" s="17" t="n"/>
       <c r="G312" s="30" t="n">
-        <v>26.1</v>
+        <v>43.5</v>
       </c>
       <c r="H312" s="17" t="n"/>
       <c r="I312" s="17" t="n"/>
@@ -10577,100 +10577,100 @@
       <c r="L312" s="17" t="n"/>
     </row>
     <row r="313">
-      <c r="B313" s="21" t="n"/>
-      <c r="C313" s="22" t="inlineStr">
+      <c r="B313" s="23" t="n">
+        <v>124</v>
+      </c>
+      <c r="C313" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D313" s="24" t="inlineStr">
+        <is>
+          <t>764315235</t>
+        </is>
+      </c>
+      <c r="E313" s="24" t="inlineStr">
+        <is>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+        </is>
+      </c>
+      <c r="F313" s="23" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G313" s="25" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H313" s="26" t="n"/>
+      <c r="I313" s="26">
+        <f>IF(H313="",0,G313*H313)</f>
+        <v/>
+      </c>
+      <c r="J313" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K313" s="31" t="inlineStr">
+        <is>
+          <t>⚠ chapter OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/podminky/cu201/800-764-Konstrukce-klem]</t>
+        </is>
+      </c>
+      <c r="L313" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76 Klempíř</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" s="17" t="n"/>
+      <c r="C314" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D314" s="17" t="n"/>
+      <c r="E314" s="29" t="inlineStr">
+        <is>
+          <t>DXF klempířina total 173.8 m × 0.15 (vikýře+atika+lemy) = 26.1 bm</t>
+        </is>
+      </c>
+      <c r="F314" s="17" t="n"/>
+      <c r="G314" s="30" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H314" s="17" t="n"/>
+      <c r="I314" s="17" t="n"/>
+      <c r="J314" s="17" t="n"/>
+      <c r="K314" s="17" t="n"/>
+      <c r="L314" s="17" t="n"/>
+    </row>
+    <row r="315">
+      <c r="B315" s="21" t="n"/>
+      <c r="C315" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D313" s="22" t="inlineStr">
+      <c r="D315" s="22" t="inlineStr">
         <is>
           <t>PSV-76</t>
         </is>
       </c>
-      <c r="E313" s="22" t="inlineStr">
+      <c r="E315" s="22" t="inlineStr">
         <is>
           <t>PSV-76 Truhlář</t>
         </is>
       </c>
-      <c r="F313" s="21" t="n"/>
-      <c r="G313" s="21" t="n"/>
-      <c r="H313" s="21" t="n"/>
-      <c r="I313" s="21" t="n"/>
-      <c r="J313" s="21" t="n"/>
-      <c r="K313" s="21" t="n"/>
-      <c r="L313" s="21" t="n"/>
-    </row>
-    <row r="314">
-      <c r="B314" s="23" t="n">
-        <v>124</v>
-      </c>
-      <c r="C314" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D314" s="24" t="inlineStr">
-        <is>
-          <t>766811111</t>
-        </is>
-      </c>
-      <c r="E314" s="24" t="inlineStr">
-        <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
-        </is>
-      </c>
-      <c r="F314" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G314" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="H314" s="26" t="n"/>
-      <c r="I314" s="26">
-        <f>IF(H314="",0,G314*H314)</f>
-        <v/>
-      </c>
-      <c r="J314" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K314" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L314" s="5" t="inlineStr">
-        <is>
-          <t>PSV-76 Truhlář</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="B315" s="17" t="n"/>
-      <c r="C315" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D315" s="17" t="n"/>
-      <c r="E315" s="29" t="inlineStr">
-        <is>
-          <t>2 schodiště × ~8 stupňů = 16</t>
-        </is>
-      </c>
-      <c r="F315" s="17" t="n"/>
-      <c r="G315" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="H315" s="17" t="n"/>
-      <c r="I315" s="17" t="n"/>
-      <c r="J315" s="17" t="n"/>
-      <c r="K315" s="17" t="n"/>
-      <c r="L315" s="17" t="n"/>
+      <c r="F315" s="21" t="n"/>
+      <c r="G315" s="21" t="n"/>
+      <c r="H315" s="21" t="n"/>
+      <c r="I315" s="21" t="n"/>
+      <c r="J315" s="21" t="n"/>
+      <c r="K315" s="21" t="n"/>
+      <c r="L315" s="21" t="n"/>
     </row>
     <row r="316">
       <c r="B316" s="23" t="n">
@@ -10681,19 +10681,23 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D316" s="24" t="inlineStr"/>
+      <c r="D316" s="24" t="inlineStr">
+        <is>
+          <t>766811111</t>
+        </is>
+      </c>
       <c r="E316" s="24" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F316" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G316" s="25" t="n">
-        <v>9.23</v>
+        <v>16</v>
       </c>
       <c r="H316" s="26" t="n"/>
       <c r="I316" s="26">
@@ -10705,9 +10709,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K316" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
+      <c r="K316" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L316" s="5" t="inlineStr">
@@ -10726,12 +10730,12 @@
       <c r="D317" s="17" t="n"/>
       <c r="E317" s="29" t="inlineStr">
         <is>
-          <t>Situace měření 2026-05-29 — dřevěná terasa (line-hatch zpevněné plochy) = 9.23 m². Dříve ODHAD 30 m². Terče + podkladní skladba viz HSV1.005 (split-by-trade).</t>
+          <t>2 schodiště × ~8 stupňů = 16</t>
         </is>
       </c>
       <c r="F317" s="17" t="n"/>
       <c r="G317" s="30" t="n">
-        <v>9.23</v>
+        <v>16</v>
       </c>
       <c r="H317" s="17" t="n"/>
       <c r="I317" s="17" t="n"/>
@@ -10740,100 +10744,96 @@
       <c r="L317" s="17" t="n"/>
     </row>
     <row r="318">
-      <c r="B318" s="21" t="n"/>
-      <c r="C318" s="22" t="inlineStr">
+      <c r="B318" s="23" t="n">
+        <v>126</v>
+      </c>
+      <c r="C318" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D318" s="24" t="inlineStr"/>
+      <c r="E318" s="24" t="inlineStr">
+        <is>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+        </is>
+      </c>
+      <c r="F318" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G318" s="25" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="H318" s="26" t="n"/>
+      <c r="I318" s="26">
+        <f>IF(H318="",0,G318*H318)</f>
+        <v/>
+      </c>
+      <c r="J318" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K318" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L318" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76 Truhlář</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" s="17" t="n"/>
+      <c r="C319" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D319" s="17" t="n"/>
+      <c r="E319" s="29" t="inlineStr">
+        <is>
+          <t>Situace měření 2026-05-29 — dřevěná terasa (line-hatch zpevněné plochy) = 9.23 m². Dříve ODHAD 30 m². Terče + podkladní skladba viz HSV1.005 (split-by-trade).</t>
+        </is>
+      </c>
+      <c r="F319" s="17" t="n"/>
+      <c r="G319" s="30" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="H319" s="17" t="n"/>
+      <c r="I319" s="17" t="n"/>
+      <c r="J319" s="17" t="n"/>
+      <c r="K319" s="17" t="n"/>
+      <c r="L319" s="17" t="n"/>
+    </row>
+    <row r="320">
+      <c r="B320" s="21" t="n"/>
+      <c r="C320" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D318" s="22" t="inlineStr">
+      <c r="D320" s="22" t="inlineStr">
         <is>
           <t>PSV-76</t>
         </is>
       </c>
-      <c r="E318" s="22" t="inlineStr">
+      <c r="E320" s="22" t="inlineStr">
         <is>
           <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
-      <c r="F318" s="21" t="n"/>
-      <c r="G318" s="21" t="n"/>
-      <c r="H318" s="21" t="n"/>
-      <c r="I318" s="21" t="n"/>
-      <c r="J318" s="21" t="n"/>
-      <c r="K318" s="21" t="n"/>
-      <c r="L318" s="21" t="n"/>
-    </row>
-    <row r="319">
-      <c r="B319" s="23" t="n">
-        <v>126</v>
-      </c>
-      <c r="C319" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D319" s="24" t="inlineStr">
-        <is>
-          <t>766621011</t>
-        </is>
-      </c>
-      <c r="E319" s="24" t="inlineStr">
-        <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
-        </is>
-      </c>
-      <c r="F319" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G319" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H319" s="26" t="n"/>
-      <c r="I319" s="26">
-        <f>IF(H319="",0,G319*H319)</f>
-        <v/>
-      </c>
-      <c r="J319" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K319" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.vekra.cz/radce/plastova-okna-s-trojsklem/]</t>
-        </is>
-      </c>
-      <c r="L319" s="5" t="inlineStr">
-        <is>
-          <t>PSV-76 Výplně otvorů</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="B320" s="17" t="n"/>
-      <c r="C320" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D320" s="17" t="n"/>
-      <c r="E320" s="29" t="inlineStr">
-        <is>
-          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
-        </is>
-      </c>
-      <c r="F320" s="17" t="n"/>
-      <c r="G320" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H320" s="17" t="n"/>
-      <c r="I320" s="17" t="n"/>
-      <c r="J320" s="17" t="n"/>
-      <c r="K320" s="17" t="n"/>
-      <c r="L320" s="17" t="n"/>
+      <c r="F320" s="21" t="n"/>
+      <c r="G320" s="21" t="n"/>
+      <c r="H320" s="21" t="n"/>
+      <c r="I320" s="21" t="n"/>
+      <c r="J320" s="21" t="n"/>
+      <c r="K320" s="21" t="n"/>
+      <c r="L320" s="21" t="n"/>
     </row>
     <row r="321">
       <c r="B321" s="23" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="E321" s="24" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F321" s="23" t="inlineStr">
@@ -10860,7 +10860,7 @@
         </is>
       </c>
       <c r="G321" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H321" s="26" t="n"/>
       <c r="I321" s="26">
@@ -10872,9 +10872,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K321" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K321" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.vekra.cz/radce/plastova-okna-s-trojsklem/]</t>
         </is>
       </c>
       <c r="L321" s="5" t="inlineStr">
@@ -10893,12 +10893,12 @@
       <c r="D322" s="17" t="n"/>
       <c r="E322" s="29" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
+          <t>DXF INSERT block name 'okno 1.NP' count = 2 ks × bbox 1185×1600 mm = 3.8 m² fasády</t>
         </is>
       </c>
       <c r="F322" s="17" t="n"/>
       <c r="G322" s="30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H322" s="17" t="n"/>
       <c r="I322" s="17" t="n"/>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="E323" s="24" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F323" s="23" t="inlineStr">
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="G323" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H323" s="26" t="n"/>
       <c r="I323" s="26">
@@ -10964,12 +10964,12 @@
       <c r="D324" s="17" t="n"/>
       <c r="E324" s="29" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
+          <t>DXF INSERT block name 'okno 1.NP vzadu' count = 3 ks × bbox 920×1600 mm = 4.41 m² fasády</t>
         </is>
       </c>
       <c r="F324" s="17" t="n"/>
       <c r="G324" s="30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H324" s="17" t="n"/>
       <c r="I324" s="17" t="n"/>
@@ -10993,7 +10993,7 @@
       </c>
       <c r="E325" s="24" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F325" s="23" t="inlineStr">
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="G325" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H325" s="26" t="n"/>
       <c r="I325" s="26">
@@ -11035,12 +11035,12 @@
       <c r="D326" s="17" t="n"/>
       <c r="E326" s="29" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
+          <t>DXF INSERT block name 'okno 2.NP' count = 4 ks × bbox 1160×1480 mm = 6.88 m² fasády</t>
         </is>
       </c>
       <c r="F326" s="17" t="n"/>
       <c r="G326" s="30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H326" s="17" t="n"/>
       <c r="I326" s="17" t="n"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E327" s="24" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F327" s="23" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G327" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H327" s="26" t="n"/>
       <c r="I327" s="26">
@@ -11106,12 +11106,12 @@
       <c r="D328" s="17" t="n"/>
       <c r="E328" s="29" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP' count = 3 ks × bbox 1785×1241 mm = 6.66 m² fasády</t>
         </is>
       </c>
       <c r="F328" s="17" t="n"/>
       <c r="G328" s="30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H328" s="17" t="n"/>
       <c r="I328" s="17" t="n"/>
@@ -11135,7 +11135,7 @@
       </c>
       <c r="E329" s="24" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F329" s="23" t="inlineStr">
@@ -11177,7 +11177,7 @@
       <c r="D330" s="17" t="n"/>
       <c r="E330" s="29" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
+          <t>DXF INSERT block name 'okno 3.NP vzadu' count = 1 ks × bbox 2075×1241 mm = 2.57 m² fasády</t>
         </is>
       </c>
       <c r="F330" s="17" t="n"/>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="E331" s="24" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F331" s="23" t="inlineStr">
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="G331" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H331" s="26" t="n"/>
       <c r="I331" s="26">
@@ -11248,12 +11248,12 @@
       <c r="D332" s="17" t="n"/>
       <c r="E332" s="29" t="inlineStr">
         <is>
-          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
+          <t>DXF INSERT block name 'okno male 3.NP vzadu' count = 1 ks × bbox 800×1241 mm = 0.99 m² fasády</t>
         </is>
       </c>
       <c r="F332" s="17" t="n"/>
       <c r="G332" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H332" s="17" t="n"/>
       <c r="I332" s="17" t="n"/>
@@ -11272,12 +11272,12 @@
       </c>
       <c r="D333" s="24" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E333" s="24" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F333" s="23" t="inlineStr">
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="G333" s="25" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H333" s="26" t="n"/>
       <c r="I333" s="26">
@@ -11319,12 +11319,12 @@
       <c r="D334" s="17" t="n"/>
       <c r="E334" s="29" t="inlineStr">
         <is>
-          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
+          <t>DXF INSERT block name 'okno malé vzadu' count = 2 ks × bbox 700×800 mm = 1.12 m² fasády</t>
         </is>
       </c>
       <c r="F334" s="17" t="n"/>
       <c r="G334" s="30" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H334" s="17" t="n"/>
       <c r="I334" s="17" t="n"/>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="D335" s="24" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E335" s="24" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F335" s="23" t="inlineStr">
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="G335" s="25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H335" s="26" t="n"/>
       <c r="I335" s="26">
@@ -11390,12 +11390,12 @@
       <c r="D336" s="17" t="n"/>
       <c r="E336" s="29" t="inlineStr">
         <is>
-          <t>TZ ARS — vstupní plastové dveře</t>
+          <t>Σ uličních oken (block names bez 'vzadu' = okno 1.NP 2 + okno 2.NP 4 + okno 3.NP 3) = 9 ks</t>
         </is>
       </c>
       <c r="F336" s="17" t="n"/>
       <c r="G336" s="30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H336" s="17" t="n"/>
       <c r="I336" s="17" t="n"/>
@@ -11414,12 +11414,12 @@
       </c>
       <c r="D337" s="24" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E337" s="24" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F337" s="23" t="inlineStr">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="G337" s="25" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H337" s="26" t="n"/>
       <c r="I337" s="26">
@@ -11461,12 +11461,12 @@
       <c r="D338" s="17" t="n"/>
       <c r="E338" s="29" t="inlineStr">
         <is>
-          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
+          <t>TZ ARS — vstupní plastové dveře</t>
         </is>
       </c>
       <c r="F338" s="17" t="n"/>
       <c r="G338" s="30" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H338" s="17" t="n"/>
       <c r="I338" s="17" t="n"/>
@@ -11485,12 +11485,12 @@
       </c>
       <c r="D339" s="24" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E339" s="24" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F339" s="23" t="inlineStr">
@@ -11499,7 +11499,7 @@
         </is>
       </c>
       <c r="G339" s="25" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H339" s="26" t="n"/>
       <c r="I339" s="26">
@@ -11532,12 +11532,12 @@
       <c r="D340" s="17" t="n"/>
       <c r="E340" s="29" t="inlineStr">
         <is>
-          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
+          <t>3 patra × ~5 dveří (4 pokoje + chodba): 1.NP byt + 2.NP děti + 3.NP nový byt</t>
         </is>
       </c>
       <c r="F340" s="17" t="n"/>
       <c r="G340" s="30" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H340" s="17" t="n"/>
       <c r="I340" s="17" t="n"/>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="D341" s="24" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E341" s="24" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F341" s="23" t="inlineStr">
@@ -11570,7 +11570,7 @@
         </is>
       </c>
       <c r="G341" s="25" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H341" s="26" t="n"/>
       <c r="I341" s="26">
@@ -11603,12 +11603,12 @@
       <c r="D342" s="17" t="n"/>
       <c r="E342" s="29" t="inlineStr">
         <is>
-          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
+          <t>1× dveře na vrcholu schodiště 1.PP/1.NP (room 1.08 → 0.01) per PBŘ TUSPO</t>
         </is>
       </c>
       <c r="F342" s="17" t="n"/>
       <c r="G342" s="30" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H342" s="17" t="n"/>
       <c r="I342" s="17" t="n"/>
@@ -11617,100 +11617,100 @@
       <c r="L342" s="17" t="n"/>
     </row>
     <row r="343">
-      <c r="B343" s="21" t="n"/>
-      <c r="C343" s="22" t="inlineStr">
+      <c r="B343" s="23" t="n">
+        <v>138</v>
+      </c>
+      <c r="C343" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D343" s="24" t="inlineStr">
+        <is>
+          <t>764811112</t>
+        </is>
+      </c>
+      <c r="E343" s="24" t="inlineStr">
+        <is>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+        </is>
+      </c>
+      <c r="F343" s="23" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G343" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="H343" s="26" t="n"/>
+      <c r="I343" s="26">
+        <f>IF(H343="",0,G343*H343)</f>
+        <v/>
+      </c>
+      <c r="J343" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K343" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L343" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" s="17" t="n"/>
+      <c r="C344" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D344" s="17" t="n"/>
+      <c r="E344" s="29" t="inlineStr">
+        <is>
+          <t>DXF okno × 16 ks (Path C Tier 4) = 16 parapetů</t>
+        </is>
+      </c>
+      <c r="F344" s="17" t="n"/>
+      <c r="G344" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="H344" s="17" t="n"/>
+      <c r="I344" s="17" t="n"/>
+      <c r="J344" s="17" t="n"/>
+      <c r="K344" s="17" t="n"/>
+      <c r="L344" s="17" t="n"/>
+    </row>
+    <row r="345">
+      <c r="B345" s="21" t="n"/>
+      <c r="C345" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D343" s="22" t="inlineStr">
+      <c r="D345" s="22" t="inlineStr">
         <is>
           <t>PSV-76</t>
         </is>
       </c>
-      <c r="E343" s="22" t="inlineStr">
+      <c r="E345" s="22" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
-      <c r="F343" s="21" t="n"/>
-      <c r="G343" s="21" t="n"/>
-      <c r="H343" s="21" t="n"/>
-      <c r="I343" s="21" t="n"/>
-      <c r="J343" s="21" t="n"/>
-      <c r="K343" s="21" t="n"/>
-      <c r="L343" s="21" t="n"/>
-    </row>
-    <row r="344">
-      <c r="B344" s="23" t="n">
-        <v>138</v>
-      </c>
-      <c r="C344" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D344" s="24" t="inlineStr">
-        <is>
-          <t>767531111</t>
-        </is>
-      </c>
-      <c r="E344" s="24" t="inlineStr">
-        <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
-        </is>
-      </c>
-      <c r="F344" s="23" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G344" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H344" s="26" t="n"/>
-      <c r="I344" s="26">
-        <f>IF(H344="",0,G344*H344)</f>
-        <v/>
-      </c>
-      <c r="J344" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K344" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.obchodprodilnu.cz/produkty/stavebni-prvky-a-mate]</t>
-        </is>
-      </c>
-      <c r="L344" s="5" t="inlineStr">
-        <is>
-          <t>PSV-76 Zámečnictví</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="B345" s="17" t="n"/>
-      <c r="C345" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D345" s="17" t="n"/>
-      <c r="E345" s="29" t="inlineStr">
-        <is>
-          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
-        </is>
-      </c>
-      <c r="F345" s="17" t="n"/>
-      <c r="G345" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H345" s="17" t="n"/>
-      <c r="I345" s="17" t="n"/>
-      <c r="J345" s="17" t="n"/>
-      <c r="K345" s="17" t="n"/>
-      <c r="L345" s="17" t="n"/>
+      <c r="F345" s="21" t="n"/>
+      <c r="G345" s="21" t="n"/>
+      <c r="H345" s="21" t="n"/>
+      <c r="I345" s="21" t="n"/>
+      <c r="J345" s="21" t="n"/>
+      <c r="K345" s="21" t="n"/>
+      <c r="L345" s="21" t="n"/>
     </row>
     <row r="346">
       <c r="B346" s="23" t="n">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="E346" s="24" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F346" s="23" t="inlineStr">
@@ -11770,7 +11770,7 @@
       <c r="D347" s="17" t="n"/>
       <c r="E347" s="29" t="inlineStr">
         <is>
-          <t>1 schodiště do podkroví (TZ ARS)</t>
+          <t>1 schodiště (~8 stupňů × ~3 m výška)</t>
         </is>
       </c>
       <c r="F347" s="17" t="n"/>
@@ -11794,21 +11794,21 @@
       </c>
       <c r="D348" s="24" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E348" s="24" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F348" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G348" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H348" s="26" t="n"/>
       <c r="I348" s="26">
@@ -11820,9 +11820,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K348" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K348" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.obchodprodilnu.cz/produkty/stavebni-prvky-a-mate]</t>
         </is>
       </c>
       <c r="L348" s="5" t="inlineStr">
@@ -11841,12 +11841,12 @@
       <c r="D349" s="17" t="n"/>
       <c r="E349" s="29" t="inlineStr">
         <is>
-          <t>2 vstupy</t>
+          <t>1 schodiště do podkroví (TZ ARS)</t>
         </is>
       </c>
       <c r="F349" s="17" t="n"/>
       <c r="G349" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H349" s="17" t="n"/>
       <c r="I349" s="17" t="n"/>
@@ -11865,21 +11865,21 @@
       </c>
       <c r="D350" s="24" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E350" s="24" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F350" s="23" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G350" s="25" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H350" s="26" t="n"/>
       <c r="I350" s="26">
@@ -11912,12 +11912,12 @@
       <c r="D351" s="17" t="n"/>
       <c r="E351" s="29" t="inlineStr">
         <is>
-          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
+          <t>2 vstupy</t>
         </is>
       </c>
       <c r="F351" s="17" t="n"/>
       <c r="G351" s="30" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H351" s="17" t="n"/>
       <c r="I351" s="17" t="n"/>
@@ -11926,100 +11926,100 @@
       <c r="L351" s="17" t="n"/>
     </row>
     <row r="352">
-      <c r="B352" s="21" t="n"/>
-      <c r="C352" s="22" t="inlineStr">
+      <c r="B352" s="23" t="n">
+        <v>142</v>
+      </c>
+      <c r="C352" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D352" s="24" t="inlineStr">
+        <is>
+          <t>767163115</t>
+        </is>
+      </c>
+      <c r="E352" s="24" t="inlineStr">
+        <is>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+        </is>
+      </c>
+      <c r="F352" s="23" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G352" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="H352" s="26" t="n"/>
+      <c r="I352" s="26">
+        <f>IF(H352="",0,G352*H352)</f>
+        <v/>
+      </c>
+      <c r="J352" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K352" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L352" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnictví</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" s="17" t="n"/>
+      <c r="C353" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D353" s="17" t="n"/>
+      <c r="E353" s="29" t="inlineStr">
+        <is>
+          <t>odhad 12 m interier (2 schodiště × 6 m) + 6 m terasa</t>
+        </is>
+      </c>
+      <c r="F353" s="17" t="n"/>
+      <c r="G353" s="30" t="n">
+        <v>18</v>
+      </c>
+      <c r="H353" s="17" t="n"/>
+      <c r="I353" s="17" t="n"/>
+      <c r="J353" s="17" t="n"/>
+      <c r="K353" s="17" t="n"/>
+      <c r="L353" s="17" t="n"/>
+    </row>
+    <row r="354">
+      <c r="B354" s="21" t="n"/>
+      <c r="C354" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D352" s="22" t="inlineStr">
+      <c r="D354" s="22" t="inlineStr">
         <is>
           <t>PSV-77</t>
         </is>
       </c>
-      <c r="E352" s="22" t="inlineStr">
+      <c r="E354" s="22" t="inlineStr">
         <is>
           <t>PSV-77 Podlahy</t>
         </is>
       </c>
-      <c r="F352" s="21" t="n"/>
-      <c r="G352" s="21" t="n"/>
-      <c r="H352" s="21" t="n"/>
-      <c r="I352" s="21" t="n"/>
-      <c r="J352" s="21" t="n"/>
-      <c r="K352" s="21" t="n"/>
-      <c r="L352" s="21" t="n"/>
-    </row>
-    <row r="353">
-      <c r="B353" s="23" t="n">
-        <v>142</v>
-      </c>
-      <c r="C353" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D353" s="24" t="inlineStr">
-        <is>
-          <t>776511820</t>
-        </is>
-      </c>
-      <c r="E353" s="24" t="inlineStr">
-        <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
-        </is>
-      </c>
-      <c r="F353" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G353" s="25" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="H353" s="26" t="n"/>
-      <c r="I353" s="26">
-        <f>IF(H353="",0,G353*H353)</f>
-        <v/>
-      </c>
-      <c r="J353" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K353" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://podminky.urs.cz/item/CS_URS_2021_02/776321212]</t>
-        </is>
-      </c>
-      <c r="L353" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="B354" s="17" t="n"/>
-      <c r="C354" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D354" s="17" t="n"/>
-      <c r="E354" s="29" t="inlineStr">
-        <is>
-          <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
-        </is>
-      </c>
-      <c r="F354" s="17" t="n"/>
-      <c r="G354" s="30" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="H354" s="17" t="n"/>
-      <c r="I354" s="17" t="n"/>
-      <c r="J354" s="17" t="n"/>
-      <c r="K354" s="17" t="n"/>
-      <c r="L354" s="17" t="n"/>
+      <c r="F354" s="21" t="n"/>
+      <c r="G354" s="21" t="n"/>
+      <c r="H354" s="21" t="n"/>
+      <c r="I354" s="21" t="n"/>
+      <c r="J354" s="21" t="n"/>
+      <c r="K354" s="21" t="n"/>
+      <c r="L354" s="21" t="n"/>
     </row>
     <row r="355">
       <c r="B355" s="23" t="n">
@@ -12032,12 +12032,12 @@
       </c>
       <c r="D355" s="24" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E355" s="24" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F355" s="23" t="inlineStr">
@@ -12046,7 +12046,7 @@
         </is>
       </c>
       <c r="G355" s="25" t="n">
-        <v>13.5</v>
+        <v>171.5</v>
       </c>
       <c r="H355" s="26" t="n"/>
       <c r="I355" s="26">
@@ -12058,9 +12058,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K355" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K355" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://podminky.urs.cz/item/CS_URS_2021_02/776321212]</t>
         </is>
       </c>
       <c r="L355" s="5" t="inlineStr">
@@ -12079,12 +12079,12 @@
       <c r="D356" s="17" t="n"/>
       <c r="E356" s="29" t="inlineStr">
         <is>
-          <t>1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 2.03=2.4 + 3.04=4.8 = 13.5 m²</t>
+          <t>1.01=12.4 + 1.02=3.6 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 + 2.01=7.3 + 2.02=5.9 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 + 3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.05=32.8 + 3.06=12.8 = 171.5 m²</t>
         </is>
       </c>
       <c r="F356" s="17" t="n"/>
       <c r="G356" s="30" t="n">
-        <v>13.5</v>
+        <v>171.5</v>
       </c>
       <c r="H356" s="17" t="n"/>
       <c r="I356" s="17" t="n"/>
@@ -12108,7 +12108,7 @@
       </c>
       <c r="E357" s="24" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F357" s="23" t="inlineStr">
@@ -12117,7 +12117,7 @@
         </is>
       </c>
       <c r="G357" s="25" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="H357" s="26" t="n"/>
       <c r="I357" s="26">
@@ -12150,12 +12150,12 @@
       <c r="D358" s="17" t="n"/>
       <c r="E358" s="29" t="inlineStr">
         <is>
-          <t>0.01=3.5 + 0.02=4.4 + 0.03=22.2 + 0.04=2.3 = 32.4 m²</t>
+          <t>1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 2.03=2.4 + 3.04=4.8 = 13.5 m²</t>
         </is>
       </c>
       <c r="F358" s="17" t="n"/>
       <c r="G358" s="30" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="H358" s="17" t="n"/>
       <c r="I358" s="17" t="n"/>
@@ -12174,12 +12174,12 @@
       </c>
       <c r="D359" s="24" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E359" s="24" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F359" s="23" t="inlineStr">
@@ -12188,7 +12188,7 @@
         </is>
       </c>
       <c r="G359" s="25" t="n">
-        <v>25</v>
+        <v>32.4</v>
       </c>
       <c r="H359" s="26" t="n"/>
       <c r="I359" s="26">
@@ -12221,12 +12221,12 @@
       <c r="D360" s="17" t="n"/>
       <c r="E360" s="29" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
+          <t>0.01=3.5 + 0.02=4.4 + 0.03=22.2 + 0.04=2.3 = 32.4 m²</t>
         </is>
       </c>
       <c r="F360" s="17" t="n"/>
       <c r="G360" s="30" t="n">
-        <v>25</v>
+        <v>32.4</v>
       </c>
       <c r="H360" s="17" t="n"/>
       <c r="I360" s="17" t="n"/>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="D361" s="24" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E361" s="24" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F361" s="23" t="inlineStr">
@@ -12259,7 +12259,7 @@
         </is>
       </c>
       <c r="G361" s="25" t="n">
-        <v>126.4</v>
+        <v>25</v>
       </c>
       <c r="H361" s="26" t="n"/>
       <c r="I361" s="26">
@@ -12292,12 +12292,12 @@
       <c r="D362" s="17" t="n"/>
       <c r="E362" s="29" t="inlineStr">
         <is>
-          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
+          <t>TZ ARS dům §3.2.3 — 'patro pro přespání z biodesky nad kleštinami'; DXF dum_DPZ NEMÁ samostatnou místnost s biodeska klasifikací (PLOT_DREVENY_04=0 v dum_DPZ, ten block je terasa v situaci). Fallback TZ.</t>
         </is>
       </c>
       <c r="F362" s="17" t="n"/>
       <c r="G362" s="30" t="n">
-        <v>126.4</v>
+        <v>25</v>
       </c>
       <c r="H362" s="17" t="n"/>
       <c r="I362" s="17" t="n"/>
@@ -12316,21 +12316,21 @@
       </c>
       <c r="D363" s="24" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E363" s="24" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F363" s="23" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G363" s="25" t="n">
-        <v>72.03</v>
+        <v>126.4</v>
       </c>
       <c r="H363" s="26" t="n"/>
       <c r="I363" s="26">
@@ -12363,12 +12363,12 @@
       <c r="D364" s="17" t="n"/>
       <c r="E364" s="29" t="inlineStr">
         <is>
-          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
+          <t>vinyl 1.NP+3.NP + dlažba mokré (vyňato 2.NP suchá skladba) = 126.4 m²</t>
         </is>
       </c>
       <c r="F364" s="17" t="n"/>
       <c r="G364" s="30" t="n">
-        <v>72.03</v>
+        <v>126.4</v>
       </c>
       <c r="H364" s="17" t="n"/>
       <c r="I364" s="17" t="n"/>
@@ -12387,12 +12387,12 @@
       </c>
       <c r="D365" s="24" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E365" s="24" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F365" s="23" t="inlineStr">
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="G365" s="25" t="n">
-        <v>19.28</v>
+        <v>72.03</v>
       </c>
       <c r="H365" s="26" t="n"/>
       <c r="I365" s="26">
@@ -12434,12 +12434,12 @@
       <c r="D366" s="17" t="n"/>
       <c r="E366" s="29" t="inlineStr">
         <is>
-          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
+          <t>vinyl plocha 171.5 m² × 0.42 m soklíku/m² (typ. obvod/plocha ratio v Czech RD místnosti) = 72.03 bm</t>
         </is>
       </c>
       <c r="F366" s="17" t="n"/>
       <c r="G366" s="30" t="n">
-        <v>19.28</v>
+        <v>72.03</v>
       </c>
       <c r="H366" s="17" t="n"/>
       <c r="I366" s="17" t="n"/>
@@ -12448,100 +12448,100 @@
       <c r="L366" s="17" t="n"/>
     </row>
     <row r="367">
-      <c r="B367" s="21" t="n"/>
-      <c r="C367" s="22" t="inlineStr">
+      <c r="B367" s="23" t="n">
+        <v>149</v>
+      </c>
+      <c r="C367" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D367" s="24" t="inlineStr">
+        <is>
+          <t>771274107</t>
+        </is>
+      </c>
+      <c r="E367" s="24" t="inlineStr">
+        <is>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+        </is>
+      </c>
+      <c r="F367" s="23" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G367" s="25" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="H367" s="26" t="n"/>
+      <c r="I367" s="26">
+        <f>IF(H367="",0,G367*H367)</f>
+        <v/>
+      </c>
+      <c r="J367" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K367" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L367" s="5" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" s="17" t="n"/>
+      <c r="C368" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D368" s="17" t="n"/>
+      <c r="E368" s="29" t="inlineStr">
+        <is>
+          <t>(dlažba mokré 13.5 + dlažba sklep 32.4) × 0.42 m soklíku/m² = 19.28 bm</t>
+        </is>
+      </c>
+      <c r="F368" s="17" t="n"/>
+      <c r="G368" s="30" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="H368" s="17" t="n"/>
+      <c r="I368" s="17" t="n"/>
+      <c r="J368" s="17" t="n"/>
+      <c r="K368" s="17" t="n"/>
+      <c r="L368" s="17" t="n"/>
+    </row>
+    <row r="369">
+      <c r="B369" s="21" t="n"/>
+      <c r="C369" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D367" s="22" t="inlineStr">
+      <c r="D369" s="22" t="inlineStr">
         <is>
           <t>PSV-78</t>
         </is>
       </c>
-      <c r="E367" s="22" t="inlineStr">
+      <c r="E369" s="22" t="inlineStr">
         <is>
           <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
-      <c r="F367" s="21" t="n"/>
-      <c r="G367" s="21" t="n"/>
-      <c r="H367" s="21" t="n"/>
-      <c r="I367" s="21" t="n"/>
-      <c r="J367" s="21" t="n"/>
-      <c r="K367" s="21" t="n"/>
-      <c r="L367" s="21" t="n"/>
-    </row>
-    <row r="368">
-      <c r="B368" s="23" t="n">
-        <v>149</v>
-      </c>
-      <c r="C368" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D368" s="24" t="inlineStr">
-        <is>
-          <t>612311311</t>
-        </is>
-      </c>
-      <c r="E368" s="24" t="inlineStr">
-        <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
-        </is>
-      </c>
-      <c r="F368" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G368" s="25" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="H368" s="26" t="n"/>
-      <c r="I368" s="26">
-        <f>IF(H368="",0,G368*H368)</f>
-        <v/>
-      </c>
-      <c r="J368" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K368" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L368" s="5" t="inlineStr">
-        <is>
-          <t>PSV-78 Povrchové úpravy</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="B369" s="17" t="n"/>
-      <c r="C369" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D369" s="17" t="n"/>
-      <c r="E369" s="29" t="inlineStr">
-        <is>
-          <t>Σ obvodů rooms 1.PP (0.01=3.5m²→7.64m, 0.02=4.4m²→8.56m, 0.03=22.2m²→19.24m, 0.04=2.3m²→6.19m) = 41.63 m × výška 2.1 m = 87.4 m² stěn; − okna 6.61 − dveře 2.6 = 78.2 m²</t>
-        </is>
-      </c>
-      <c r="F369" s="17" t="n"/>
-      <c r="G369" s="30" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="H369" s="17" t="n"/>
-      <c r="I369" s="17" t="n"/>
-      <c r="J369" s="17" t="n"/>
-      <c r="K369" s="17" t="n"/>
-      <c r="L369" s="17" t="n"/>
+      <c r="F369" s="21" t="n"/>
+      <c r="G369" s="21" t="n"/>
+      <c r="H369" s="21" t="n"/>
+      <c r="I369" s="21" t="n"/>
+      <c r="J369" s="21" t="n"/>
+      <c r="K369" s="21" t="n"/>
+      <c r="L369" s="21" t="n"/>
     </row>
     <row r="370">
       <c r="B370" s="23" t="n">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="E370" s="24" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F370" s="23" t="inlineStr">
@@ -12568,7 +12568,7 @@
         </is>
       </c>
       <c r="G370" s="25" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="H370" s="26" t="n"/>
       <c r="I370" s="26">
@@ -12601,12 +12601,12 @@
       <c r="D371" s="17" t="n"/>
       <c r="E371" s="29" t="inlineStr">
         <is>
-          <t>Σ obvodů rooms 1.NP (1.01=12.4m²→14.38m, 1.02=3.6m²→7.75m, 1.03=0.7m²→3.42m, 1.04=1.5m²→5.0m, 1.05=4.1m²→8.27m, 1.06=24.0m²→20.0m, 1.07=9.4m²→12.52m, 1.08=3.8m²→7.96m) = 79.3 m × výška 2.795 m = 221.6 m² stěn; − okna 6.61 − dveře 6.6 = 208.4 m²</t>
+          <t>Σ obvodů rooms 1.PP (0.01=3.5m²→7.64m, 0.02=4.4m²→8.56m, 0.03=22.2m²→19.24m, 0.04=2.3m²→6.19m) = 41.63 m × výška 2.1 m = 87.4 m² stěn; − okna 6.61 − dveře 2.6 = 78.2 m²</t>
         </is>
       </c>
       <c r="F371" s="17" t="n"/>
       <c r="G371" s="30" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="H371" s="17" t="n"/>
       <c r="I371" s="17" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="E372" s="24" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F372" s="23" t="inlineStr">
@@ -12639,7 +12639,7 @@
         </is>
       </c>
       <c r="G372" s="25" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="H372" s="26" t="n"/>
       <c r="I372" s="26">
@@ -12672,12 +12672,12 @@
       <c r="D373" s="17" t="n"/>
       <c r="E373" s="29" t="inlineStr">
         <is>
-          <t>Σ obvodů rooms 2.NP (2.01=7.3m²→11.03m, 2.02=5.9m²→9.92m, 2.03=2.4m²→6.32m, 2.04=15.5m²→16.07m, 2.05=14.1m²→15.33m, 2.06=15.8m²→16.23m) = 74.9 m × výška 2.865 m = 214.6 m² stěn; − okna 6.61 − dveře 6.4 = 201.6 m²</t>
+          <t>Σ obvodů rooms 1.NP (1.01=12.4m²→14.38m, 1.02=3.6m²→7.75m, 1.03=0.7m²→3.42m, 1.04=1.5m²→5.0m, 1.05=4.1m²→8.27m, 1.06=24.0m²→20.0m, 1.07=9.4m²→12.52m, 1.08=3.8m²→7.96m) = 79.3 m × výška 2.795 m = 221.6 m² stěn; − okna 6.61 − dveře 6.6 = 208.4 m²</t>
         </is>
       </c>
       <c r="F373" s="17" t="n"/>
       <c r="G373" s="30" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="H373" s="17" t="n"/>
       <c r="I373" s="17" t="n"/>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="E374" s="24" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F374" s="23" t="inlineStr">
@@ -12710,7 +12710,7 @@
         </is>
       </c>
       <c r="G374" s="25" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="H374" s="26" t="n"/>
       <c r="I374" s="26">
@@ -12743,12 +12743,12 @@
       <c r="D375" s="17" t="n"/>
       <c r="E375" s="29" t="inlineStr">
         <is>
-          <t>Σ obvodů rooms 3.NP (3.01=7.6m²→11.25m, 3.02=4.1m²→8.27m, 3.03=2.4m²→6.32m, 3.04=4.8m²→8.94m, 3.05=32.8m²→23.38m, 3.06=12.8m²→14.61m) = 72.77 m × výška 2.63 m = 191.4 m² stěn; − okna 6.61 − dveře 5.7 = 179.1 m²</t>
+          <t>Σ obvodů rooms 2.NP (2.01=7.3m²→11.03m, 2.02=5.9m²→9.92m, 2.03=2.4m²→6.32m, 2.04=15.5m²→16.07m, 2.05=14.1m²→15.33m, 2.06=15.8m²→16.23m) = 74.9 m × výška 2.865 m = 214.6 m² stěn; − okna 6.61 − dveře 6.4 = 201.6 m²</t>
         </is>
       </c>
       <c r="F375" s="17" t="n"/>
       <c r="G375" s="30" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="H375" s="17" t="n"/>
       <c r="I375" s="17" t="n"/>
@@ -12767,12 +12767,12 @@
       </c>
       <c r="D376" s="24" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E376" s="24" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F376" s="23" t="inlineStr">
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="G376" s="25" t="n">
-        <v>59.5</v>
+        <v>179.1</v>
       </c>
       <c r="H376" s="26" t="n"/>
       <c r="I376" s="26">
@@ -12814,12 +12814,12 @@
       <c r="D377" s="17" t="n"/>
       <c r="E377" s="29" t="inlineStr">
         <is>
-          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
+          <t>Σ obvodů rooms 3.NP (3.01=7.6m²→11.25m, 3.02=4.1m²→8.27m, 3.03=2.4m²→6.32m, 3.04=4.8m²→8.94m, 3.05=32.8m²→23.38m, 3.06=12.8m²→14.61m) = 72.77 m × výška 2.63 m = 191.4 m² stěn; − okna 6.61 − dveře 5.7 = 179.1 m²</t>
         </is>
       </c>
       <c r="F377" s="17" t="n"/>
       <c r="G377" s="30" t="n">
-        <v>59.5</v>
+        <v>179.1</v>
       </c>
       <c r="H377" s="17" t="n"/>
       <c r="I377" s="17" t="n"/>
@@ -12843,7 +12843,7 @@
       </c>
       <c r="E378" s="24" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F378" s="23" t="inlineStr">
@@ -12852,7 +12852,7 @@
         </is>
       </c>
       <c r="G378" s="25" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="H378" s="26" t="n"/>
       <c r="I378" s="26">
@@ -12885,12 +12885,12 @@
       <c r="D379" s="17" t="n"/>
       <c r="E379" s="29" t="inlineStr">
         <is>
-          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
+          <t>1.01=12.4 + 1.02=3.6 + 1.03=0.7 + 1.04=1.5 + 1.05=4.1 + 1.06=24.0 + 1.07=9.4 + 1.08=3.8 = 59.5 m²</t>
         </is>
       </c>
       <c r="F379" s="17" t="n"/>
       <c r="G379" s="30" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="H379" s="17" t="n"/>
       <c r="I379" s="17" t="n"/>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="E380" s="24" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F380" s="23" t="inlineStr">
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="G380" s="25" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
       <c r="H380" s="26" t="n"/>
       <c r="I380" s="26">
@@ -12956,12 +12956,12 @@
       <c r="D381" s="17" t="n"/>
       <c r="E381" s="29" t="inlineStr">
         <is>
-          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
+          <t>2.01=7.3 + 2.02=5.9 + 2.03=2.4 + 2.04=15.5 + 2.05=14.1 + 2.06=15.8 = 61.1 m²</t>
         </is>
       </c>
       <c r="F381" s="17" t="n"/>
       <c r="G381" s="30" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
       <c r="H381" s="17" t="n"/>
       <c r="I381" s="17" t="n"/>
@@ -12980,12 +12980,12 @@
       </c>
       <c r="D382" s="24" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E382" s="24" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F382" s="23" t="inlineStr">
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="G382" s="25" t="n">
-        <v>13.4</v>
+        <v>64.5</v>
       </c>
       <c r="H382" s="26" t="n"/>
       <c r="I382" s="26">
@@ -13027,12 +13027,12 @@
       <c r="D383" s="17" t="n"/>
       <c r="E383" s="29" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
+          <t>3.01=7.6 + 3.02=4.1 + 3.03=2.4 + 3.04=4.8 + 3.05=32.8 + 3.06=12.8 = 64.5 m²</t>
         </is>
       </c>
       <c r="F383" s="17" t="n"/>
       <c r="G383" s="30" t="n">
-        <v>13.4</v>
+        <v>64.5</v>
       </c>
       <c r="H383" s="17" t="n"/>
       <c r="I383" s="17" t="n"/>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="E384" s="24" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F384" s="23" t="inlineStr">
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="G384" s="25" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
       <c r="H384" s="26" t="n"/>
       <c r="I384" s="26">
@@ -13098,12 +13098,12 @@
       <c r="D385" s="17" t="n"/>
       <c r="E385" s="29" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
+          <t>DXF IP_obrysy místností room 1.05 perimeter 8.4 bm × DXF km Obklady layer výška 1.6 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 13.4 m²</t>
         </is>
       </c>
       <c r="F385" s="17" t="n"/>
       <c r="G385" s="30" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
       <c r="H385" s="17" t="n"/>
       <c r="I385" s="17" t="n"/>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="E386" s="24" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F386" s="23" t="inlineStr">
@@ -13136,7 +13136,7 @@
         </is>
       </c>
       <c r="G386" s="25" t="n">
-        <v>24.3</v>
+        <v>15.2</v>
       </c>
       <c r="H386" s="26" t="n"/>
       <c r="I386" s="26">
@@ -13169,12 +13169,12 @@
       <c r="D387" s="17" t="n"/>
       <c r="E387" s="29" t="inlineStr">
         <is>
-          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
+          <t>DXF IP_obrysy místností room 2.03 perimeter 6.2 bm × DXF km Obklady layer výška 2.45 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 15.2 m²</t>
         </is>
       </c>
       <c r="F387" s="17" t="n"/>
       <c r="G387" s="30" t="n">
-        <v>24.3</v>
+        <v>15.2</v>
       </c>
       <c r="H387" s="17" t="n"/>
       <c r="I387" s="17" t="n"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="E388" s="24" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F388" s="23" t="inlineStr">
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="G388" s="25" t="n">
-        <v>10</v>
+        <v>24.3</v>
       </c>
       <c r="H388" s="26" t="n"/>
       <c r="I388" s="26">
@@ -13240,12 +13240,12 @@
       <c r="D389" s="17" t="n"/>
       <c r="E389" s="29" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
+          <t>DXF IP_obrysy místností room 3.04 perimeter 9.0 bm × DXF km Obklady layer výška 2.7 m (per-koupelna explicit, NE uniform 2.0 m fallback) = 24.3 m²</t>
         </is>
       </c>
       <c r="F389" s="17" t="n"/>
       <c r="G389" s="30" t="n">
-        <v>10</v>
+        <v>24.3</v>
       </c>
       <c r="H389" s="17" t="n"/>
       <c r="I389" s="17" t="n"/>
@@ -13264,12 +13264,12 @@
       </c>
       <c r="D390" s="24" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E390" s="24" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F390" s="23" t="inlineStr">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="G390" s="25" t="n">
-        <v>78.2</v>
+        <v>10</v>
       </c>
       <c r="H390" s="26" t="n"/>
       <c r="I390" s="26">
@@ -13311,12 +13311,12 @@
       <c r="D391" s="17" t="n"/>
       <c r="E391" s="29" t="inlineStr">
         <is>
-          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT (rooms 1.06 obyt+kuchyně + 3.05 obyt+kuchyně) × 5 m² obklad za linkou = 10 m²</t>
         </is>
       </c>
       <c r="F391" s="17" t="n"/>
       <c r="G391" s="30" t="n">
-        <v>78.2</v>
+        <v>10</v>
       </c>
       <c r="H391" s="17" t="n"/>
       <c r="I391" s="17" t="n"/>
@@ -13340,7 +13340,7 @@
       </c>
       <c r="E392" s="24" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F392" s="23" t="inlineStr">
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="G392" s="25" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="H392" s="26" t="n"/>
       <c r="I392" s="26">
@@ -13382,12 +13382,12 @@
       <c r="D393" s="17" t="n"/>
       <c r="E393" s="29" t="inlineStr">
         <is>
-          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 1.PP 78.2 m² + SDK podhled 0 m² − obklad 0 m² = 78.2 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="F393" s="17" t="n"/>
       <c r="G393" s="30" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="H393" s="17" t="n"/>
       <c r="I393" s="17" t="n"/>
@@ -13411,7 +13411,7 @@
       </c>
       <c r="E394" s="24" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F394" s="23" t="inlineStr">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="G394" s="25" t="n">
-        <v>247.5</v>
+        <v>254.5</v>
       </c>
       <c r="H394" s="26" t="n"/>
       <c r="I394" s="26">
@@ -13453,12 +13453,12 @@
       <c r="D395" s="17" t="n"/>
       <c r="E395" s="29" t="inlineStr">
         <is>
-          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 1.NP 208.4 m² + SDK podhled 59.5 m² − obklad 13.4 m² = 254.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="F395" s="17" t="n"/>
       <c r="G395" s="30" t="n">
-        <v>247.5</v>
+        <v>254.5</v>
       </c>
       <c r="H395" s="17" t="n"/>
       <c r="I395" s="17" t="n"/>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="E396" s="24" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F396" s="23" t="inlineStr">
@@ -13491,7 +13491,7 @@
         </is>
       </c>
       <c r="G396" s="25" t="n">
-        <v>219.3</v>
+        <v>247.5</v>
       </c>
       <c r="H396" s="26" t="n"/>
       <c r="I396" s="26">
@@ -13524,12 +13524,12 @@
       <c r="D397" s="17" t="n"/>
       <c r="E397" s="29" t="inlineStr">
         <is>
-          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
+          <t>omítka 2.NP 201.6 m² + SDK podhled 61.1 m² − obklad 15.2 m² = 247.5 m² (per-podlaží split per audit v2 GAP_007)</t>
         </is>
       </c>
       <c r="F397" s="17" t="n"/>
       <c r="G397" s="30" t="n">
-        <v>219.3</v>
+        <v>247.5</v>
       </c>
       <c r="H397" s="17" t="n"/>
       <c r="I397" s="17" t="n"/>
@@ -13538,100 +13538,100 @@
       <c r="L397" s="17" t="n"/>
     </row>
     <row r="398">
-      <c r="B398" s="21" t="n"/>
-      <c r="C398" s="22" t="inlineStr">
+      <c r="B398" s="23" t="n">
+        <v>164</v>
+      </c>
+      <c r="C398" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D398" s="24" t="inlineStr">
+        <is>
+          <t>784121011</t>
+        </is>
+      </c>
+      <c r="E398" s="24" t="inlineStr">
+        <is>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+        </is>
+      </c>
+      <c r="F398" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G398" s="25" t="n">
+        <v>219.3</v>
+      </c>
+      <c r="H398" s="26" t="n"/>
+      <c r="I398" s="26">
+        <f>IF(H398="",0,G398*H398)</f>
+        <v/>
+      </c>
+      <c r="J398" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K398" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L398" s="5" t="inlineStr">
+        <is>
+          <t>PSV-78 Povrchové úpravy</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" s="17" t="n"/>
+      <c r="C399" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D399" s="17" t="n"/>
+      <c r="E399" s="29" t="inlineStr">
+        <is>
+          <t>omítka 3.NP 179.1 m² + SDK podhled 64.5 m² − obklad 24.3 m² = 219.3 m² (per-podlaží split per audit v2 GAP_007)</t>
+        </is>
+      </c>
+      <c r="F399" s="17" t="n"/>
+      <c r="G399" s="30" t="n">
+        <v>219.3</v>
+      </c>
+      <c r="H399" s="17" t="n"/>
+      <c r="I399" s="17" t="n"/>
+      <c r="J399" s="17" t="n"/>
+      <c r="K399" s="17" t="n"/>
+      <c r="L399" s="17" t="n"/>
+    </row>
+    <row r="400">
+      <c r="B400" s="21" t="n"/>
+      <c r="C400" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D398" s="22" t="inlineStr">
+      <c r="D400" s="22" t="inlineStr">
         <is>
           <t>PSV-95</t>
         </is>
       </c>
-      <c r="E398" s="22" t="inlineStr">
+      <c r="E400" s="22" t="inlineStr">
         <is>
           <t>PSV-95 Detekce požární</t>
         </is>
       </c>
-      <c r="F398" s="21" t="n"/>
-      <c r="G398" s="21" t="n"/>
-      <c r="H398" s="21" t="n"/>
-      <c r="I398" s="21" t="n"/>
-      <c r="J398" s="21" t="n"/>
-      <c r="K398" s="21" t="n"/>
-      <c r="L398" s="21" t="n"/>
-    </row>
-    <row r="399">
-      <c r="B399" s="23" t="n">
-        <v>164</v>
-      </c>
-      <c r="C399" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D399" s="24" t="inlineStr">
-        <is>
-          <t>375211101</t>
-        </is>
-      </c>
-      <c r="E399" s="24" t="inlineStr">
-        <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
-        </is>
-      </c>
-      <c r="F399" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G399" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H399" s="26" t="n"/>
-      <c r="I399" s="26">
-        <f>IF(H399="",0,G399*H399)</f>
-        <v/>
-      </c>
-      <c r="J399" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K399" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.technicke-normy-csn.cz/csn-en-14604-342711-18294]</t>
-        </is>
-      </c>
-      <c r="L399" s="5" t="inlineStr">
-        <is>
-          <t>PSV-95 Detekce požární</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="B400" s="17" t="n"/>
-      <c r="C400" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D400" s="17" t="n"/>
-      <c r="E400" s="29" t="inlineStr">
-        <is>
-          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
-        </is>
-      </c>
-      <c r="F400" s="17" t="n"/>
-      <c r="G400" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="H400" s="17" t="n"/>
-      <c r="I400" s="17" t="n"/>
-      <c r="J400" s="17" t="n"/>
-      <c r="K400" s="17" t="n"/>
-      <c r="L400" s="17" t="n"/>
+      <c r="F400" s="21" t="n"/>
+      <c r="G400" s="21" t="n"/>
+      <c r="H400" s="21" t="n"/>
+      <c r="I400" s="21" t="n"/>
+      <c r="J400" s="21" t="n"/>
+      <c r="K400" s="21" t="n"/>
+      <c r="L400" s="21" t="n"/>
     </row>
     <row r="401">
       <c r="B401" s="23" t="n">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="D401" s="24" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E401" s="24" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F401" s="23" t="inlineStr">
@@ -13658,7 +13658,7 @@
         </is>
       </c>
       <c r="G401" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H401" s="26" t="n"/>
       <c r="I401" s="26">
@@ -13670,9 +13670,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K401" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K401" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.technicke-normy-csn.cz/csn-en-14604-342711-18294]</t>
         </is>
       </c>
       <c r="L401" s="5" t="inlineStr">
@@ -13691,12 +13691,12 @@
       <c r="D402" s="17" t="n"/>
       <c r="E402" s="29" t="inlineStr">
         <is>
-          <t>TZ PBŘ — min. 1 ks 34A</t>
+          <t>TZ PBŘ — 4 hlásiče v daných místnostech</t>
         </is>
       </c>
       <c r="F402" s="17" t="n"/>
       <c r="G402" s="30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H402" s="17" t="n"/>
       <c r="I402" s="17" t="n"/>
@@ -13705,125 +13705,125 @@
       <c r="L402" s="17" t="n"/>
     </row>
     <row r="403">
-      <c r="B403" s="19" t="n"/>
-      <c r="C403" s="20" t="inlineStr">
+      <c r="B403" s="23" t="n">
+        <v>166</v>
+      </c>
+      <c r="C403" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D403" s="24" t="inlineStr">
+        <is>
+          <t>966067121</t>
+        </is>
+      </c>
+      <c r="E403" s="24" t="inlineStr">
+        <is>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+        </is>
+      </c>
+      <c r="F403" s="23" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G403" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H403" s="26" t="n"/>
+      <c r="I403" s="26">
+        <f>IF(H403="",0,G403*H403)</f>
+        <v/>
+      </c>
+      <c r="J403" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K403" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L403" s="5" t="inlineStr">
+        <is>
+          <t>PSV-95 Detekce požární</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" s="17" t="n"/>
+      <c r="C404" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D404" s="17" t="n"/>
+      <c r="E404" s="29" t="inlineStr">
+        <is>
+          <t>TZ PBŘ — min. 1 ks 34A</t>
+        </is>
+      </c>
+      <c r="F404" s="17" t="n"/>
+      <c r="G404" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H404" s="17" t="n"/>
+      <c r="I404" s="17" t="n"/>
+      <c r="J404" s="17" t="n"/>
+      <c r="K404" s="17" t="n"/>
+      <c r="L404" s="17" t="n"/>
+    </row>
+    <row r="405">
+      <c r="B405" s="19" t="n"/>
+      <c r="C405" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D403" s="20" t="inlineStr">
+      <c r="D405" s="20" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E403" s="20" t="inlineStr">
+      <c r="E405" s="20" t="inlineStr">
         <is>
           <t>Vedlejší rozpočtové náklady</t>
         </is>
       </c>
-      <c r="F403" s="19" t="n"/>
-      <c r="G403" s="19" t="n"/>
-      <c r="H403" s="19" t="n"/>
-      <c r="I403" s="19" t="n"/>
-      <c r="J403" s="19" t="n"/>
-      <c r="K403" s="19" t="n"/>
-      <c r="L403" s="19" t="n"/>
-    </row>
-    <row r="404">
-      <c r="B404" s="21" t="n"/>
-      <c r="C404" s="22" t="inlineStr">
+      <c r="F405" s="19" t="n"/>
+      <c r="G405" s="19" t="n"/>
+      <c r="H405" s="19" t="n"/>
+      <c r="I405" s="19" t="n"/>
+      <c r="J405" s="19" t="n"/>
+      <c r="K405" s="19" t="n"/>
+      <c r="L405" s="19" t="n"/>
+    </row>
+    <row r="406">
+      <c r="B406" s="21" t="n"/>
+      <c r="C406" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D404" s="22" t="inlineStr">
+      <c r="D406" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E404" s="22" t="inlineStr">
+      <c r="E406" s="22" t="inlineStr">
         <is>
           <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
-      <c r="F404" s="21" t="n"/>
-      <c r="G404" s="21" t="n"/>
-      <c r="H404" s="21" t="n"/>
-      <c r="I404" s="21" t="n"/>
-      <c r="J404" s="21" t="n"/>
-      <c r="K404" s="21" t="n"/>
-      <c r="L404" s="21" t="n"/>
-    </row>
-    <row r="405">
-      <c r="B405" s="23" t="n">
-        <v>166</v>
-      </c>
-      <c r="C405" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D405" s="24" t="inlineStr">
-        <is>
-          <t>030011000</t>
-        </is>
-      </c>
-      <c r="E405" s="24" t="inlineStr">
-        <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
-        </is>
-      </c>
-      <c r="F405" s="23" t="inlineStr">
-        <is>
-          <t>kpl-měs</t>
-        </is>
-      </c>
-      <c r="G405" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="H405" s="26" t="n"/>
-      <c r="I405" s="26">
-        <f>IF(H405="",0,G405*H405)</f>
-        <v/>
-      </c>
-      <c r="J405" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K405" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L405" s="5" t="inlineStr">
-        <is>
-          <t>VRN — Zařízení staveniště</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="B406" s="17" t="n"/>
-      <c r="C406" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D406" s="17" t="n"/>
-      <c r="E406" s="29" t="inlineStr">
-        <is>
-          <t>realizace odhad 8 měs (demolice 1.5 + hrubá 2.5 + dokončování 4)</t>
-        </is>
-      </c>
-      <c r="F406" s="17" t="n"/>
-      <c r="G406" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="H406" s="17" t="n"/>
-      <c r="I406" s="17" t="n"/>
-      <c r="J406" s="17" t="n"/>
-      <c r="K406" s="17" t="n"/>
-      <c r="L406" s="17" t="n"/>
+      <c r="F406" s="21" t="n"/>
+      <c r="G406" s="21" t="n"/>
+      <c r="H406" s="21" t="n"/>
+      <c r="I406" s="21" t="n"/>
+      <c r="J406" s="21" t="n"/>
+      <c r="K406" s="21" t="n"/>
+      <c r="L406" s="21" t="n"/>
     </row>
     <row r="407">
       <c r="B407" s="23" t="n">
@@ -13836,17 +13836,17 @@
       </c>
       <c r="D407" s="24" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E407" s="24" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F407" s="23" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G407" s="25" t="n">
@@ -13883,7 +13883,7 @@
       <c r="D408" s="17" t="n"/>
       <c r="E408" s="29" t="inlineStr">
         <is>
-          <t>1 ks × 8 měs realizace</t>
+          <t>realizace odhad 8 měs (demolice 1.5 + hrubá 2.5 + dokončování 4)</t>
         </is>
       </c>
       <c r="F408" s="17" t="n"/>
@@ -13907,21 +13907,21 @@
       </c>
       <c r="D409" s="24" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E409" s="24" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F409" s="23" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G409" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H409" s="26" t="n"/>
       <c r="I409" s="26">
@@ -13954,12 +13954,12 @@
       <c r="D410" s="17" t="n"/>
       <c r="E410" s="29" t="inlineStr">
         <is>
-          <t>Komplexní zřízení + provoz po dobu stavby</t>
+          <t>1 ks × 8 měs realizace</t>
         </is>
       </c>
       <c r="F410" s="17" t="n"/>
       <c r="G410" s="30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H410" s="17" t="n"/>
       <c r="I410" s="17" t="n"/>
@@ -13978,12 +13978,12 @@
       </c>
       <c r="D411" s="24" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E411" s="24" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F411" s="23" t="inlineStr">
@@ -14025,7 +14025,7 @@
       <c r="D412" s="17" t="n"/>
       <c r="E412" s="29" t="inlineStr">
         <is>
-          <t>1 paušál pro dobu výstavby (TZ B m.5 'Zásobování stavby vodou: stávající')</t>
+          <t>Komplexní zřízení + provoz po dobu stavby</t>
         </is>
       </c>
       <c r="F412" s="17" t="n"/>
@@ -14039,284 +14039,284 @@
       <c r="L412" s="17" t="n"/>
     </row>
     <row r="413">
-      <c r="B413" s="21" t="n"/>
-      <c r="C413" s="22" t="inlineStr">
+      <c r="B413" s="23" t="n">
+        <v>170</v>
+      </c>
+      <c r="C413" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D413" s="24" t="inlineStr">
+        <is>
+          <t>012103101</t>
+        </is>
+      </c>
+      <c r="E413" s="24" t="inlineStr">
+        <is>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+        </is>
+      </c>
+      <c r="F413" s="23" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G413" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H413" s="26" t="n"/>
+      <c r="I413" s="26">
+        <f>IF(H413="",0,G413*H413)</f>
+        <v/>
+      </c>
+      <c r="J413" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K413" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L413" s="5" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" s="17" t="n"/>
+      <c r="C414" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D414" s="17" t="n"/>
+      <c r="E414" s="29" t="inlineStr">
+        <is>
+          <t>1 paušál pro dobu výstavby (TZ B m.5 'Zásobování stavby vodou: stávající')</t>
+        </is>
+      </c>
+      <c r="F414" s="17" t="n"/>
+      <c r="G414" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H414" s="17" t="n"/>
+      <c r="I414" s="17" t="n"/>
+      <c r="J414" s="17" t="n"/>
+      <c r="K414" s="17" t="n"/>
+      <c r="L414" s="17" t="n"/>
+    </row>
+    <row r="415">
+      <c r="B415" s="21" t="n"/>
+      <c r="C415" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D413" s="22" t="inlineStr">
+      <c r="D415" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E413" s="22" t="inlineStr">
+      <c r="E415" s="22" t="inlineStr">
         <is>
           <t>VRN — Přesun hmot</t>
         </is>
       </c>
-      <c r="F413" s="21" t="n"/>
-      <c r="G413" s="21" t="n"/>
-      <c r="H413" s="21" t="n"/>
-      <c r="I413" s="21" t="n"/>
-      <c r="J413" s="21" t="n"/>
-      <c r="K413" s="21" t="n"/>
-      <c r="L413" s="21" t="n"/>
-    </row>
-    <row r="414">
-      <c r="B414" s="23" t="n">
-        <v>170</v>
-      </c>
-      <c r="C414" s="23" t="inlineStr">
+      <c r="F415" s="21" t="n"/>
+      <c r="G415" s="21" t="n"/>
+      <c r="H415" s="21" t="n"/>
+      <c r="I415" s="21" t="n"/>
+      <c r="J415" s="21" t="n"/>
+      <c r="K415" s="21" t="n"/>
+      <c r="L415" s="21" t="n"/>
+    </row>
+    <row r="416">
+      <c r="B416" s="23" t="n">
+        <v>171</v>
+      </c>
+      <c r="C416" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D414" s="24" t="inlineStr"/>
-      <c r="E414" s="24" t="inlineStr">
+      <c r="D416" s="24" t="inlineStr"/>
+      <c r="E416" s="24" t="inlineStr">
         <is>
           <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
-      <c r="F414" s="23" t="inlineStr">
+      <c r="F416" s="23" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="G414" s="25" t="n">
+      <c r="G416" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H414" s="26" t="n"/>
-      <c r="I414" s="26">
-        <f>IF(H414="",0,G414*H414)</f>
+      <c r="H416" s="26" t="n"/>
+      <c r="I416" s="26">
+        <f>IF(H416="",0,G416*H416)</f>
         <v/>
       </c>
-      <c r="J414" s="23" t="inlineStr">
+      <c r="J416" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K414" s="33" t="inlineStr">
+      <c r="K416" s="33" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
-      <c r="L414" s="5" t="inlineStr">
+      <c r="L416" s="5" t="inlineStr">
         <is>
           <t>VRN — Přesun hmot</t>
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="B415" s="17" t="n"/>
-      <c r="C415" s="28" t="inlineStr">
+    <row r="417">
+      <c r="B417" s="17" t="n"/>
+      <c r="C417" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D415" s="17" t="n"/>
-      <c r="E415" s="29" t="inlineStr">
+      <c r="D417" s="17" t="n"/>
+      <c r="E417" s="29" t="inlineStr">
         <is>
           <t>TBD — buď % z HSV nákladů (běžně 2-4 %) nebo dle celkové tonáže přesouvaných hmot; množství doplní rozpočtář při cenotvorbě</t>
         </is>
       </c>
-      <c r="F415" s="17" t="n"/>
-      <c r="G415" s="30" t="n">
+      <c r="F417" s="17" t="n"/>
+      <c r="G417" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H415" s="17" t="n"/>
-      <c r="I415" s="17" t="n"/>
-      <c r="J415" s="17" t="n"/>
-      <c r="K415" s="17" t="n"/>
-      <c r="L415" s="17" t="n"/>
-    </row>
-    <row r="416">
-      <c r="B416" s="21" t="n"/>
-      <c r="C416" s="22" t="inlineStr">
+      <c r="H417" s="17" t="n"/>
+      <c r="I417" s="17" t="n"/>
+      <c r="J417" s="17" t="n"/>
+      <c r="K417" s="17" t="n"/>
+      <c r="L417" s="17" t="n"/>
+    </row>
+    <row r="418">
+      <c r="B418" s="21" t="n"/>
+      <c r="C418" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D416" s="22" t="inlineStr">
+      <c r="D418" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E416" s="22" t="inlineStr">
+      <c r="E418" s="22" t="inlineStr">
         <is>
           <t>VRN — Lešení</t>
         </is>
       </c>
-      <c r="F416" s="21" t="n"/>
-      <c r="G416" s="21" t="n"/>
-      <c r="H416" s="21" t="n"/>
-      <c r="I416" s="21" t="n"/>
-      <c r="J416" s="21" t="n"/>
-      <c r="K416" s="21" t="n"/>
-      <c r="L416" s="21" t="n"/>
-    </row>
-    <row r="417">
-      <c r="B417" s="23" t="n">
-        <v>171</v>
-      </c>
-      <c r="C417" s="23" t="inlineStr">
+      <c r="F418" s="21" t="n"/>
+      <c r="G418" s="21" t="n"/>
+      <c r="H418" s="21" t="n"/>
+      <c r="I418" s="21" t="n"/>
+      <c r="J418" s="21" t="n"/>
+      <c r="K418" s="21" t="n"/>
+      <c r="L418" s="21" t="n"/>
+    </row>
+    <row r="419">
+      <c r="B419" s="23" t="n">
+        <v>172</v>
+      </c>
+      <c r="C419" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D417" s="24" t="inlineStr"/>
-      <c r="E417" s="24" t="inlineStr">
+      <c r="D419" s="24" t="inlineStr"/>
+      <c r="E419" s="24" t="inlineStr">
         <is>
           <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
-      <c r="F417" s="23" t="inlineStr">
+      <c r="F419" s="23" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="G417" s="25" t="n">
+      <c r="G419" s="25" t="n">
         <v>503.1</v>
       </c>
-      <c r="H417" s="26" t="n"/>
-      <c r="I417" s="26">
-        <f>IF(H417="",0,G417*H417)</f>
+      <c r="H419" s="26" t="n"/>
+      <c r="I419" s="26">
+        <f>IF(H419="",0,G419*H419)</f>
         <v/>
       </c>
-      <c r="J417" s="23" t="inlineStr">
+      <c r="J419" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K417" s="33" t="inlineStr">
+      <c r="K419" s="33" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
-      <c r="L417" s="5" t="inlineStr">
+      <c r="L419" s="5" t="inlineStr">
         <is>
           <t>VRN — Lešení</t>
         </is>
       </c>
     </row>
-    <row r="418">
-      <c r="B418" s="17" t="n"/>
-      <c r="C418" s="28" t="inlineStr">
+    <row r="420">
+      <c r="B420" s="17" t="n"/>
+      <c r="C420" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D418" s="17" t="n"/>
-      <c r="E418" s="29" t="inlineStr">
+      <c r="D420" s="17" t="n"/>
+      <c r="E420" s="29" t="inlineStr">
         <is>
           <t>obvod domu 38.7 m × výška 13.0 m = 503.1 m² lešenné plochy (pro ETICS fasádu 276.7 m² + krov + klempířinu)</t>
         </is>
       </c>
-      <c r="F418" s="17" t="n"/>
-      <c r="G418" s="30" t="n">
+      <c r="F420" s="17" t="n"/>
+      <c r="G420" s="30" t="n">
         <v>503.1</v>
       </c>
-      <c r="H418" s="17" t="n"/>
-      <c r="I418" s="17" t="n"/>
-      <c r="J418" s="17" t="n"/>
-      <c r="K418" s="17" t="n"/>
-      <c r="L418" s="17" t="n"/>
-    </row>
-    <row r="419">
-      <c r="B419" s="21" t="n"/>
-      <c r="C419" s="22" t="inlineStr">
+      <c r="H420" s="17" t="n"/>
+      <c r="I420" s="17" t="n"/>
+      <c r="J420" s="17" t="n"/>
+      <c r="K420" s="17" t="n"/>
+      <c r="L420" s="17" t="n"/>
+    </row>
+    <row r="421">
+      <c r="B421" s="21" t="n"/>
+      <c r="C421" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D419" s="22" t="inlineStr">
+      <c r="D421" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E419" s="22" t="inlineStr">
+      <c r="E421" s="22" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
-      <c r="F419" s="21" t="n"/>
-      <c r="G419" s="21" t="n"/>
-      <c r="H419" s="21" t="n"/>
-      <c r="I419" s="21" t="n"/>
-      <c r="J419" s="21" t="n"/>
-      <c r="K419" s="21" t="n"/>
-      <c r="L419" s="21" t="n"/>
-    </row>
-    <row r="420">
-      <c r="B420" s="23" t="n">
-        <v>172</v>
-      </c>
-      <c r="C420" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D420" s="24" t="inlineStr">
-        <is>
-          <t>997013211</t>
-        </is>
-      </c>
-      <c r="E420" s="24" t="inlineStr">
-        <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
-        </is>
-      </c>
-      <c r="F420" s="23" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G420" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="H420" s="26" t="n"/>
-      <c r="I420" s="26">
-        <f>IF(H420="",0,G420*H420)</f>
-        <v/>
-      </c>
-      <c r="J420" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K420" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L420" s="5" t="inlineStr">
-        <is>
-          <t>VRN — Doprava + odpad</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="B421" s="17" t="n"/>
-      <c r="C421" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D421" s="17" t="n"/>
-      <c r="E421" s="29" t="inlineStr">
-        <is>
-          <t>TZ B m.10.e: 56.9 t celkem → ~7 kontejnerů 8 m³ (beton/cihly hlavní hmota)</t>
-        </is>
-      </c>
-      <c r="F421" s="17" t="n"/>
-      <c r="G421" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="H421" s="17" t="n"/>
-      <c r="I421" s="17" t="n"/>
-      <c r="J421" s="17" t="n"/>
-      <c r="K421" s="17" t="n"/>
-      <c r="L421" s="17" t="n"/>
+      <c r="F421" s="21" t="n"/>
+      <c r="G421" s="21" t="n"/>
+      <c r="H421" s="21" t="n"/>
+      <c r="I421" s="21" t="n"/>
+      <c r="J421" s="21" t="n"/>
+      <c r="K421" s="21" t="n"/>
+      <c r="L421" s="21" t="n"/>
     </row>
     <row r="422">
       <c r="B422" s="23" t="n">
@@ -14329,21 +14329,21 @@
       </c>
       <c r="D422" s="24" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E422" s="24" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F422" s="23" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G422" s="25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H422" s="26" t="n"/>
       <c r="I422" s="26">
@@ -14376,12 +14376,12 @@
       <c r="D423" s="17" t="n"/>
       <c r="E423" s="29" t="inlineStr">
         <is>
-          <t>Standard paušální koeficient pro RD městská zástavba 2-3 % z PN</t>
+          <t>TZ B m.10.e: 56.9 t celkem → ~7 kontejnerů 8 m³ (beton/cihly hlavní hmota)</t>
         </is>
       </c>
       <c r="F423" s="17" t="n"/>
       <c r="G423" s="30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H423" s="17" t="n"/>
       <c r="I423" s="17" t="n"/>
@@ -14400,21 +14400,21 @@
       </c>
       <c r="D424" s="24" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E424" s="24" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F424" s="23" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G424" s="25" t="n">
-        <v>56.9</v>
+        <v>1</v>
       </c>
       <c r="H424" s="26" t="n"/>
       <c r="I424" s="26">
@@ -14447,12 +14447,12 @@
       <c r="D425" s="17" t="n"/>
       <c r="E425" s="29" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance: 46+9+0.1+0.1+0.2+1.0 = 56.4 t (round 56.9 vč. drobných)</t>
+          <t>Standard paušální koeficient pro RD městská zástavba 2-3 % z PN</t>
         </is>
       </c>
       <c r="F425" s="17" t="n"/>
       <c r="G425" s="30" t="n">
-        <v>56.9</v>
+        <v>1</v>
       </c>
       <c r="H425" s="17" t="n"/>
       <c r="I425" s="17" t="n"/>
@@ -14461,196 +14461,196 @@
       <c r="L425" s="17" t="n"/>
     </row>
     <row r="426">
-      <c r="B426" s="21" t="n"/>
-      <c r="C426" s="22" t="inlineStr">
+      <c r="B426" s="23" t="n">
+        <v>175</v>
+      </c>
+      <c r="C426" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D426" s="24" t="inlineStr">
+        <is>
+          <t>997013211</t>
+        </is>
+      </c>
+      <c r="E426" s="24" t="inlineStr">
+        <is>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+        </is>
+      </c>
+      <c r="F426" s="23" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G426" s="25" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="H426" s="26" t="n"/>
+      <c r="I426" s="26">
+        <f>IF(H426="",0,G426*H426)</f>
+        <v/>
+      </c>
+      <c r="J426" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K426" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L426" s="5" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" s="17" t="n"/>
+      <c r="C427" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D427" s="17" t="n"/>
+      <c r="E427" s="29" t="inlineStr">
+        <is>
+          <t>TZ B m.10.e bilance: 46+9+0.1+0.1+0.2+1.0 = 56.4 t (round 56.9 vč. drobných)</t>
+        </is>
+      </c>
+      <c r="F427" s="17" t="n"/>
+      <c r="G427" s="30" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="H427" s="17" t="n"/>
+      <c r="I427" s="17" t="n"/>
+      <c r="J427" s="17" t="n"/>
+      <c r="K427" s="17" t="n"/>
+      <c r="L427" s="17" t="n"/>
+    </row>
+    <row r="428">
+      <c r="B428" s="21" t="n"/>
+      <c r="C428" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D426" s="22" t="inlineStr">
+      <c r="D428" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E426" s="22" t="inlineStr">
+      <c r="E428" s="22" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
-      <c r="F426" s="21" t="n"/>
-      <c r="G426" s="21" t="n"/>
-      <c r="H426" s="21" t="n"/>
-      <c r="I426" s="21" t="n"/>
-      <c r="J426" s="21" t="n"/>
-      <c r="K426" s="21" t="n"/>
-      <c r="L426" s="21" t="n"/>
-    </row>
-    <row r="427">
-      <c r="B427" s="23" t="n">
-        <v>175</v>
-      </c>
-      <c r="C427" s="23" t="inlineStr">
+      <c r="F428" s="21" t="n"/>
+      <c r="G428" s="21" t="n"/>
+      <c r="H428" s="21" t="n"/>
+      <c r="I428" s="21" t="n"/>
+      <c r="J428" s="21" t="n"/>
+      <c r="K428" s="21" t="n"/>
+      <c r="L428" s="21" t="n"/>
+    </row>
+    <row r="429">
+      <c r="B429" s="23" t="n">
+        <v>176</v>
+      </c>
+      <c r="C429" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D427" s="24" t="inlineStr">
+      <c r="D429" s="24" t="inlineStr">
         <is>
           <t>030141000</t>
         </is>
       </c>
-      <c r="E427" s="24" t="inlineStr">
+      <c r="E429" s="24" t="inlineStr">
         <is>
           <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
-      <c r="F427" s="23" t="inlineStr">
+      <c r="F429" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G427" s="25" t="n">
+      <c r="G429" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H427" s="26" t="n"/>
-      <c r="I427" s="26">
-        <f>IF(H427="",0,G427*H427)</f>
+      <c r="H429" s="26" t="n"/>
+      <c r="I429" s="26">
+        <f>IF(H429="",0,G429*H429)</f>
         <v/>
       </c>
-      <c r="J427" s="23" t="inlineStr">
+      <c r="J429" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K427" s="32" t="inlineStr">
+      <c r="K429" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L427" s="5" t="inlineStr">
+      <c r="L429" s="5" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
     </row>
-    <row r="428">
-      <c r="B428" s="17" t="n"/>
-      <c r="C428" s="28" t="inlineStr">
+    <row r="430">
+      <c r="B430" s="17" t="n"/>
+      <c r="C430" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D428" s="17" t="n"/>
-      <c r="E428" s="29" t="inlineStr">
+      <c r="D430" s="17" t="n"/>
+      <c r="E430" s="29" t="inlineStr">
         <is>
           <t>2 etapy geodet × 1 kpl</t>
         </is>
       </c>
-      <c r="F428" s="17" t="n"/>
-      <c r="G428" s="30" t="n">
+      <c r="F430" s="17" t="n"/>
+      <c r="G430" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="H428" s="17" t="n"/>
-      <c r="I428" s="17" t="n"/>
-      <c r="J428" s="17" t="n"/>
-      <c r="K428" s="17" t="n"/>
-      <c r="L428" s="17" t="n"/>
-    </row>
-    <row r="429">
-      <c r="B429" s="21" t="n"/>
-      <c r="C429" s="22" t="inlineStr">
+      <c r="H430" s="17" t="n"/>
+      <c r="I430" s="17" t="n"/>
+      <c r="J430" s="17" t="n"/>
+      <c r="K430" s="17" t="n"/>
+      <c r="L430" s="17" t="n"/>
+    </row>
+    <row r="431">
+      <c r="B431" s="21" t="n"/>
+      <c r="C431" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D429" s="22" t="inlineStr">
+      <c r="D431" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E429" s="22" t="inlineStr">
+      <c r="E431" s="22" t="inlineStr">
         <is>
           <t>VRN — Průzkumy</t>
         </is>
       </c>
-      <c r="F429" s="21" t="n"/>
-      <c r="G429" s="21" t="n"/>
-      <c r="H429" s="21" t="n"/>
-      <c r="I429" s="21" t="n"/>
-      <c r="J429" s="21" t="n"/>
-      <c r="K429" s="21" t="n"/>
-      <c r="L429" s="21" t="n"/>
-    </row>
-    <row r="430">
-      <c r="B430" s="23" t="n">
-        <v>176</v>
-      </c>
-      <c r="C430" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D430" s="24" t="inlineStr">
-        <is>
-          <t>030131000</t>
-        </is>
-      </c>
-      <c r="E430" s="24" t="inlineStr">
-        <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
-        </is>
-      </c>
-      <c r="F430" s="23" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G430" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H430" s="26" t="n"/>
-      <c r="I430" s="26">
-        <f>IF(H430="",0,G430*H430)</f>
-        <v/>
-      </c>
-      <c r="J430" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K430" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L430" s="5" t="inlineStr">
-        <is>
-          <t>VRN — Průzkumy</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="B431" s="17" t="n"/>
-      <c r="C431" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D431" s="17" t="n"/>
-      <c r="E431" s="29" t="inlineStr">
-        <is>
-          <t>TZ ARS §3.2.3 — 'při bourání bude proveden mykologický průzkum dřev. trámů (zhlaví)'</t>
-        </is>
-      </c>
-      <c r="F431" s="17" t="n"/>
-      <c r="G431" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H431" s="17" t="n"/>
-      <c r="I431" s="17" t="n"/>
-      <c r="J431" s="17" t="n"/>
-      <c r="K431" s="17" t="n"/>
-      <c r="L431" s="17" t="n"/>
+      <c r="F431" s="21" t="n"/>
+      <c r="G431" s="21" t="n"/>
+      <c r="H431" s="21" t="n"/>
+      <c r="I431" s="21" t="n"/>
+      <c r="J431" s="21" t="n"/>
+      <c r="K431" s="21" t="n"/>
+      <c r="L431" s="21" t="n"/>
     </row>
     <row r="432">
       <c r="B432" s="23" t="n">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="D432" s="24" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E432" s="24" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F432" s="23" t="inlineStr">
@@ -14710,7 +14710,7 @@
       <c r="D433" s="17" t="n"/>
       <c r="E433" s="29" t="inlineStr">
         <is>
-          <t>TZ B m.7.a — 'předběžné ohledání negativní, podrobný průzkum před bouráním'</t>
+          <t>TZ ARS §3.2.3 — 'při bourání bude proveden mykologický průzkum dřev. trámů (zhlaví)'</t>
         </is>
       </c>
       <c r="F433" s="17" t="n"/>
@@ -14724,388 +14724,388 @@
       <c r="L433" s="17" t="n"/>
     </row>
     <row r="434">
-      <c r="B434" s="21" t="n"/>
-      <c r="C434" s="22" t="inlineStr">
+      <c r="B434" s="23" t="n">
+        <v>178</v>
+      </c>
+      <c r="C434" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D434" s="24" t="inlineStr">
+        <is>
+          <t>030133000</t>
+        </is>
+      </c>
+      <c r="E434" s="24" t="inlineStr">
+        <is>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+        </is>
+      </c>
+      <c r="F434" s="23" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G434" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H434" s="26" t="n"/>
+      <c r="I434" s="26">
+        <f>IF(H434="",0,G434*H434)</f>
+        <v/>
+      </c>
+      <c r="J434" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K434" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L434" s="5" t="inlineStr">
+        <is>
+          <t>VRN — Průzkumy</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" s="17" t="n"/>
+      <c r="C435" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D435" s="17" t="n"/>
+      <c r="E435" s="29" t="inlineStr">
+        <is>
+          <t>TZ B m.7.a — 'předběžné ohledání negativní, podrobný průzkum před bouráním'</t>
+        </is>
+      </c>
+      <c r="F435" s="17" t="n"/>
+      <c r="G435" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H435" s="17" t="n"/>
+      <c r="I435" s="17" t="n"/>
+      <c r="J435" s="17" t="n"/>
+      <c r="K435" s="17" t="n"/>
+      <c r="L435" s="17" t="n"/>
+    </row>
+    <row r="436">
+      <c r="B436" s="21" t="n"/>
+      <c r="C436" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D434" s="22" t="inlineStr">
+      <c r="D436" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E434" s="22" t="inlineStr">
+      <c r="E436" s="22" t="inlineStr">
         <is>
           <t>VRN — BOZP</t>
         </is>
       </c>
-      <c r="F434" s="21" t="n"/>
-      <c r="G434" s="21" t="n"/>
-      <c r="H434" s="21" t="n"/>
-      <c r="I434" s="21" t="n"/>
-      <c r="J434" s="21" t="n"/>
-      <c r="K434" s="21" t="n"/>
-      <c r="L434" s="21" t="n"/>
-    </row>
-    <row r="435">
-      <c r="B435" s="23" t="n">
-        <v>178</v>
-      </c>
-      <c r="C435" s="23" t="inlineStr">
+      <c r="F436" s="21" t="n"/>
+      <c r="G436" s="21" t="n"/>
+      <c r="H436" s="21" t="n"/>
+      <c r="I436" s="21" t="n"/>
+      <c r="J436" s="21" t="n"/>
+      <c r="K436" s="21" t="n"/>
+      <c r="L436" s="21" t="n"/>
+    </row>
+    <row r="437">
+      <c r="B437" s="23" t="n">
+        <v>179</v>
+      </c>
+      <c r="C437" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D435" s="24" t="inlineStr">
+      <c r="D437" s="24" t="inlineStr">
         <is>
           <t>030091000</t>
         </is>
       </c>
-      <c r="E435" s="24" t="inlineStr">
+      <c r="E437" s="24" t="inlineStr">
         <is>
           <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
-      <c r="F435" s="23" t="inlineStr">
+      <c r="F437" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G435" s="25" t="n">
+      <c r="G437" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H435" s="26" t="n"/>
-      <c r="I435" s="26">
-        <f>IF(H435="",0,G435*H435)</f>
+      <c r="H437" s="26" t="n"/>
+      <c r="I437" s="26">
+        <f>IF(H437="",0,G437*H437)</f>
         <v/>
       </c>
-      <c r="J435" s="23" t="inlineStr">
+      <c r="J437" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K435" s="32" t="inlineStr">
+      <c r="K437" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L435" s="5" t="inlineStr">
+      <c r="L437" s="5" t="inlineStr">
         <is>
           <t>VRN — BOZP</t>
         </is>
       </c>
     </row>
-    <row r="436">
-      <c r="B436" s="17" t="n"/>
-      <c r="C436" s="28" t="inlineStr">
+    <row r="438">
+      <c r="B438" s="17" t="n"/>
+      <c r="C438" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D436" s="17" t="n"/>
-      <c r="E436" s="29" t="inlineStr">
+      <c r="D438" s="17" t="n"/>
+      <c r="E438" s="29" t="inlineStr">
         <is>
           <t>realizace ~8 měs</t>
         </is>
       </c>
-      <c r="F436" s="17" t="n"/>
-      <c r="G436" s="30" t="n">
+      <c r="F438" s="17" t="n"/>
+      <c r="G438" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H436" s="17" t="n"/>
-      <c r="I436" s="17" t="n"/>
-      <c r="J436" s="17" t="n"/>
-      <c r="K436" s="17" t="n"/>
-      <c r="L436" s="17" t="n"/>
-    </row>
-    <row r="437">
-      <c r="B437" s="21" t="n"/>
-      <c r="C437" s="22" t="inlineStr">
+      <c r="H438" s="17" t="n"/>
+      <c r="I438" s="17" t="n"/>
+      <c r="J438" s="17" t="n"/>
+      <c r="K438" s="17" t="n"/>
+      <c r="L438" s="17" t="n"/>
+    </row>
+    <row r="439">
+      <c r="B439" s="21" t="n"/>
+      <c r="C439" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D437" s="22" t="inlineStr">
+      <c r="D439" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E437" s="22" t="inlineStr">
+      <c r="E439" s="22" t="inlineStr">
         <is>
           <t>VRN — Dokumentace</t>
         </is>
       </c>
-      <c r="F437" s="21" t="n"/>
-      <c r="G437" s="21" t="n"/>
-      <c r="H437" s="21" t="n"/>
-      <c r="I437" s="21" t="n"/>
-      <c r="J437" s="21" t="n"/>
-      <c r="K437" s="21" t="n"/>
-      <c r="L437" s="21" t="n"/>
-    </row>
-    <row r="438">
-      <c r="B438" s="23" t="n">
-        <v>179</v>
-      </c>
-      <c r="C438" s="23" t="inlineStr">
+      <c r="F439" s="21" t="n"/>
+      <c r="G439" s="21" t="n"/>
+      <c r="H439" s="21" t="n"/>
+      <c r="I439" s="21" t="n"/>
+      <c r="J439" s="21" t="n"/>
+      <c r="K439" s="21" t="n"/>
+      <c r="L439" s="21" t="n"/>
+    </row>
+    <row r="440">
+      <c r="B440" s="23" t="n">
+        <v>180</v>
+      </c>
+      <c r="C440" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D438" s="24" t="inlineStr">
+      <c r="D440" s="24" t="inlineStr">
         <is>
           <t>030151000</t>
         </is>
       </c>
-      <c r="E438" s="24" t="inlineStr">
+      <c r="E440" s="24" t="inlineStr">
         <is>
           <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
-      <c r="F438" s="23" t="inlineStr">
+      <c r="F440" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G438" s="25" t="n">
+      <c r="G440" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H438" s="26" t="n"/>
-      <c r="I438" s="26">
-        <f>IF(H438="",0,G438*H438)</f>
+      <c r="H440" s="26" t="n"/>
+      <c r="I440" s="26">
+        <f>IF(H440="",0,G440*H440)</f>
         <v/>
       </c>
-      <c r="J438" s="23" t="inlineStr">
+      <c r="J440" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K438" s="32" t="inlineStr">
+      <c r="K440" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L438" s="5" t="inlineStr">
+      <c r="L440" s="5" t="inlineStr">
         <is>
           <t>VRN — Dokumentace</t>
         </is>
       </c>
     </row>
-    <row r="439">
-      <c r="B439" s="17" t="n"/>
-      <c r="C439" s="28" t="inlineStr">
+    <row r="441">
+      <c r="B441" s="17" t="n"/>
+      <c r="C441" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D439" s="17" t="n"/>
-      <c r="E439" s="29" t="inlineStr">
+      <c r="D441" s="17" t="n"/>
+      <c r="E441" s="29" t="inlineStr">
         <is>
           <t>Standard — DSP pro kolaudaci</t>
         </is>
       </c>
-      <c r="F439" s="17" t="n"/>
-      <c r="G439" s="30" t="n">
+      <c r="F441" s="17" t="n"/>
+      <c r="G441" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H439" s="17" t="n"/>
-      <c r="I439" s="17" t="n"/>
-      <c r="J439" s="17" t="n"/>
-      <c r="K439" s="17" t="n"/>
-      <c r="L439" s="17" t="n"/>
-    </row>
-    <row r="440">
-      <c r="B440" s="21" t="n"/>
-      <c r="C440" s="22" t="inlineStr">
+      <c r="H441" s="17" t="n"/>
+      <c r="I441" s="17" t="n"/>
+      <c r="J441" s="17" t="n"/>
+      <c r="K441" s="17" t="n"/>
+      <c r="L441" s="17" t="n"/>
+    </row>
+    <row r="442">
+      <c r="B442" s="21" t="n"/>
+      <c r="C442" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D440" s="22" t="inlineStr">
+      <c r="D442" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E440" s="22" t="inlineStr">
+      <c r="E442" s="22" t="inlineStr">
         <is>
           <t>VRN — Kolaudace</t>
         </is>
       </c>
-      <c r="F440" s="21" t="n"/>
-      <c r="G440" s="21" t="n"/>
-      <c r="H440" s="21" t="n"/>
-      <c r="I440" s="21" t="n"/>
-      <c r="J440" s="21" t="n"/>
-      <c r="K440" s="21" t="n"/>
-      <c r="L440" s="21" t="n"/>
-    </row>
-    <row r="441">
-      <c r="B441" s="23" t="n">
-        <v>180</v>
-      </c>
-      <c r="C441" s="23" t="inlineStr">
+      <c r="F442" s="21" t="n"/>
+      <c r="G442" s="21" t="n"/>
+      <c r="H442" s="21" t="n"/>
+      <c r="I442" s="21" t="n"/>
+      <c r="J442" s="21" t="n"/>
+      <c r="K442" s="21" t="n"/>
+      <c r="L442" s="21" t="n"/>
+    </row>
+    <row r="443">
+      <c r="B443" s="23" t="n">
+        <v>181</v>
+      </c>
+      <c r="C443" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D441" s="24" t="inlineStr">
+      <c r="D443" s="24" t="inlineStr">
         <is>
           <t>030171000</t>
         </is>
       </c>
-      <c r="E441" s="24" t="inlineStr">
+      <c r="E443" s="24" t="inlineStr">
         <is>
           <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
-      <c r="F441" s="23" t="inlineStr">
+      <c r="F443" s="23" t="inlineStr">
         <is>
           <t>paušál</t>
         </is>
       </c>
-      <c r="G441" s="25" t="n">
+      <c r="G443" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H441" s="26" t="n"/>
-      <c r="I441" s="26">
-        <f>IF(H441="",0,G441*H441)</f>
+      <c r="H443" s="26" t="n"/>
+      <c r="I443" s="26">
+        <f>IF(H443="",0,G443*H443)</f>
         <v/>
       </c>
-      <c r="J441" s="23" t="inlineStr">
+      <c r="J443" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K441" s="32" t="inlineStr">
+      <c r="K443" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L441" s="5" t="inlineStr">
+      <c r="L443" s="5" t="inlineStr">
         <is>
           <t>VRN — Kolaudace</t>
         </is>
       </c>
     </row>
-    <row r="442">
-      <c r="B442" s="17" t="n"/>
-      <c r="C442" s="28" t="inlineStr">
+    <row r="444">
+      <c r="B444" s="17" t="n"/>
+      <c r="C444" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D442" s="17" t="n"/>
-      <c r="E442" s="29" t="inlineStr">
+      <c r="D444" s="17" t="n"/>
+      <c r="E444" s="29" t="inlineStr">
         <is>
           <t>Standard — paušál kolaudace</t>
         </is>
       </c>
-      <c r="F442" s="17" t="n"/>
-      <c r="G442" s="30" t="n">
+      <c r="F444" s="17" t="n"/>
+      <c r="G444" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H442" s="17" t="n"/>
-      <c r="I442" s="17" t="n"/>
-      <c r="J442" s="17" t="n"/>
-      <c r="K442" s="17" t="n"/>
-      <c r="L442" s="17" t="n"/>
-    </row>
-    <row r="443">
-      <c r="B443" s="21" t="n"/>
-      <c r="C443" s="22" t="inlineStr">
+      <c r="H444" s="17" t="n"/>
+      <c r="I444" s="17" t="n"/>
+      <c r="J444" s="17" t="n"/>
+      <c r="K444" s="17" t="n"/>
+      <c r="L444" s="17" t="n"/>
+    </row>
+    <row r="445">
+      <c r="B445" s="21" t="n"/>
+      <c r="C445" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D443" s="22" t="inlineStr">
+      <c r="D445" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E443" s="22" t="inlineStr">
+      <c r="E445" s="22" t="inlineStr">
         <is>
           <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
-      <c r="F443" s="21" t="n"/>
-      <c r="G443" s="21" t="n"/>
-      <c r="H443" s="21" t="n"/>
-      <c r="I443" s="21" t="n"/>
-      <c r="J443" s="21" t="n"/>
-      <c r="K443" s="21" t="n"/>
-      <c r="L443" s="21" t="n"/>
-    </row>
-    <row r="444">
-      <c r="B444" s="23" t="n">
-        <v>181</v>
-      </c>
-      <c r="C444" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D444" s="24" t="inlineStr">
-        <is>
-          <t>030081000</t>
-        </is>
-      </c>
-      <c r="E444" s="24" t="inlineStr">
-        <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
-        </is>
-      </c>
-      <c r="F444" s="23" t="inlineStr">
-        <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G444" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H444" s="26" t="n"/>
-      <c r="I444" s="26">
-        <f>IF(H444="",0,G444*H444)</f>
-        <v/>
-      </c>
-      <c r="J444" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K444" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L444" s="5" t="inlineStr">
-        <is>
-          <t>VRN — Pojištění + zábory</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="B445" s="17" t="n"/>
-      <c r="C445" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D445" s="17" t="n"/>
-      <c r="E445" s="29" t="inlineStr">
-        <is>
-          <t>Standard pojistná sazba 0.3-0.5 % z přímých nákladů</t>
-        </is>
-      </c>
-      <c r="F445" s="17" t="n"/>
-      <c r="G445" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H445" s="17" t="n"/>
-      <c r="I445" s="17" t="n"/>
-      <c r="J445" s="17" t="n"/>
-      <c r="K445" s="17" t="n"/>
-      <c r="L445" s="17" t="n"/>
+      <c r="F445" s="21" t="n"/>
+      <c r="G445" s="21" t="n"/>
+      <c r="H445" s="21" t="n"/>
+      <c r="I445" s="21" t="n"/>
+      <c r="J445" s="21" t="n"/>
+      <c r="K445" s="21" t="n"/>
+      <c r="L445" s="21" t="n"/>
     </row>
     <row r="446">
       <c r="B446" s="23" t="n">
@@ -15118,17 +15118,17 @@
       </c>
       <c r="D446" s="24" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E446" s="24" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F446" s="23" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G446" s="25" t="n">
@@ -15165,7 +15165,7 @@
       <c r="D447" s="17" t="n"/>
       <c r="E447" s="29" t="inlineStr">
         <is>
-          <t>Řadová zástavba úzká ulice — opakované krátkodobé zábory cumulative ~30 dnů</t>
+          <t>Standard pojistná sazba 0.3-0.5 % z přímých nákladů</t>
         </is>
       </c>
       <c r="F447" s="17" t="n"/>
@@ -15179,100 +15179,171 @@
       <c r="L447" s="17" t="n"/>
     </row>
     <row r="448">
-      <c r="B448" s="21" t="n"/>
-      <c r="C448" s="22" t="inlineStr">
+      <c r="B448" s="23" t="n">
+        <v>183</v>
+      </c>
+      <c r="C448" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D448" s="24" t="inlineStr">
+        <is>
+          <t>030083000</t>
+        </is>
+      </c>
+      <c r="E448" s="24" t="inlineStr">
+        <is>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+        </is>
+      </c>
+      <c r="F448" s="23" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G448" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H448" s="26" t="n"/>
+      <c r="I448" s="26">
+        <f>IF(H448="",0,G448*H448)</f>
+        <v/>
+      </c>
+      <c r="J448" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K448" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L448" s="5" t="inlineStr">
+        <is>
+          <t>VRN — Pojištění + zábory</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" s="17" t="n"/>
+      <c r="C449" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D449" s="17" t="n"/>
+      <c r="E449" s="29" t="inlineStr">
+        <is>
+          <t>Řadová zástavba úzká ulice — opakované krátkodobé zábory cumulative ~30 dnů</t>
+        </is>
+      </c>
+      <c r="F449" s="17" t="n"/>
+      <c r="G449" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H449" s="17" t="n"/>
+      <c r="I449" s="17" t="n"/>
+      <c r="J449" s="17" t="n"/>
+      <c r="K449" s="17" t="n"/>
+      <c r="L449" s="17" t="n"/>
+    </row>
+    <row r="450">
+      <c r="B450" s="21" t="n"/>
+      <c r="C450" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D448" s="22" t="inlineStr">
+      <c r="D450" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E448" s="22" t="inlineStr">
+      <c r="E450" s="22" t="inlineStr">
         <is>
           <t>VRN — Revize</t>
         </is>
       </c>
-      <c r="F448" s="21" t="n"/>
-      <c r="G448" s="21" t="n"/>
-      <c r="H448" s="21" t="n"/>
-      <c r="I448" s="21" t="n"/>
-      <c r="J448" s="21" t="n"/>
-      <c r="K448" s="21" t="n"/>
-      <c r="L448" s="21" t="n"/>
-    </row>
-    <row r="449">
-      <c r="B449" s="23" t="n">
-        <v>183</v>
-      </c>
-      <c r="C449" s="23" t="inlineStr">
+      <c r="F450" s="21" t="n"/>
+      <c r="G450" s="21" t="n"/>
+      <c r="H450" s="21" t="n"/>
+      <c r="I450" s="21" t="n"/>
+      <c r="J450" s="21" t="n"/>
+      <c r="K450" s="21" t="n"/>
+      <c r="L450" s="21" t="n"/>
+    </row>
+    <row r="451">
+      <c r="B451" s="23" t="n">
+        <v>184</v>
+      </c>
+      <c r="C451" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D449" s="24" t="inlineStr">
+      <c r="D451" s="24" t="inlineStr">
         <is>
           <t>030161000</t>
         </is>
       </c>
-      <c r="E449" s="24" t="inlineStr">
+      <c r="E451" s="24" t="inlineStr">
         <is>
           <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
-      <c r="F449" s="23" t="inlineStr">
+      <c r="F451" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G449" s="25" t="n">
+      <c r="G451" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H449" s="26" t="n"/>
-      <c r="I449" s="26">
-        <f>IF(H449="",0,G449*H449)</f>
+      <c r="H451" s="26" t="n"/>
+      <c r="I451" s="26">
+        <f>IF(H451="",0,G451*H451)</f>
         <v/>
       </c>
-      <c r="J449" s="23" t="inlineStr">
+      <c r="J451" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K449" s="32" t="inlineStr">
+      <c r="K451" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L449" s="5" t="inlineStr">
+      <c r="L451" s="5" t="inlineStr">
         <is>
           <t>VRN — Revize</t>
         </is>
       </c>
     </row>
-    <row r="450">
-      <c r="B450" s="17" t="n"/>
-      <c r="C450" s="28" t="inlineStr">
+    <row r="452">
+      <c r="B452" s="17" t="n"/>
+      <c r="C452" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D450" s="17" t="n"/>
-      <c r="E450" s="29" t="inlineStr">
+      <c r="D452" s="17" t="n"/>
+      <c r="E452" s="29" t="inlineStr">
         <is>
           <t>TZ PBŘ dům — vnější hydrant DN min. 80, vzdálenost 100 m</t>
         </is>
       </c>
-      <c r="F450" s="17" t="n"/>
-      <c r="G450" s="30" t="n">
+      <c r="F452" s="17" t="n"/>
+      <c r="G452" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H450" s="17" t="n"/>
-      <c r="I450" s="17" t="n"/>
-      <c r="J450" s="17" t="n"/>
-      <c r="K450" s="17" t="n"/>
-      <c r="L450" s="17" t="n"/>
+      <c r="H452" s="17" t="n"/>
+      <c r="I452" s="17" t="n"/>
+      <c r="J452" s="17" t="n"/>
+      <c r="K452" s="17" t="n"/>
+      <c r="L452" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -17969,7 +18040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H234"/>
+  <dimension ref="B2:H235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -18048,7 +18119,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
@@ -18058,7 +18129,7 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13">
@@ -25205,6 +25276,43 @@
       <c r="H234" s="24" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" s="24" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.017</t>
+        </is>
+      </c>
+      <c r="C235" s="24" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="D235" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="E235" s="24" t="inlineStr">
+        <is>
+          <t>762085112</t>
+        </is>
+      </c>
+      <c r="F235" s="24" t="inlineStr">
+        <is>
+          <t>762085</t>
+        </is>
+      </c>
+      <c r="G235" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 </t>
+        </is>
+      </c>
+      <c r="H235" s="24" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
     </row>
@@ -25230,7 +25338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N215"/>
+  <dimension ref="B2:N216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -34610,6 +34718,51 @@
       </c>
       <c r="N215" s="24" t="inlineStr"/>
     </row>
+    <row r="216">
+      <c r="B216" s="24" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV5.017</t>
+        </is>
+      </c>
+      <c r="C216" s="24" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
+        </is>
+      </c>
+      <c r="D216" s="24" t="inlineStr">
+        <is>
+          <t>Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spoje</t>
+        </is>
+      </c>
+      <c r="E216" s="24" t="inlineStr">
+        <is>
+          <t>762085112</t>
+        </is>
+      </c>
+      <c r="F216" s="24" t="inlineStr"/>
+      <c r="G216" s="24" t="inlineStr">
+        <is>
+          <t>762085</t>
+        </is>
+      </c>
+      <c r="H216" s="24" t="inlineStr">
+        <is>
+          <t>matched_catalog</t>
+        </is>
+      </c>
+      <c r="I216" s="35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J216" s="32" t="inlineStr"/>
+      <c r="K216" s="24" t="inlineStr"/>
+      <c r="L216" s="24" t="inlineStr"/>
+      <c r="M216" s="24" t="inlineStr">
+        <is>
+          <t>KROS 762085112 — Montáž svorníků/šroubů tesařských spojů délky přes 150 do 300 mm (MJ ks). Materiál samostatně (atomic): tyč závitová Pz 4.6 M12 31197004 (m), matice DIN 934-8 M12 3111006 (100 ks), po</t>
+        </is>
+      </c>
+      <c r="N216" s="24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
@@ -20248,7 +20248,7 @@
     <row r="61">
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV71.001</t>
+          <t>260219_dum.PSV71.101</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
@@ -20281,7 +20281,7 @@
     <row r="62">
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV71.002</t>
+          <t>260219_dum.PSV71.102</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -20347,7 +20347,7 @@
     <row r="64">
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.001</t>
+          <t>260219_dum.PSV76.101</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="65">
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.102</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -20413,7 +20413,7 @@
     <row r="66">
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.PSV76.103</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -20446,7 +20446,7 @@
     <row r="67">
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.004</t>
+          <t>260219_dum.PSV76.104</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -20479,7 +20479,7 @@
     <row r="68">
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.001</t>
+          <t>260219_dum.PSV76.201</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -20512,7 +20512,7 @@
     <row r="69">
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.202</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -23083,7 +23083,7 @@
     <row r="150">
       <c r="B150" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.PSV76.203</t>
         </is>
       </c>
       <c r="C150" s="24" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="151">
       <c r="B151" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.004</t>
+          <t>260219_dum.PSV76.204</t>
         </is>
       </c>
       <c r="C151" s="24" t="inlineStr">
@@ -23149,7 +23149,7 @@
     <row r="152">
       <c r="B152" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.001</t>
+          <t>260219_dum.PSV76.301</t>
         </is>
       </c>
       <c r="C152" s="24" t="inlineStr">
@@ -23182,7 +23182,7 @@
     <row r="153">
       <c r="B153" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.302</t>
         </is>
       </c>
       <c r="C153" s="24" t="inlineStr">
@@ -24601,7 +24601,7 @@
     <row r="196">
       <c r="B196" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.101</t>
         </is>
       </c>
       <c r="C196" s="24" t="inlineStr">
@@ -24634,7 +24634,7 @@
     <row r="197">
       <c r="B197" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.201</t>
         </is>
       </c>
       <c r="C197" s="24" t="inlineStr">
@@ -24667,7 +24667,7 @@
     <row r="198">
       <c r="B198" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.301</t>
         </is>
       </c>
       <c r="C198" s="24" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="199">
       <c r="B199" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.002</t>
+          <t>260219_dum.VRN.302</t>
         </is>
       </c>
       <c r="C199" s="24" t="inlineStr">
@@ -24733,7 +24733,7 @@
     <row r="200">
       <c r="B200" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.401</t>
         </is>
       </c>
       <c r="C200" s="24" t="inlineStr">
@@ -24766,7 +24766,7 @@
     <row r="201">
       <c r="B201" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.002</t>
+          <t>260219_dum.VRN.402</t>
         </is>
       </c>
       <c r="C201" s="24" t="inlineStr">
@@ -24799,7 +24799,7 @@
     <row r="202">
       <c r="B202" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.501</t>
         </is>
       </c>
       <c r="C202" s="24" t="inlineStr">
@@ -24832,7 +24832,7 @@
     <row r="203">
       <c r="B203" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.601</t>
         </is>
       </c>
       <c r="C203" s="24" t="inlineStr">
@@ -24865,7 +24865,7 @@
     <row r="204">
       <c r="B204" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.701</t>
         </is>
       </c>
       <c r="C204" s="24" t="inlineStr">
@@ -24898,7 +24898,7 @@
     <row r="205">
       <c r="B205" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.801</t>
         </is>
       </c>
       <c r="C205" s="24" t="inlineStr">
@@ -24931,7 +24931,7 @@
     <row r="206">
       <c r="B206" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.002</t>
+          <t>260219_dum.VRN.102</t>
         </is>
       </c>
       <c r="C206" s="24" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="207">
       <c r="B207" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.003</t>
+          <t>260219_dum.VRN.103</t>
         </is>
       </c>
       <c r="C207" s="24" t="inlineStr">
@@ -25063,7 +25063,7 @@
     <row r="210">
       <c r="B210" s="24" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.001</t>
+          <t>260217_sklad.VRN.101</t>
         </is>
       </c>
       <c r="C210" s="24" t="inlineStr">
@@ -25096,7 +25096,7 @@
     <row r="211">
       <c r="B211" s="24" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.001</t>
+          <t>260217_sklad.VRN.201</t>
         </is>
       </c>
       <c r="C211" s="24" t="inlineStr">
@@ -31016,7 +31016,7 @@
     <row r="105">
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV71.001</t>
+          <t>260219_dum.PSV71.101</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -31073,7 +31073,7 @@
     <row r="106">
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV71.002</t>
+          <t>260219_dum.PSV71.102</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
@@ -31548,7 +31548,7 @@
     <row r="117">
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.001</t>
+          <t>260219_dum.PSV76.101</t>
         </is>
       </c>
       <c r="C117" s="24" t="inlineStr">
@@ -31597,7 +31597,7 @@
     <row r="118">
       <c r="B118" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.102</t>
         </is>
       </c>
       <c r="C118" s="24" t="inlineStr">
@@ -31646,7 +31646,7 @@
     <row r="119">
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.PSV76.103</t>
         </is>
       </c>
       <c r="C119" s="24" t="inlineStr">
@@ -31695,7 +31695,7 @@
     <row r="120">
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.004</t>
+          <t>260219_dum.PSV76.104</t>
         </is>
       </c>
       <c r="C120" s="24" t="inlineStr">
@@ -31744,7 +31744,7 @@
     <row r="121">
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.001</t>
+          <t>260219_dum.PSV76.201</t>
         </is>
       </c>
       <c r="C121" s="24" t="inlineStr">
@@ -31793,7 +31793,7 @@
     <row r="122">
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.202</t>
         </is>
       </c>
       <c r="C122" s="24" t="inlineStr">
@@ -31842,7 +31842,7 @@
     <row r="123">
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.003</t>
+          <t>260219_dum.PSV76.203</t>
         </is>
       </c>
       <c r="C123" s="24" t="inlineStr">
@@ -31883,7 +31883,7 @@
     <row r="124">
       <c r="B124" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.004</t>
+          <t>260219_dum.PSV76.204</t>
         </is>
       </c>
       <c r="C124" s="24" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="125">
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.001</t>
+          <t>260219_dum.PSV76.301</t>
         </is>
       </c>
       <c r="C125" s="24" t="inlineStr">
@@ -31965,7 +31965,7 @@
     <row r="126">
       <c r="B126" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.PSV76.002</t>
+          <t>260219_dum.PSV76.302</t>
         </is>
       </c>
       <c r="C126" s="24" t="inlineStr">
@@ -33985,7 +33985,7 @@
     <row r="174">
       <c r="B174" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.101</t>
         </is>
       </c>
       <c r="C174" s="24" t="inlineStr">
@@ -34026,7 +34026,7 @@
     <row r="175">
       <c r="B175" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.201</t>
         </is>
       </c>
       <c r="C175" s="24" t="inlineStr">
@@ -34067,7 +34067,7 @@
     <row r="176">
       <c r="B176" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.301</t>
         </is>
       </c>
       <c r="C176" s="24" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="177">
       <c r="B177" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.002</t>
+          <t>260219_dum.VRN.302</t>
         </is>
       </c>
       <c r="C177" s="24" t="inlineStr">
@@ -34149,7 +34149,7 @@
     <row r="178">
       <c r="B178" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.401</t>
         </is>
       </c>
       <c r="C178" s="24" t="inlineStr">
@@ -34190,7 +34190,7 @@
     <row r="179">
       <c r="B179" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.002</t>
+          <t>260219_dum.VRN.402</t>
         </is>
       </c>
       <c r="C179" s="24" t="inlineStr">
@@ -34231,7 +34231,7 @@
     <row r="180">
       <c r="B180" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.501</t>
         </is>
       </c>
       <c r="C180" s="24" t="inlineStr">
@@ -34272,7 +34272,7 @@
     <row r="181">
       <c r="B181" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.601</t>
         </is>
       </c>
       <c r="C181" s="24" t="inlineStr">
@@ -34313,7 +34313,7 @@
     <row r="182">
       <c r="B182" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.701</t>
         </is>
       </c>
       <c r="C182" s="24" t="inlineStr">
@@ -34354,7 +34354,7 @@
     <row r="183">
       <c r="B183" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.001</t>
+          <t>260219_dum.VRN.801</t>
         </is>
       </c>
       <c r="C183" s="24" t="inlineStr">
@@ -34395,7 +34395,7 @@
     <row r="184">
       <c r="B184" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.002</t>
+          <t>260219_dum.VRN.102</t>
         </is>
       </c>
       <c r="C184" s="24" t="inlineStr">
@@ -34436,7 +34436,7 @@
     <row r="185">
       <c r="B185" s="24" t="inlineStr">
         <is>
-          <t>260219_dum.VRN.003</t>
+          <t>260219_dum.VRN.103</t>
         </is>
       </c>
       <c r="C185" s="24" t="inlineStr">
@@ -34559,7 +34559,7 @@
     <row r="188">
       <c r="B188" s="24" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.001</t>
+          <t>260217_sklad.VRN.101</t>
         </is>
       </c>
       <c r="C188" s="24" t="inlineStr">
@@ -34600,7 +34600,7 @@
     <row r="189">
       <c r="B189" s="24" t="inlineStr">
         <is>
-          <t>260217_sklad.VRN.001</t>
+          <t>260217_sklad.VRN.201</t>
         </is>
       </c>
       <c r="C189" s="24" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <f>SUM('SO_260217_Sklad'!I34:I102)</f>
+        <f>SUM('SO_260217_Sklad'!I34:I106)</f>
         <v/>
       </c>
       <c r="E15" s="7">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="G228" s="25" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H228" s="26" t="n"/>
       <c r="I228" s="26">
@@ -7680,13 +7680,14 @@
         </is>
       </c>
       <c r="D229" s="17" t="n"/>
-      <c r="E229" s="29">
-        <f> obvod 38.7 m × výška soklu 0.6 m ≈ 23 m²</f>
-        <v/>
+      <c r="E229" s="29" t="inlineStr">
+        <is>
+          <t>obvod 38.7 m × výška soklu 0.6 m × řadovka 0.7 (volný obvod) = 16.3 ≈ 16 m² (OVĚŘIT)</t>
+        </is>
       </c>
       <c r="F229" s="17" t="n"/>
       <c r="G229" s="30" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H229" s="17" t="n"/>
       <c r="I229" s="17" t="n"/>
@@ -15953,7 +15954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L103"/>
+  <dimension ref="B2:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -16114,7 +16115,7 @@
         </is>
       </c>
       <c r="D16" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C16)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C16)</f>
         <v/>
       </c>
     </row>
@@ -16126,7 +16127,7 @@
         </is>
       </c>
       <c r="D17" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C17)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C17)</f>
         <v/>
       </c>
     </row>
@@ -16138,7 +16139,7 @@
         </is>
       </c>
       <c r="D18" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C18)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C18)</f>
         <v/>
       </c>
     </row>
@@ -16150,7 +16151,7 @@
         </is>
       </c>
       <c r="D19" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C19)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C19)</f>
         <v/>
       </c>
     </row>
@@ -16162,7 +16163,7 @@
         </is>
       </c>
       <c r="D20" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C20)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C20)</f>
         <v/>
       </c>
     </row>
@@ -16174,7 +16175,7 @@
         </is>
       </c>
       <c r="D21" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C21)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C21)</f>
         <v/>
       </c>
     </row>
@@ -16186,7 +16187,7 @@
         </is>
       </c>
       <c r="D22" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C22)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C22)</f>
         <v/>
       </c>
     </row>
@@ -16198,7 +16199,7 @@
         </is>
       </c>
       <c r="D23" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C23)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C23)</f>
         <v/>
       </c>
     </row>
@@ -16210,7 +16211,7 @@
         </is>
       </c>
       <c r="D24" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C24)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C24)</f>
         <v/>
       </c>
     </row>
@@ -16222,7 +16223,7 @@
         </is>
       </c>
       <c r="D25" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C25)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C25)</f>
         <v/>
       </c>
     </row>
@@ -16234,7 +16235,7 @@
         </is>
       </c>
       <c r="D26" s="7">
-        <f>SUMIFS(I32:I103,L32:L103,C26)</f>
+        <f>SUMIFS(I32:I107,L32:L107,C26)</f>
         <v/>
       </c>
     </row>
@@ -16673,7 +16674,7 @@
         </is>
       </c>
       <c r="G42" s="25" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="H42" s="26" t="n"/>
       <c r="I42" s="26">
@@ -16706,12 +16707,12 @@
       <c r="D43" s="17" t="n"/>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>podlaha sklad 21.2 m² × 0.15 m štěrku</t>
+          <t>podlaha sklad 17.6 m² (legenda místností) × 0.15 m podkladní kamenná drť</t>
         </is>
       </c>
       <c r="F43" s="17" t="n"/>
       <c r="G43" s="30" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="H43" s="17" t="n"/>
       <c r="I43" s="17" t="n"/>
@@ -17115,7 +17116,7 @@
         </is>
       </c>
       <c r="G55" s="25" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="H55" s="26" t="n"/>
       <c r="I55" s="26">
@@ -17148,12 +17149,12 @@
       <c r="D56" s="17" t="n"/>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>21.2 × 0.10 = 2.12</t>
+          <t>podlaha sklad 17.6 m² (legenda) × 0.10 m kladecí kamenná drť</t>
         </is>
       </c>
       <c r="F56" s="17" t="n"/>
       <c r="G56" s="30" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="H56" s="17" t="n"/>
       <c r="I56" s="17" t="n"/>
@@ -17471,170 +17472,161 @@
       <c r="L65" s="17" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="21" t="n"/>
-      <c r="C66" s="22" t="inlineStr">
+      <c r="B66" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr"/>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G66" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H66" s="26" t="n"/>
+      <c r="I66" s="26">
+        <f>IF(H66="",0,G66*H66)</f>
+        <v/>
+      </c>
+      <c r="J66" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K66" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="17" t="n"/>
+      <c r="C67" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="n"/>
+      <c r="E67" s="29">
+        <f> S04 6.35×3.0 ≈19 + S03a 2×3.6×~2.0 ≈14 = 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="F67" s="17" t="n"/>
+      <c r="G67" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H67" s="17" t="n"/>
+      <c r="I67" s="17" t="n"/>
+      <c r="J67" s="17" t="n"/>
+      <c r="K67" s="17" t="n"/>
+      <c r="L67" s="17" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr"/>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G68" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="H68" s="26" t="n"/>
+      <c r="I68" s="26">
+        <f>IF(H68="",0,G68*H68)</f>
+        <v/>
+      </c>
+      <c r="J68" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K68" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="17" t="n"/>
+      <c r="C69" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="n"/>
+      <c r="E69" s="29">
+        <f> plocha stěn pod terénem 33 m² (řez D.1.1.03/04, OVĚŘIT)</f>
+        <v/>
+      </c>
+      <c r="F69" s="17" t="n"/>
+      <c r="G69" s="30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H69" s="17" t="n"/>
+      <c r="I69" s="17" t="n"/>
+      <c r="J69" s="17" t="n"/>
+      <c r="K69" s="17" t="n"/>
+      <c r="L69" s="17" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="21" t="n"/>
+      <c r="C70" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D66" s="22" t="inlineStr">
+      <c r="D70" s="22" t="inlineStr">
         <is>
           <t>HSV-4</t>
         </is>
       </c>
-      <c r="E66" s="22" t="inlineStr">
+      <c r="E70" s="22" t="inlineStr">
         <is>
           <t>HSV-4 Vodorovné</t>
         </is>
       </c>
-      <c r="F66" s="21" t="n"/>
-      <c r="G66" s="21" t="n"/>
-      <c r="H66" s="21" t="n"/>
-      <c r="I66" s="21" t="n"/>
-      <c r="J66" s="21" t="n"/>
-      <c r="K66" s="21" t="n"/>
-      <c r="L66" s="21" t="n"/>
-    </row>
-    <row r="67">
-      <c r="B67" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="C67" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D67" s="24" t="inlineStr">
-        <is>
-          <t>762341110</t>
-        </is>
-      </c>
-      <c r="E67" s="24" t="inlineStr">
-        <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
-        </is>
-      </c>
-      <c r="F67" s="23" t="inlineStr">
-        <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G67" s="25" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="H67" s="26" t="n"/>
-      <c r="I67" s="26">
-        <f>IF(H67="",0,G67*H67)</f>
-        <v/>
-      </c>
-      <c r="J67" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="17" t="n"/>
-      <c r="C68" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="n"/>
-      <c r="E68" s="29" t="inlineStr">
-        <is>
-          <t>rozpon 3.34 × počet stropnic (6.35/0.625 = 10) = ~10 ks × 3.34 = 33.4</t>
-        </is>
-      </c>
-      <c r="F68" s="17" t="n"/>
-      <c r="G68" s="30" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="H68" s="17" t="n"/>
-      <c r="I68" s="17" t="n"/>
-      <c r="J68" s="17" t="n"/>
-      <c r="K68" s="17" t="n"/>
-      <c r="L68" s="17" t="n"/>
-    </row>
-    <row r="69">
-      <c r="B69" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="C69" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D69" s="24" t="inlineStr">
-        <is>
-          <t>762331110</t>
-        </is>
-      </c>
-      <c r="E69" s="24" t="inlineStr">
-        <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
-        </is>
-      </c>
-      <c r="F69" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G69" s="25" t="n">
-        <v>21.209</v>
-      </c>
-      <c r="H69" s="26" t="n"/>
-      <c r="I69" s="26">
-        <f>IF(H69="",0,G69*H69)</f>
-        <v/>
-      </c>
-      <c r="J69" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
-        </is>
-      </c>
-      <c r="L69" s="5" t="inlineStr">
-        <is>
-          <t>HSV-4 Vodorovné</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="17" t="n"/>
-      <c r="C70" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D70" s="17" t="n"/>
-      <c r="E70" s="29">
-        <f> 21.2 m² strop skladu</f>
-        <v/>
-      </c>
-      <c r="F70" s="17" t="n"/>
-      <c r="G70" s="30" t="n">
-        <v>21.209</v>
-      </c>
-      <c r="H70" s="17" t="n"/>
-      <c r="I70" s="17" t="n"/>
-      <c r="J70" s="17" t="n"/>
-      <c r="K70" s="17" t="n"/>
-      <c r="L70" s="17" t="n"/>
+      <c r="F70" s="21" t="n"/>
+      <c r="G70" s="21" t="n"/>
+      <c r="H70" s="21" t="n"/>
+      <c r="I70" s="21" t="n"/>
+      <c r="J70" s="21" t="n"/>
+      <c r="K70" s="21" t="n"/>
+      <c r="L70" s="21" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="23" t="n">
@@ -17647,21 +17639,21 @@
       </c>
       <c r="D71" s="24" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G71" s="25" t="n">
-        <v>22.26945</v>
+        <v>36.74</v>
       </c>
       <c r="H71" s="26" t="n"/>
       <c r="I71" s="26">
@@ -17694,12 +17686,12 @@
       <c r="D72" s="17" t="n"/>
       <c r="E72" s="29" t="inlineStr">
         <is>
-          <t>21.2 × 1.05 přesah</t>
+          <t>6.35/0.625 = 10.16 → 11 ks × 3.34 m (rozpon 3.1 + uložení) = 36.74 bm</t>
         </is>
       </c>
       <c r="F72" s="17" t="n"/>
       <c r="G72" s="30" t="n">
-        <v>22.26945</v>
+        <v>36.74</v>
       </c>
       <c r="H72" s="17" t="n"/>
       <c r="I72" s="17" t="n"/>
@@ -17718,21 +17710,21 @@
       </c>
       <c r="D73" s="24" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G73" s="25" t="n">
-        <v>921</v>
+        <v>21.209</v>
       </c>
       <c r="H73" s="26" t="n"/>
       <c r="I73" s="26">
@@ -17763,14 +17755,13 @@
         </is>
       </c>
       <c r="D74" s="17" t="n"/>
-      <c r="E74" s="29" t="inlineStr">
-        <is>
-          <t>7 ks × 7 m × 18.8 kg/m = 921</t>
-        </is>
+      <c r="E74" s="29">
+        <f> 21.2 m² strop skladu</f>
+        <v/>
       </c>
       <c r="F74" s="17" t="n"/>
       <c r="G74" s="30" t="n">
-        <v>921</v>
+        <v>21.209</v>
       </c>
       <c r="H74" s="17" t="n"/>
       <c r="I74" s="17" t="n"/>
@@ -17789,12 +17780,12 @@
       </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
@@ -17803,7 +17794,7 @@
         </is>
       </c>
       <c r="G75" s="25" t="n">
-        <v>44.6</v>
+        <v>22.26945</v>
       </c>
       <c r="H75" s="26" t="n"/>
       <c r="I75" s="26">
@@ -17815,9 +17806,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K75" s="31" t="inlineStr">
-        <is>
-          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
@@ -17836,12 +17827,12 @@
       <c r="D76" s="17" t="n"/>
       <c r="E76" s="29" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+          <t>21.2 × 1.05 přesah</t>
         </is>
       </c>
       <c r="F76" s="17" t="n"/>
       <c r="G76" s="30" t="n">
-        <v>44.6</v>
+        <v>22.26945</v>
       </c>
       <c r="H76" s="17" t="n"/>
       <c r="I76" s="17" t="n"/>
@@ -17860,12 +17851,12 @@
       </c>
       <c r="D77" s="24" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E77" s="24" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
@@ -17874,7 +17865,7 @@
         </is>
       </c>
       <c r="G77" s="25" t="n">
-        <v>1551</v>
+        <v>921</v>
       </c>
       <c r="H77" s="26" t="n"/>
       <c r="I77" s="26">
@@ -17905,13 +17896,14 @@
         </is>
       </c>
       <c r="D78" s="17" t="n"/>
-      <c r="E78" s="29">
-        <f> hmotnost IPE180 (921 kg) + odhad pororoštů (21 m² × 30 kg/m²) = ~1551</f>
-        <v/>
+      <c r="E78" s="29" t="inlineStr">
+        <is>
+          <t>7 ks × 7 m × 18.8 kg/m = 921</t>
+        </is>
       </c>
       <c r="F78" s="17" t="n"/>
       <c r="G78" s="30" t="n">
-        <v>1551</v>
+        <v>921</v>
       </c>
       <c r="H78" s="17" t="n"/>
       <c r="I78" s="17" t="n"/>
@@ -17920,125 +17912,145 @@
       <c r="L78" s="17" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="21" t="n"/>
-      <c r="C79" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D79" s="22" t="inlineStr">
-        <is>
-          <t>HSV-5</t>
-        </is>
-      </c>
-      <c r="E79" s="22" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-      <c r="F79" s="21" t="n"/>
-      <c r="G79" s="21" t="n"/>
-      <c r="H79" s="21" t="n"/>
-      <c r="I79" s="21" t="n"/>
-      <c r="J79" s="21" t="n"/>
-      <c r="K79" s="21" t="n"/>
-      <c r="L79" s="21" t="n"/>
+      <c r="B79" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C79" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>411321515</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G79" s="25" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H79" s="26" t="n"/>
+      <c r="I79" s="26">
+        <f>IF(H79="",0,G79*H79)</f>
+        <v/>
+      </c>
+      <c r="J79" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>⚠ family OK, leaf KROS lookup [evidence: https://www.cs-urs.cz/cenova-soustava-urs/]</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="B80" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="C80" s="23" t="inlineStr">
+      <c r="B80" s="17" t="n"/>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="n"/>
+      <c r="E80" s="29" t="inlineStr">
+        <is>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.01 (stání pororošt) = 44.60 m². Prior rough estimate 21.0 m² (7×3) under-counted by 112.4% — actual parking footprint covers full sklad+access zone 2 cars + manoeuvring strip.</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="n"/>
+      <c r="G80" s="30" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H80" s="17" t="n"/>
+      <c r="I80" s="17" t="n"/>
+      <c r="J80" s="17" t="n"/>
+      <c r="K80" s="17" t="n"/>
+      <c r="L80" s="17" t="n"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="C81" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D80" s="24" t="inlineStr">
-        <is>
-          <t>121301101</t>
-        </is>
-      </c>
-      <c r="E80" s="24" t="inlineStr">
-        <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
-        </is>
-      </c>
-      <c r="F80" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G80" s="25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H80" s="26" t="n"/>
-      <c r="I80" s="26">
-        <f>IF(H80="",0,G80*H80)</f>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>783201001</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G81" s="25" t="n">
+        <v>1551</v>
+      </c>
+      <c r="H81" s="26" t="n"/>
+      <c r="I81" s="26">
+        <f>IF(H81="",0,G81*H81)</f>
         <v/>
       </c>
-      <c r="J80" s="23" t="inlineStr">
+      <c r="J81" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K80" s="32" t="inlineStr">
+      <c r="K81" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L80" s="5" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + schodiště</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="17" t="n"/>
-      <c r="C81" s="28" t="inlineStr">
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="17" t="n"/>
+      <c r="C82" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D81" s="17" t="n"/>
-      <c r="E81" s="29" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
-        </is>
-      </c>
-      <c r="F81" s="17" t="n"/>
-      <c r="G81" s="30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H81" s="17" t="n"/>
-      <c r="I81" s="17" t="n"/>
-      <c r="J81" s="17" t="n"/>
-      <c r="K81" s="17" t="n"/>
-      <c r="L81" s="17" t="n"/>
-    </row>
-    <row r="82">
-      <c r="B82" s="19" t="n"/>
-      <c r="C82" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D82" s="20" t="inlineStr">
-        <is>
-          <t>PSV</t>
-        </is>
-      </c>
-      <c r="E82" s="20" t="inlineStr">
-        <is>
-          <t>Práce a dodávky PSV</t>
-        </is>
-      </c>
-      <c r="F82" s="19" t="n"/>
-      <c r="G82" s="19" t="n"/>
-      <c r="H82" s="19" t="n"/>
-      <c r="I82" s="19" t="n"/>
-      <c r="J82" s="19" t="n"/>
-      <c r="K82" s="19" t="n"/>
-      <c r="L82" s="19" t="n"/>
+      <c r="D82" s="17" t="n"/>
+      <c r="E82" s="29">
+        <f> hmotnost IPE180 (921 kg) + odhad pororoštů (21 m² × 30 kg/m²) = ~1551</f>
+        <v/>
+      </c>
+      <c r="F82" s="17" t="n"/>
+      <c r="G82" s="30" t="n">
+        <v>1551</v>
+      </c>
+      <c r="H82" s="17" t="n"/>
+      <c r="I82" s="17" t="n"/>
+      <c r="J82" s="17" t="n"/>
+      <c r="K82" s="17" t="n"/>
+      <c r="L82" s="17" t="n"/>
     </row>
     <row r="83">
       <c r="B83" s="21" t="n"/>
@@ -18049,12 +18061,12 @@
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>PSV-76</t>
+          <t>HSV-5</t>
         </is>
       </c>
       <c r="E83" s="22" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="F83" s="21" t="n"/>
@@ -18067,7 +18079,7 @@
     </row>
     <row r="84">
       <c r="B84" s="23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C84" s="23" t="inlineStr">
         <is>
@@ -18076,21 +18088,21 @@
       </c>
       <c r="D84" s="24" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E84" s="24" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G84" s="25" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="H84" s="26" t="n"/>
       <c r="I84" s="26">
@@ -18109,7 +18121,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
     </row>
@@ -18123,12 +18135,12 @@
       <c r="D85" s="17" t="n"/>
       <c r="E85" s="29" t="inlineStr">
         <is>
-          <t>1 ks vstupní dveře skladu</t>
+          <t>DXF sklad_DPZ km_tabulka místností: room 1.02 schodiště plocha = 5.50 m². 9 stupňů 179.5×250 mm vyznačené v půdoryse parking sheet (Phase 3.5 cross-check)</t>
         </is>
       </c>
       <c r="F85" s="17" t="n"/>
       <c r="G85" s="30" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="H85" s="17" t="n"/>
       <c r="I85" s="17" t="n"/>
@@ -18137,212 +18149,216 @@
       <c r="L85" s="17" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="21" t="n"/>
-      <c r="C86" s="22" t="inlineStr">
+      <c r="B86" s="19" t="n"/>
+      <c r="C86" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D86" s="22" t="inlineStr">
+      <c r="D86" s="20" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="E86" s="20" t="inlineStr">
+        <is>
+          <t>Práce a dodávky PSV</t>
+        </is>
+      </c>
+      <c r="F86" s="19" t="n"/>
+      <c r="G86" s="19" t="n"/>
+      <c r="H86" s="19" t="n"/>
+      <c r="I86" s="19" t="n"/>
+      <c r="J86" s="19" t="n"/>
+      <c r="K86" s="19" t="n"/>
+      <c r="L86" s="19" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="21" t="n"/>
+      <c r="C87" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="inlineStr">
         <is>
           <t>PSV-76</t>
         </is>
       </c>
-      <c r="E86" s="22" t="inlineStr">
+      <c r="E87" s="22" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+      <c r="F87" s="21" t="n"/>
+      <c r="G87" s="21" t="n"/>
+      <c r="H87" s="21" t="n"/>
+      <c r="I87" s="21" t="n"/>
+      <c r="J87" s="21" t="n"/>
+      <c r="K87" s="21" t="n"/>
+      <c r="L87" s="21" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="C88" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>766682111</t>
+        </is>
+      </c>
+      <c r="E88" s="24" t="inlineStr">
+        <is>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+        </is>
+      </c>
+      <c r="F88" s="23" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G88" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="26" t="n"/>
+      <c r="I88" s="26">
+        <f>IF(H88="",0,G88*H88)</f>
+        <v/>
+      </c>
+      <c r="J88" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K88" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>PSV-76 Výplně otvorů</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="17" t="n"/>
+      <c r="C89" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="n"/>
+      <c r="E89" s="29" t="inlineStr">
+        <is>
+          <t>1 ks vstupní dveře skladu</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="n"/>
+      <c r="G89" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="17" t="n"/>
+      <c r="I89" s="17" t="n"/>
+      <c r="J89" s="17" t="n"/>
+      <c r="K89" s="17" t="n"/>
+      <c r="L89" s="17" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="21" t="n"/>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>PSV-76</t>
+        </is>
+      </c>
+      <c r="E90" s="22" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
-      <c r="F86" s="21" t="n"/>
-      <c r="G86" s="21" t="n"/>
-      <c r="H86" s="21" t="n"/>
-      <c r="I86" s="21" t="n"/>
-      <c r="J86" s="21" t="n"/>
-      <c r="K86" s="21" t="n"/>
-      <c r="L86" s="21" t="n"/>
-    </row>
-    <row r="87">
-      <c r="B87" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="C87" s="23" t="inlineStr">
+      <c r="F90" s="21" t="n"/>
+      <c r="G90" s="21" t="n"/>
+      <c r="H90" s="21" t="n"/>
+      <c r="I90" s="21" t="n"/>
+      <c r="J90" s="21" t="n"/>
+      <c r="K90" s="21" t="n"/>
+      <c r="L90" s="21" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="C91" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D87" s="24" t="inlineStr"/>
-      <c r="E87" s="24" t="inlineStr">
+      <c r="D91" s="24" t="inlineStr"/>
+      <c r="E91" s="24" t="inlineStr">
         <is>
           <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
-      <c r="F87" s="23" t="inlineStr">
+      <c r="F91" s="23" t="inlineStr">
         <is>
           <t>ks</t>
         </is>
       </c>
-      <c r="G87" s="25" t="n">
+      <c r="G91" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H87" s="26" t="n"/>
-      <c r="I87" s="26">
-        <f>IF(H87="",0,G87*H87)</f>
+      <c r="H91" s="26" t="n"/>
+      <c r="I91" s="26">
+        <f>IF(H91="",0,G91*H91)</f>
         <v/>
       </c>
-      <c r="J87" s="23" t="inlineStr">
+      <c r="J91" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K87" s="33" t="inlineStr">
+      <c r="K91" s="33" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
-      <c r="L87" s="5" t="inlineStr">
+      <c r="L91" s="5" t="inlineStr">
         <is>
           <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="17" t="n"/>
-      <c r="C88" s="28" t="inlineStr">
+    <row r="92">
+      <c r="B92" s="17" t="n"/>
+      <c r="C92" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D88" s="17" t="n"/>
-      <c r="E88" s="29">
+      <c r="D92" s="17" t="n"/>
+      <c r="E92" s="29">
         <f> 1 brána (Dodatek PD č.1)</f>
         <v/>
       </c>
-      <c r="F88" s="17" t="n"/>
-      <c r="G88" s="30" t="n">
+      <c r="F92" s="17" t="n"/>
+      <c r="G92" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H88" s="17" t="n"/>
-      <c r="I88" s="17" t="n"/>
-      <c r="J88" s="17" t="n"/>
-      <c r="K88" s="17" t="n"/>
-      <c r="L88" s="17" t="n"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="21" t="n"/>
-      <c r="C89" s="22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D89" s="22" t="inlineStr">
-        <is>
-          <t>PSV-77</t>
-        </is>
-      </c>
-      <c r="E89" s="22" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="n"/>
-      <c r="H89" s="21" t="n"/>
-      <c r="I89" s="21" t="n"/>
-      <c r="J89" s="21" t="n"/>
-      <c r="K89" s="21" t="n"/>
-      <c r="L89" s="21" t="n"/>
-    </row>
-    <row r="90">
-      <c r="B90" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="C90" s="23" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D90" s="24" t="inlineStr"/>
-      <c r="E90" s="24" t="inlineStr">
-        <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
-        </is>
-      </c>
-      <c r="F90" s="23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G90" s="25" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="H90" s="26" t="n"/>
-      <c r="I90" s="26">
-        <f>IF(H90="",0,G90*H90)</f>
-        <v/>
-      </c>
-      <c r="J90" s="23" t="inlineStr">
-        <is>
-          <t>ÚRS 2026</t>
-        </is>
-      </c>
-      <c r="K90" s="33" t="inlineStr">
-        <is>
-          <t>❌ MANUAL — KROS catalog lookup</t>
-        </is>
-      </c>
-      <c r="L90" s="5" t="inlineStr">
-        <is>
-          <t>PSV-77 Podlahy</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="17" t="n"/>
-      <c r="C91" s="28" t="inlineStr">
-        <is>
-          <t>VV</t>
-        </is>
-      </c>
-      <c r="D91" s="17" t="n"/>
-      <c r="E91" s="29" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
-        </is>
-      </c>
-      <c r="F91" s="17" t="n"/>
-      <c r="G91" s="30" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="H91" s="17" t="n"/>
-      <c r="I91" s="17" t="n"/>
-      <c r="J91" s="17" t="n"/>
-      <c r="K91" s="17" t="n"/>
-      <c r="L91" s="17" t="n"/>
-    </row>
-    <row r="92">
-      <c r="B92" s="19" t="n"/>
-      <c r="C92" s="20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D92" s="20" t="inlineStr">
-        <is>
-          <t>VRN</t>
-        </is>
-      </c>
-      <c r="E92" s="20" t="inlineStr">
-        <is>
-          <t>Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="F92" s="19" t="n"/>
-      <c r="G92" s="19" t="n"/>
-      <c r="H92" s="19" t="n"/>
-      <c r="I92" s="19" t="n"/>
-      <c r="J92" s="19" t="n"/>
-      <c r="K92" s="19" t="n"/>
-      <c r="L92" s="19" t="n"/>
+      <c r="H92" s="17" t="n"/>
+      <c r="I92" s="17" t="n"/>
+      <c r="J92" s="17" t="n"/>
+      <c r="K92" s="17" t="n"/>
+      <c r="L92" s="17" t="n"/>
     </row>
     <row r="93">
       <c r="B93" s="21" t="n"/>
@@ -18353,12 +18369,12 @@
       </c>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>VRN</t>
+          <t>PSV-77</t>
         </is>
       </c>
       <c r="E93" s="22" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="F93" s="21" t="n"/>
@@ -18371,30 +18387,26 @@
     </row>
     <row r="94">
       <c r="B94" s="23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C94" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D94" s="24" t="inlineStr">
-        <is>
-          <t>030001000</t>
-        </is>
-      </c>
+      <c r="D94" s="24" t="inlineStr"/>
       <c r="E94" s="24" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G94" s="25" t="n">
-        <v>1</v>
+        <v>17.6</v>
       </c>
       <c r="H94" s="26" t="n"/>
       <c r="I94" s="26">
@@ -18406,14 +18418,14 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K94" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K94" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
     </row>
@@ -18427,12 +18439,12 @@
       <c r="D95" s="17" t="n"/>
       <c r="E95" s="29" t="inlineStr">
         <is>
-          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 0.01 (sklad zahradní techniky) = 17.60 m² (inner usable area per DXF room table, walls excluded). Prior estimate 21.209 m² (outer 6.35×3.34) over-counted by 17.0% — walls of tvarovky ZB tl. 250 mm take ~3.6 m² of outer footprint.</t>
         </is>
       </c>
       <c r="F95" s="17" t="n"/>
       <c r="G95" s="30" t="n">
-        <v>1</v>
+        <v>17.6</v>
       </c>
       <c r="H95" s="17" t="n"/>
       <c r="I95" s="17" t="n"/>
@@ -18441,267 +18453,388 @@
       <c r="L95" s="17" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="21" t="n"/>
-      <c r="C96" s="22" t="inlineStr">
+      <c r="B96" s="19" t="n"/>
+      <c r="C96" s="20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D96" s="22" t="inlineStr">
+      <c r="D96" s="20" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E96" s="22" t="inlineStr">
+      <c r="E96" s="20" t="inlineStr">
+        <is>
+          <t>Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="F96" s="19" t="n"/>
+      <c r="G96" s="19" t="n"/>
+      <c r="H96" s="19" t="n"/>
+      <c r="I96" s="19" t="n"/>
+      <c r="J96" s="19" t="n"/>
+      <c r="K96" s="19" t="n"/>
+      <c r="L96" s="19" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="21" t="n"/>
+      <c r="C97" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E97" s="22" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="F97" s="21" t="n"/>
+      <c r="G97" s="21" t="n"/>
+      <c r="H97" s="21" t="n"/>
+      <c r="I97" s="21" t="n"/>
+      <c r="J97" s="21" t="n"/>
+      <c r="K97" s="21" t="n"/>
+      <c r="L97" s="21" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="C98" s="23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D98" s="24" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E98" s="24" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G98" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="26" t="n"/>
+      <c r="I98" s="26">
+        <f>IF(H98="",0,G98*H98)</f>
+        <v/>
+      </c>
+      <c r="J98" s="23" t="inlineStr">
+        <is>
+          <t>ÚRS 2026</t>
+        </is>
+      </c>
+      <c r="K98" s="32" t="inlineStr">
+        <is>
+          <t>? needs production lookup</t>
+        </is>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="17" t="n"/>
+      <c r="C99" s="28" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D99" s="17" t="n"/>
+      <c r="E99" s="29" t="inlineStr">
+        <is>
+          <t>Standard paušální alokace VRN pro paralelně realizovaný menší objekt</t>
+        </is>
+      </c>
+      <c r="F99" s="17" t="n"/>
+      <c r="G99" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="17" t="n"/>
+      <c r="I99" s="17" t="n"/>
+      <c r="J99" s="17" t="n"/>
+      <c r="K99" s="17" t="n"/>
+      <c r="L99" s="17" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="21" t="n"/>
+      <c r="C100" s="22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D100" s="22" t="inlineStr">
+        <is>
+          <t>VRN</t>
+        </is>
+      </c>
+      <c r="E100" s="22" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
-      <c r="F96" s="21" t="n"/>
-      <c r="G96" s="21" t="n"/>
-      <c r="H96" s="21" t="n"/>
-      <c r="I96" s="21" t="n"/>
-      <c r="J96" s="21" t="n"/>
-      <c r="K96" s="21" t="n"/>
-      <c r="L96" s="21" t="n"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="23" t="n">
-        <v>27</v>
-      </c>
-      <c r="C97" s="23" t="inlineStr">
+      <c r="F100" s="21" t="n"/>
+      <c r="G100" s="21" t="n"/>
+      <c r="H100" s="21" t="n"/>
+      <c r="I100" s="21" t="n"/>
+      <c r="J100" s="21" t="n"/>
+      <c r="K100" s="21" t="n"/>
+      <c r="L100" s="21" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="C101" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D97" s="24" t="inlineStr">
+      <c r="D101" s="24" t="inlineStr">
         <is>
           <t>031032000</t>
         </is>
       </c>
-      <c r="E97" s="24" t="inlineStr">
+      <c r="E101" s="24" t="inlineStr">
         <is>
           <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
-      <c r="F97" s="23" t="inlineStr">
+      <c r="F101" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G97" s="25" t="n">
+      <c r="G101" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H97" s="26" t="n"/>
-      <c r="I97" s="26">
-        <f>IF(H97="",0,G97*H97)</f>
+      <c r="H101" s="26" t="n"/>
+      <c r="I101" s="26">
+        <f>IF(H101="",0,G101*H101)</f>
         <v/>
       </c>
-      <c r="J97" s="23" t="inlineStr">
+      <c r="J101" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K97" s="32" t="inlineStr">
+      <c r="K101" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="L101" s="5" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="17" t="n"/>
-      <c r="C98" s="28" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="17" t="n"/>
+      <c r="C102" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D98" s="17" t="n"/>
-      <c r="E98" s="29" t="inlineStr">
+      <c r="D102" s="17" t="n"/>
+      <c r="E102" s="29" t="inlineStr">
         <is>
           <t>Standard doprava prefa Herkul autem s hyd. rukou pro lokální distribuci</t>
         </is>
       </c>
-      <c r="F98" s="17" t="n"/>
-      <c r="G98" s="30" t="n">
+      <c r="F102" s="17" t="n"/>
+      <c r="G102" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H98" s="17" t="n"/>
-      <c r="I98" s="17" t="n"/>
-      <c r="J98" s="17" t="n"/>
-      <c r="K98" s="17" t="n"/>
-      <c r="L98" s="17" t="n"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="C99" s="23" t="inlineStr">
+      <c r="H102" s="17" t="n"/>
+      <c r="I102" s="17" t="n"/>
+      <c r="J102" s="17" t="n"/>
+      <c r="K102" s="17" t="n"/>
+      <c r="L102" s="17" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="C103" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D99" s="24" t="inlineStr">
+      <c r="D103" s="24" t="inlineStr">
         <is>
           <t>997013211</t>
         </is>
       </c>
-      <c r="E99" s="24" t="inlineStr">
+      <c r="E103" s="24" t="inlineStr">
         <is>
           <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
-      <c r="F99" s="23" t="inlineStr">
+      <c r="F103" s="23" t="inlineStr">
         <is>
           <t>t</t>
         </is>
       </c>
-      <c r="G99" s="25" t="n">
+      <c r="G103" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="H99" s="26" t="n"/>
-      <c r="I99" s="26">
-        <f>IF(H99="",0,G99*H99)</f>
+      <c r="H103" s="26" t="n"/>
+      <c r="I103" s="26">
+        <f>IF(H103="",0,G103*H103)</f>
         <v/>
       </c>
-      <c r="J99" s="23" t="inlineStr">
+      <c r="J103" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K99" s="32" t="inlineStr">
+      <c r="K103" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>VRN — Doprava + odpad</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="17" t="n"/>
-      <c r="C100" s="28" t="inlineStr">
+    <row r="104">
+      <c r="B104" s="17" t="n"/>
+      <c r="C104" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D100" s="17" t="n"/>
-      <c r="E100" s="29" t="inlineStr">
+      <c r="D104" s="17" t="n"/>
+      <c r="E104" s="29" t="inlineStr">
         <is>
           <t>Odhad: kamenné zídky ~6 t + dřevo+výkop ~2 t = 8 t</t>
         </is>
       </c>
-      <c r="F100" s="17" t="n"/>
-      <c r="G100" s="30" t="n">
+      <c r="F104" s="17" t="n"/>
+      <c r="G104" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="H100" s="17" t="n"/>
-      <c r="I100" s="17" t="n"/>
-      <c r="J100" s="17" t="n"/>
-      <c r="K100" s="17" t="n"/>
-      <c r="L100" s="17" t="n"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="21" t="n"/>
-      <c r="C101" s="22" t="inlineStr">
+      <c r="H104" s="17" t="n"/>
+      <c r="I104" s="17" t="n"/>
+      <c r="J104" s="17" t="n"/>
+      <c r="K104" s="17" t="n"/>
+      <c r="L104" s="17" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="21" t="n"/>
+      <c r="C105" s="22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D101" s="22" t="inlineStr">
+      <c r="D105" s="22" t="inlineStr">
         <is>
           <t>VRN</t>
         </is>
       </c>
-      <c r="E101" s="22" t="inlineStr">
+      <c r="E105" s="22" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
-      <c r="F101" s="21" t="n"/>
-      <c r="G101" s="21" t="n"/>
-      <c r="H101" s="21" t="n"/>
-      <c r="I101" s="21" t="n"/>
-      <c r="J101" s="21" t="n"/>
-      <c r="K101" s="21" t="n"/>
-      <c r="L101" s="21" t="n"/>
-    </row>
-    <row r="102">
-      <c r="B102" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="C102" s="23" t="inlineStr">
+      <c r="F105" s="21" t="n"/>
+      <c r="G105" s="21" t="n"/>
+      <c r="H105" s="21" t="n"/>
+      <c r="I105" s="21" t="n"/>
+      <c r="J105" s="21" t="n"/>
+      <c r="K105" s="21" t="n"/>
+      <c r="L105" s="21" t="n"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="C106" s="23" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D102" s="24" t="inlineStr">
+      <c r="D106" s="24" t="inlineStr">
         <is>
           <t>030141000</t>
         </is>
       </c>
-      <c r="E102" s="24" t="inlineStr">
+      <c r="E106" s="24" t="inlineStr">
         <is>
           <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
-      <c r="F102" s="23" t="inlineStr">
+      <c r="F106" s="23" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="G102" s="25" t="n">
+      <c r="G106" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H102" s="26" t="n"/>
-      <c r="I102" s="26">
-        <f>IF(H102="",0,G102*H102)</f>
+      <c r="H106" s="26" t="n"/>
+      <c r="I106" s="26">
+        <f>IF(H106="",0,G106*H106)</f>
         <v/>
       </c>
-      <c r="J102" s="23" t="inlineStr">
+      <c r="J106" s="23" t="inlineStr">
         <is>
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K102" s="32" t="inlineStr">
+      <c r="K106" s="32" t="inlineStr">
         <is>
           <t>? needs production lookup</t>
         </is>
       </c>
-      <c r="L102" s="5" t="inlineStr">
+      <c r="L106" s="5" t="inlineStr">
         <is>
           <t>VRN — Geodet</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" s="17" t="n"/>
-      <c r="C103" s="28" t="inlineStr">
+    <row r="107">
+      <c r="B107" s="17" t="n"/>
+      <c r="C107" s="28" t="inlineStr">
         <is>
           <t>VV</t>
         </is>
       </c>
-      <c r="D103" s="17" t="n"/>
-      <c r="E103" s="29" t="inlineStr">
+      <c r="D107" s="17" t="n"/>
+      <c r="E107" s="29" t="inlineStr">
         <is>
           <t>Standard geodet vytýčení pro nový objekt</t>
         </is>
       </c>
-      <c r="F103" s="17" t="n"/>
-      <c r="G103" s="30" t="n">
+      <c r="F107" s="17" t="n"/>
+      <c r="G107" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H103" s="17" t="n"/>
-      <c r="I103" s="17" t="n"/>
-      <c r="J103" s="17" t="n"/>
-      <c r="K103" s="17" t="n"/>
-      <c r="L103" s="17" t="n"/>
+      <c r="H107" s="17" t="n"/>
+      <c r="I107" s="17" t="n"/>
+      <c r="J107" s="17" t="n"/>
+      <c r="K107" s="17" t="n"/>
+      <c r="L107" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -18727,7 +18860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H251"/>
+  <dimension ref="B2:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -18806,7 +18939,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -18816,7 +18949,7 @@
         </is>
       </c>
       <c r="C10" s="34" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13">
@@ -26466,6 +26599,64 @@
         </is>
       </c>
       <c r="H251" s="24" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.004</t>
+        </is>
+      </c>
+      <c r="C252" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D252" s="24" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="E252" s="24" t="inlineStr"/>
+      <c r="F252" s="24" t="inlineStr"/>
+      <c r="G252" s="24" t="inlineStr">
+        <is>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné s</t>
+        </is>
+      </c>
+      <c r="H252" s="24" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.005</t>
+        </is>
+      </c>
+      <c r="C253" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="D253" s="24" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="E253" s="24" t="inlineStr"/>
+      <c r="F253" s="24" t="inlineStr"/>
+      <c r="G253" s="24" t="inlineStr">
+        <is>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + op</t>
+        </is>
+      </c>
+      <c r="H253" s="24" t="inlineStr">
         <is>
           <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
@@ -26493,7 +26684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N232"/>
+  <dimension ref="B2:N234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -36470,6 +36661,72 @@
       <c r="M232" s="24" t="inlineStr"/>
       <c r="N232" s="24" t="inlineStr"/>
     </row>
+    <row r="233">
+      <c r="B233" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.004</t>
+        </is>
+      </c>
+      <c r="C233" s="24" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="D233" s="24" t="inlineStr">
+        <is>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04)</t>
+        </is>
+      </c>
+      <c r="E233" s="24" t="inlineStr"/>
+      <c r="F233" s="24" t="inlineStr"/>
+      <c r="G233" s="24" t="inlineStr"/>
+      <c r="H233" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I233" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="33" t="inlineStr"/>
+      <c r="K233" s="24" t="inlineStr"/>
+      <c r="L233" s="24" t="inlineStr"/>
+      <c r="M233" s="24" t="inlineStr"/>
+      <c r="N233" s="24" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="B234" s="24" t="inlineStr">
+        <is>
+          <t>260217_sklad.HSV3.005</t>
+        </is>
+      </c>
+      <c r="C234" s="24" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="D234" s="24" t="inlineStr">
+        <is>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěn</t>
+        </is>
+      </c>
+      <c r="E234" s="24" t="inlineStr"/>
+      <c r="F234" s="24" t="inlineStr"/>
+      <c r="G234" s="24" t="inlineStr"/>
+      <c r="H234" s="24" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="I234" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="33" t="inlineStr"/>
+      <c r="K234" s="24" t="inlineStr"/>
+      <c r="L234" s="24" t="inlineStr"/>
+      <c r="M234" s="24" t="inlineStr"/>
+      <c r="N234" s="24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
@@ -17316,7 +17316,7 @@
       <c r="D61" s="17" t="n"/>
       <c r="E61" s="29" t="inlineStr">
         <is>
-          <t>odhad — výška ~1.6 m × šíře 6.35 m / blok 0.8×0.4 = ~32 bloků × 2 řady = 64; round 60</t>
+          <t>opěrná stěna S04 face 6.35 × 3.0 m (řez A-A: stěna 3000 + zákl. 1000) = 19.05 m² ÷ ~0.32 m²/blok ≈ 60 ks (OVĚŘIT rozměr H-BLOK z tech. listu)</t>
         </is>
       </c>
       <c r="F61" s="17" t="n"/>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="G60" s="25" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H60" s="26" t="n"/>
       <c r="I60" s="26">
@@ -17316,12 +17316,12 @@
       <c r="D61" s="17" t="n"/>
       <c r="E61" s="29" t="inlineStr">
         <is>
-          <t>opěrná stěna S04 face 6.35 × 3.0 m (řez A-A: stěna 3000 + zákl. 1000) = 19.05 m² ÷ ~0.32 m²/blok ≈ 60 ks (OVĚŘIT rozměr H-BLOK z tech. listu)</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m² ÷ 1.08 m²/blok (H-BLOK Standard 1800×600mm líc, web-ověřeno) = 17.6 → 18 ks; layout: 4 bloky/řada × 5 řad = 20 ks (s řezy) — použito 18 ks plocha-přesné</t>
         </is>
       </c>
       <c r="F61" s="17" t="n"/>
       <c r="G61" s="30" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H61" s="17" t="n"/>
       <c r="I61" s="17" t="n"/>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
@@ -17316,7 +17316,7 @@
       <c r="D61" s="17" t="n"/>
       <c r="E61" s="29" t="inlineStr">
         <is>
-          <t>S04 líc 6.35 × 3.0 m = 19.05 m² ÷ 1.08 m²/blok (H-BLOK Standard 1800×600mm líc, web-ověřeno) = 17.6 → 18 ks; layout: 4 bloky/řada × 5 řad = 20 ks (s řezy) — použito 18 ks plocha-přesné</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m² (řez A-A measured) ÷ ~1.08 m²/blok = 17.6 → 18 ks. POZOR: rozměr bloku 1800×600 mm je ODHAD z analogie (web BB6 stejných gabaritů + AI-souhrn), NE z Herkul tech. listu napřímo (hblok.cz nedostupný). H-BLOK má interlocking profil — modul může být jiný. OVĚŘIT u Herkul.</t>
         </is>
       </c>
       <c r="F61" s="17" t="n"/>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-06-01_v3_final.xlsx
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="G60" s="25" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H60" s="26" t="n"/>
       <c r="I60" s="26">
@@ -17316,12 +17316,12 @@
       <c r="D61" s="17" t="n"/>
       <c r="E61" s="29" t="inlineStr">
         <is>
-          <t>opěrná stěna S04 face 6.35 × 3.0 m (řez A-A: stěna 3000 + zákl. 1000) = 19.05 m² ÷ ~0.32 m²/blok ≈ 60 ks (OVĚŘIT rozměr H-BLOK z tech. listu)</t>
+          <t>S04 líc 6.35 × 3.0 m = 19.05 m² (řez A-A measured) ÷ ~1.08 m²/blok = 17.6 → 18 ks. POZOR: rozměr bloku 1800×600 mm je ODHAD z analogie (web BB6 stejných gabaritů + AI-souhrn), NE z Herkul tech. listu napřímo (hblok.cz nedostupný). H-BLOK má interlocking profil — modul může být jiný. OVĚŘIT u Herkul.</t>
         </is>
       </c>
       <c r="F61" s="17" t="n"/>
       <c r="G61" s="30" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H61" s="17" t="n"/>
       <c r="I61" s="17" t="n"/>
